--- a/catalog/MFL_Dataset_Registry.xlsx
+++ b/catalog/MFL_Dataset_Registry.xlsx
@@ -20,7 +20,7 @@
     <definedName name="MOSAIC_Access">Reference!$I$2:$I$4</definedName>
     <definedName name="MOSAIC_Migration">Reference!$O$2:$O$3</definedName>
     <definedName name="MOSAIC_UpdFreq">Reference!$Q$2:$Q$7</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">' Registry'!$A$2:$W$91</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">' Registry'!$A$2:$W$96</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -1221,7 +1221,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W91"/>
+  <dimension ref="A1:W96"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -9975,8 +9975,553 @@
       </c>
       <c r="W91" s="8" t="n"/>
     </row>
+    <row r="92">
+      <c r="A92" s="10" t="inlineStr">
+        <is>
+          <t>MFL-2026-093</t>
+        </is>
+      </c>
+      <c r="B92" s="10" t="inlineStr">
+        <is>
+          <t>Land cover Kef-Siliana region (2017)</t>
+        </is>
+      </c>
+      <c r="C92" s="10" t="inlineStr">
+        <is>
+          <t>Tunisia</t>
+        </is>
+      </c>
+      <c r="D92" s="10" t="inlineStr">
+        <is>
+          <t>Land cover / land use</t>
+        </is>
+      </c>
+      <c r="E92" s="10" t="inlineStr">
+        <is>
+          <t>TUN-NW — Northwestern Tunisia</t>
+        </is>
+      </c>
+      <c r="F92" s="10" t="inlineStr">
+        <is>
+          <t>Raster</t>
+        </is>
+      </c>
+      <c r="G92" s="10" t="inlineStr">
+        <is>
+          <t>10 m</t>
+        </is>
+      </c>
+      <c r="H92" s="10" t="inlineStr">
+        <is>
+          <t>2017</t>
+        </is>
+      </c>
+      <c r="I92" s="10" t="inlineStr">
+        <is>
+          <t>ICARDA</t>
+        </is>
+      </c>
+      <c r="J92" s="10" t="inlineStr">
+        <is>
+          <t>Layal Atassi (l.atassi@cgiar.org)</t>
+        </is>
+      </c>
+      <c r="K92" s="10" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="L92" s="10" t="inlineStr">
+        <is>
+          <t>CC BY-SA 4.0</t>
+        </is>
+      </c>
+      <c r="M92" s="10" t="inlineStr">
+        <is>
+          <t>Processed</t>
+        </is>
+      </c>
+      <c r="N92" s="10" t="inlineStr">
+        <is>
+          <t>Land_cover_Kef_Siliana_region_2017.tif; LC_2017.csv</t>
+        </is>
+      </c>
+      <c r="O92" s="10" t="inlineStr">
+        <is>
+          <t>MEL data portal (data.mel.cgiar.org)</t>
+        </is>
+      </c>
+      <c r="P92" s="10" t="n"/>
+      <c r="Q92" s="10" t="n"/>
+      <c r="R92" s="11" t="inlineStr">
+        <is>
+          <t>Land cover map of the Kef-Siliana region, Tunisia, for 2017, produced by ICARDA from ESRI Sentinel-2 Land Cover Explorer rasters (ArcGIS Living Atlas of the World), 10 m cell size. Classes 1 Water; 2 Forest; 4 Flooded vegetation; 5 Crop; 7 Built area; 8 Bare land; 11 Rangeland. Source data coordinate system UTM WGS 84; service coordinate system Web Mercator Auxiliary Sphere WGS 84 (EPSG:3857). Published on ICARDA's MEL data portal with data dictionaries; MOSAIC links to it there.</t>
+        </is>
+      </c>
+      <c r="S92" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="T92" s="10" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="U92" s="10" t="inlineStr">
+        <is>
+          <t>Static</t>
+        </is>
+      </c>
+      <c r="V92" s="10" t="inlineStr">
+        <is>
+          <t>https://hdl.handle.net/20.500.11766.1/FK2/HNCLNU</t>
+        </is>
+      </c>
+      <c r="W92" s="10" t="inlineStr">
+        <is>
+          <t>143 MB</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="8" t="inlineStr">
+        <is>
+          <t>MFL-2026-094</t>
+        </is>
+      </c>
+      <c r="B93" s="8" t="inlineStr">
+        <is>
+          <t>Land cover Kef-Siliana region (2022)</t>
+        </is>
+      </c>
+      <c r="C93" s="8" t="inlineStr">
+        <is>
+          <t>Tunisia</t>
+        </is>
+      </c>
+      <c r="D93" s="8" t="inlineStr">
+        <is>
+          <t>Land cover / land use</t>
+        </is>
+      </c>
+      <c r="E93" s="8" t="inlineStr">
+        <is>
+          <t>TUN-NW — Northwestern Tunisia</t>
+        </is>
+      </c>
+      <c r="F93" s="8" t="inlineStr">
+        <is>
+          <t>Raster</t>
+        </is>
+      </c>
+      <c r="G93" s="8" t="inlineStr">
+        <is>
+          <t>10 m</t>
+        </is>
+      </c>
+      <c r="H93" s="8" t="inlineStr">
+        <is>
+          <t>2022</t>
+        </is>
+      </c>
+      <c r="I93" s="8" t="inlineStr">
+        <is>
+          <t>ICARDA</t>
+        </is>
+      </c>
+      <c r="J93" s="8" t="inlineStr">
+        <is>
+          <t>Layal Atassi (l.atassi@cgiar.org)</t>
+        </is>
+      </c>
+      <c r="K93" s="8" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="L93" s="8" t="inlineStr">
+        <is>
+          <t>CC BY-SA 4.0</t>
+        </is>
+      </c>
+      <c r="M93" s="8" t="inlineStr">
+        <is>
+          <t>Processed</t>
+        </is>
+      </c>
+      <c r="N93" s="8" t="inlineStr">
+        <is>
+          <t>Land_cover_Kef_Siliana_region_2022.tif; LC_2022.csv</t>
+        </is>
+      </c>
+      <c r="O93" s="8" t="inlineStr">
+        <is>
+          <t>MEL data portal (data.mel.cgiar.org)</t>
+        </is>
+      </c>
+      <c r="P93" s="8" t="n"/>
+      <c r="Q93" s="8" t="n"/>
+      <c r="R93" s="9" t="inlineStr">
+        <is>
+          <t>Land cover map of the Kef-Siliana region, Tunisia, for 2022, produced by ICARDA from ESRI Sentinel-2 Land Cover Explorer rasters (ArcGIS Living Atlas of the World), 10 m cell size. Classes 1 Water; 2 Forest; 4 Flooded vegetation; 5 Crop; 7 Built area; 8 Bare land; 11 Rangeland. Source data coordinate system UTM WGS 84; service coordinate system Web Mercator Auxiliary Sphere WGS 84 (EPSG:3857). Companion to the 2017 map (MFL-2026-093). Published on ICARDA's MEL data portal with data dictionaries; MOSAIC links to it there.</t>
+        </is>
+      </c>
+      <c r="S93" s="8" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="T93" s="8" t="inlineStr">
+        <is>
+          <t>2025-10-30</t>
+        </is>
+      </c>
+      <c r="U93" s="8" t="inlineStr">
+        <is>
+          <t>Static</t>
+        </is>
+      </c>
+      <c r="V93" s="8" t="inlineStr">
+        <is>
+          <t>https://hdl.handle.net/20.500.11766.1/FK2/H4QIFS</t>
+        </is>
+      </c>
+      <c r="W93" s="8" t="inlineStr">
+        <is>
+          <t>143 MB</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="10" t="inlineStr">
+        <is>
+          <t>MFL-2026-095</t>
+        </is>
+      </c>
+      <c r="B94" s="10" t="inlineStr">
+        <is>
+          <t>Land Cover change in Kef-Siliana region (2017-2022)</t>
+        </is>
+      </c>
+      <c r="C94" s="10" t="inlineStr">
+        <is>
+          <t>Tunisia</t>
+        </is>
+      </c>
+      <c r="D94" s="10" t="inlineStr">
+        <is>
+          <t>Land cover / land use</t>
+        </is>
+      </c>
+      <c r="E94" s="10" t="inlineStr">
+        <is>
+          <t>TUN-NW — Northwestern Tunisia</t>
+        </is>
+      </c>
+      <c r="F94" s="10" t="inlineStr">
+        <is>
+          <t>Raster</t>
+        </is>
+      </c>
+      <c r="G94" s="10" t="inlineStr">
+        <is>
+          <t>10 m</t>
+        </is>
+      </c>
+      <c r="H94" s="10" t="inlineStr">
+        <is>
+          <t>2017-2022</t>
+        </is>
+      </c>
+      <c r="I94" s="10" t="inlineStr">
+        <is>
+          <t>ICARDA</t>
+        </is>
+      </c>
+      <c r="J94" s="10" t="inlineStr">
+        <is>
+          <t>Layal Atassi (l.atassi@cgiar.org)</t>
+        </is>
+      </c>
+      <c r="K94" s="10" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="L94" s="10" t="inlineStr">
+        <is>
+          <t>CC BY-SA 4.0</t>
+        </is>
+      </c>
+      <c r="M94" s="10" t="inlineStr">
+        <is>
+          <t>Processed</t>
+        </is>
+      </c>
+      <c r="N94" s="10" t="inlineStr">
+        <is>
+          <t>Land_Cover_change_in_Kef_Siliana_region_2017_2022.tif; LCC_2017_2022.csv</t>
+        </is>
+      </c>
+      <c r="O94" s="10" t="inlineStr">
+        <is>
+          <t>MEL data portal (data.mel.cgiar.org)</t>
+        </is>
+      </c>
+      <c r="P94" s="10" t="n"/>
+      <c r="Q94" s="10" t="n"/>
+      <c r="R94" s="11" t="inlineStr">
+        <is>
+          <t>Land cover change map of the Kef-Siliana region, Tunisia, between 2017 and 2022, derived from the two land cover maps (MFL-2026-093 and MFL-2026-094) with the Semi-Automatic Classification Plugin in QGIS 3.28.15, 10 m cell size. Pixel values encode the 49 from-to transitions between the seven land cover classes (Water, Forest, Flooded vegetation, Crop, Built area, Bare land, Rangeland); the full key is in the deposit's data dictionary. Source data coordinate system UTM WGS 84; service coordinate system Web Mercator Auxiliary Sphere WGS 84 (EPSG:3857). Published on ICARDA's MEL data portal; MOSAIC links to it there.</t>
+        </is>
+      </c>
+      <c r="S94" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="T94" s="10" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="U94" s="10" t="inlineStr">
+        <is>
+          <t>Static</t>
+        </is>
+      </c>
+      <c r="V94" s="10" t="inlineStr">
+        <is>
+          <t>https://hdl.handle.net/20.500.11766.1/FK2/YUXPQY</t>
+        </is>
+      </c>
+      <c r="W94" s="10" t="inlineStr">
+        <is>
+          <t>14 MB</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="8" t="inlineStr">
+        <is>
+          <t>MFL-2026-096</t>
+        </is>
+      </c>
+      <c r="B95" s="8" t="inlineStr">
+        <is>
+          <t>Data on landscape metrics at different scales, Kef-Siliana region and sub-spatial units of the Agroecological Living Lab Landscape in Tunisia (2017-2022)</t>
+        </is>
+      </c>
+      <c r="C95" s="8" t="inlineStr">
+        <is>
+          <t>Tunisia</t>
+        </is>
+      </c>
+      <c r="D95" s="8" t="inlineStr">
+        <is>
+          <t>Ecosystem condition</t>
+        </is>
+      </c>
+      <c r="E95" s="8" t="inlineStr">
+        <is>
+          <t>TUN-NW — Northwestern Tunisia</t>
+        </is>
+      </c>
+      <c r="F95" s="8" t="inlineStr">
+        <is>
+          <t>Tabular</t>
+        </is>
+      </c>
+      <c r="G95" s="8" t="inlineStr">
+        <is>
+          <t>Region and sub-landscape spatial units</t>
+        </is>
+      </c>
+      <c r="H95" s="8" t="inlineStr">
+        <is>
+          <t>2017-2022</t>
+        </is>
+      </c>
+      <c r="I95" s="8" t="inlineStr">
+        <is>
+          <t>ICARDA</t>
+        </is>
+      </c>
+      <c r="J95" s="8" t="inlineStr">
+        <is>
+          <t>Layal Atassi (l.atassi@cgiar.org)</t>
+        </is>
+      </c>
+      <c r="K95" s="8" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="L95" s="8" t="inlineStr">
+        <is>
+          <t>CC BY-SA 4.0</t>
+        </is>
+      </c>
+      <c r="M95" s="8" t="inlineStr">
+        <is>
+          <t>Processed</t>
+        </is>
+      </c>
+      <c r="N95" s="8" t="inlineStr">
+        <is>
+          <t>LM_KS_data.csv; LM_ALL_data.csv</t>
+        </is>
+      </c>
+      <c r="O95" s="8" t="inlineStr">
+        <is>
+          <t>MEL data portal (data.mel.cgiar.org)</t>
+        </is>
+      </c>
+      <c r="P95" s="8" t="n"/>
+      <c r="Q95" s="8" t="n"/>
+      <c r="R95" s="9" t="inlineStr">
+        <is>
+          <t>Landscape metrics computed from the 2017 and 2022 land cover maps of the Kef-Siliana region (MFL-2026-093 and MFL-2026-094) with the LecoS plugin in QGIS 3.28.15, at two scales - the Kef-Siliana region as a whole and the sub-spatial units of the Agroecological Living Lab Landscape in Tunisia. Delivered as two CSV tables with data dictionaries. Published on ICARDA's MEL data portal; MOSAIC links to it there.</t>
+        </is>
+      </c>
+      <c r="S95" s="8" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="T95" s="8" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="U95" s="8" t="inlineStr">
+        <is>
+          <t>Static</t>
+        </is>
+      </c>
+      <c r="V95" s="8" t="inlineStr">
+        <is>
+          <t>https://hdl.handle.net/20.500.11766.1/FK2/UN7DKQ</t>
+        </is>
+      </c>
+      <c r="W95" s="8" t="inlineStr">
+        <is>
+          <t>9.5 KB</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="10" t="inlineStr">
+        <is>
+          <t>MFL-2026-097</t>
+        </is>
+      </c>
+      <c r="B96" s="10" t="inlineStr">
+        <is>
+          <t>Data on the dynamics of Land Cover at different scales, Kef-Siliana region and sub-spatial units of the Agroecological Living Lab Landscape in Tunisia (2017-2022)</t>
+        </is>
+      </c>
+      <c r="C96" s="10" t="inlineStr">
+        <is>
+          <t>Tunisia</t>
+        </is>
+      </c>
+      <c r="D96" s="10" t="inlineStr">
+        <is>
+          <t>Degradation / land health</t>
+        </is>
+      </c>
+      <c r="E96" s="10" t="inlineStr">
+        <is>
+          <t>TUN-NW — Northwestern Tunisia</t>
+        </is>
+      </c>
+      <c r="F96" s="10" t="inlineStr">
+        <is>
+          <t>Tabular</t>
+        </is>
+      </c>
+      <c r="G96" s="10" t="inlineStr">
+        <is>
+          <t>Region and sub-landscape spatial units</t>
+        </is>
+      </c>
+      <c r="H96" s="10" t="inlineStr">
+        <is>
+          <t>2017-2022</t>
+        </is>
+      </c>
+      <c r="I96" s="10" t="inlineStr">
+        <is>
+          <t>ICARDA</t>
+        </is>
+      </c>
+      <c r="J96" s="10" t="inlineStr">
+        <is>
+          <t>Layal Atassi (l.atassi@cgiar.org)</t>
+        </is>
+      </c>
+      <c r="K96" s="10" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="L96" s="10" t="inlineStr">
+        <is>
+          <t>CC BY-SA 4.0</t>
+        </is>
+      </c>
+      <c r="M96" s="10" t="inlineStr">
+        <is>
+          <t>Processed</t>
+        </is>
+      </c>
+      <c r="N96" s="10" t="inlineStr">
+        <is>
+          <t>LCD_KS_data.csv; LCD_ALL_data.csv</t>
+        </is>
+      </c>
+      <c r="O96" s="10" t="inlineStr">
+        <is>
+          <t>MEL data portal (data.mel.cgiar.org)</t>
+        </is>
+      </c>
+      <c r="P96" s="10" t="n"/>
+      <c r="Q96" s="10" t="n"/>
+      <c r="R96" s="11" t="inlineStr">
+        <is>
+          <t>Land cover change statistics and the ecological degradation or improvement they imply, at two scales - the Kef-Siliana region as a whole and the sub-spatial units of the Agroecological Living Lab Landscape in Tunisia. Land cover change was analysed in QGIS 3.28.15 with the Semi-Automatic Classification Plugin; degradation and improvement were assessed following the UNCCD Good Practice Guidance. Delivered as two CSV tables with data dictionaries. Published on ICARDA's MEL data portal; MOSAIC links to it there.</t>
+        </is>
+      </c>
+      <c r="S96" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="T96" s="10" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="U96" s="10" t="inlineStr">
+        <is>
+          <t>Static</t>
+        </is>
+      </c>
+      <c r="V96" s="10" t="inlineStr">
+        <is>
+          <t>https://hdl.handle.net/20.500.11766.1/FK2/U4JHNU</t>
+        </is>
+      </c>
+      <c r="W96" s="10" t="inlineStr">
+        <is>
+          <t>18 KB</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A2:W91"/>
+  <autoFilter ref="A2:W96"/>
   <conditionalFormatting sqref="K3:K300">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
       <formula>"Open"</formula>

--- a/catalog/MFL_Dataset_Registry.xlsx
+++ b/catalog/MFL_Dataset_Registry.xlsx
@@ -4293,14 +4293,22 @@
           <t>Validated</t>
         </is>
       </c>
-      <c r="N32" s="10" t="n"/>
+      <c r="N32" s="10" t="inlineStr">
+        <is>
+          <t>Tunisia_Governorate.shp (complete shapefile set, 8 files)</t>
+        </is>
+      </c>
       <c r="O32" s="10" t="inlineStr">
         <is>
           <t>Drive</t>
         </is>
       </c>
       <c r="P32" s="10" t="n"/>
-      <c r="Q32" s="10" t="n"/>
+      <c r="Q32" s="10" t="inlineStr">
+        <is>
+          <t>MOSAIC/datasets/MFL-2026-030/raw/</t>
+        </is>
+      </c>
       <c r="R32" s="11" t="inlineStr">
         <is>
           <t>Administrative boundaries for Tunisia</t>
@@ -4314,7 +4322,11 @@
           <t>www.geoboundaries.org</t>
         </is>
       </c>
-      <c r="W32" s="10" t="n"/>
+      <c r="W32" s="10" t="inlineStr">
+        <is>
+          <t>571 KB</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="8" t="inlineStr">
@@ -4382,14 +4394,22 @@
           <t>Validated</t>
         </is>
       </c>
-      <c r="N33" s="8" t="n"/>
+      <c r="N33" s="8" t="inlineStr">
+        <is>
+          <t>Tunisia_Sector.shp (complete shapefile set, 8 files)</t>
+        </is>
+      </c>
       <c r="O33" s="8" t="inlineStr">
         <is>
           <t>Drive</t>
         </is>
       </c>
       <c r="P33" s="8" t="n"/>
-      <c r="Q33" s="8" t="n"/>
+      <c r="Q33" s="8" t="inlineStr">
+        <is>
+          <t>MOSAIC/datasets/MFL-2026-031/raw/</t>
+        </is>
+      </c>
       <c r="R33" s="9" t="inlineStr">
         <is>
           <t>Administrative boundaries for Tunisia</t>
@@ -4403,7 +4423,11 @@
           <t>www.geoboundaries.org</t>
         </is>
       </c>
-      <c r="W33" s="8" t="n"/>
+      <c r="W33" s="8" t="inlineStr">
+        <is>
+          <t>692 KB</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="10" t="inlineStr">
@@ -4471,14 +4495,22 @@
           <t>Validated</t>
         </is>
       </c>
-      <c r="N34" s="10" t="n"/>
+      <c r="N34" s="10" t="inlineStr">
+        <is>
+          <t>Tunisia_ALL.shp (complete shapefile set, 8 files)</t>
+        </is>
+      </c>
       <c r="O34" s="10" t="inlineStr">
         <is>
           <t>Drive</t>
         </is>
       </c>
       <c r="P34" s="10" t="n"/>
-      <c r="Q34" s="10" t="n"/>
+      <c r="Q34" s="10" t="inlineStr">
+        <is>
+          <t>MOSAIC/datasets/MFL-2026-032/raw/</t>
+        </is>
+      </c>
       <c r="R34" s="11" t="inlineStr">
         <is>
           <t>Administrative boundaries for Tunisia</t>
@@ -4492,7 +4524,11 @@
           <t>www.geoboundaries.org</t>
         </is>
       </c>
-      <c r="W34" s="10" t="n"/>
+      <c r="W34" s="10" t="inlineStr">
+        <is>
+          <t>723 KB</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="8" t="inlineStr">
@@ -5434,14 +5470,22 @@
           <t>Validated</t>
         </is>
       </c>
-      <c r="N45" s="8" t="n"/>
+      <c r="N45" s="8" t="inlineStr">
+        <is>
+          <t>gadm41_CIV_0.shp; gadm41_CIV_1.shp; gadm41_CIV_2.shp; gadm41_CIV_3.shp; gadm41_CIV_4.shp (five complete shapefile sets, 25 files)</t>
+        </is>
+      </c>
       <c r="O45" s="8" t="inlineStr">
         <is>
           <t>Drive</t>
         </is>
       </c>
       <c r="P45" s="8" t="n"/>
-      <c r="Q45" s="8" t="n"/>
+      <c r="Q45" s="8" t="inlineStr">
+        <is>
+          <t>MOSAIC/datasets/MFL-2026-044/raw/</t>
+        </is>
+      </c>
       <c r="R45" s="9" t="inlineStr">
         <is>
           <t>GADM 4.1 administrative boundaries for Côte d'Ivoire, levels 0 to 4: the country; 12 districts and 2 autonomous districts; 31 regions plus the 2 autonomous districts; 113 departments; and 191 sub-prefectures. Country-wide, not clipped to the N'Zi landscape. Unmodified from GADM; download from gadm.org. GADM's licence does not allow redistribution, so MOSAIC keeps only an internal quality-control copy.</t>
@@ -5463,7 +5507,11 @@
           <t>https://gadm.org/download_country.html</t>
         </is>
       </c>
-      <c r="W45" s="8" t="n"/>
+      <c r="W45" s="8" t="inlineStr">
+        <is>
+          <t>3.5 MB</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="10" t="inlineStr">
@@ -5620,14 +5668,22 @@
           <t>Validated</t>
         </is>
       </c>
-      <c r="N47" s="8" t="n"/>
+      <c r="N47" s="8" t="inlineStr">
+        <is>
+          <t>synoptic_stations_daily.xlsx (one sheet per station - Bouake, Korhogo, Ferkessedougou)</t>
+        </is>
+      </c>
       <c r="O47" s="8" t="inlineStr">
         <is>
           <t>server and drive</t>
         </is>
       </c>
       <c r="P47" s="8" t="n"/>
-      <c r="Q47" s="8" t="n"/>
+      <c r="Q47" s="8" t="inlineStr">
+        <is>
+          <t>MOSAIC/datasets/MFL-2026-046/raw/</t>
+        </is>
+      </c>
       <c r="R47" s="9" t="inlineStr">
         <is>
           <t>Daily weather data for three synoptic stations in and around the N'Zi watershed, served by AfricaRice's ARCWeather portal: Bouaké and Ferkessédougou from 1980 to 2010, Korhogo from 1994 to 2001. Korhogo holds fewer variables, and its dew point is estimated from the minimum temperature. AfricaRice's own M'Bé research-station data from 2014 onward is a separate record, MFL-2026-084.</t>
@@ -5649,7 +5705,11 @@
           <t>https://arcweather.africarice.org/en/downloads</t>
         </is>
       </c>
-      <c r="W47" s="8" t="n"/>
+      <c r="W47" s="8" t="inlineStr">
+        <is>
+          <t>3.5 MB</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="10" t="inlineStr">
@@ -5728,7 +5788,11 @@
         </is>
       </c>
       <c r="P48" s="10" t="n"/>
-      <c r="Q48" s="10" t="n"/>
+      <c r="Q48" s="10" t="inlineStr">
+        <is>
+          <t>MOSAIC/datasets/MFL-2026-048/raw/</t>
+        </is>
+      </c>
       <c r="R48" s="11" t="inlineStr">
         <is>
           <t>DSSAT soil profile file for Côte d'Ivoire (CI.SOL): 3,823 soil profiles on a 5-arc-minute grid covering the whole country, 425 of them inside the N'Zi landscape. It is the unmodified Côte d'Ivoire file of the Global High-Resolution Soil Profile Database for Crop Modeling Applications (IRI, MSU and HarvestChoice/IFPRI, 2015), published on the IFPRI Dataverse.</t>
@@ -5750,7 +5814,11 @@
           <t>https://doi.org/10.7910/DVN/1PEEY0</t>
         </is>
       </c>
-      <c r="W48" s="10" t="n"/>
+      <c r="W48" s="10" t="inlineStr">
+        <is>
+          <t>9.3 MB</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="8" t="inlineStr">
@@ -7118,7 +7186,7 @@
       </c>
       <c r="B63" s="8" t="inlineStr">
         <is>
-          <t>Tree conservation and restoration priority areas</t>
+          <t>Tree conservation and restoration priority areas (Kenya)</t>
         </is>
       </c>
       <c r="C63" s="8" t="inlineStr">
@@ -7176,14 +7244,22 @@
           <t>Validated</t>
         </is>
       </c>
-      <c r="N63" s="8" t="n"/>
+      <c r="N63" s="8" t="inlineStr">
+        <is>
+          <t>ex_situ_conservation.tif; expanding_protection.tif; landscape_restoration.tif; maintaining_protection.tif</t>
+        </is>
+      </c>
       <c r="O63" s="8" t="inlineStr">
         <is>
           <t>Dataverse repository</t>
         </is>
       </c>
       <c r="P63" s="8" t="n"/>
-      <c r="Q63" s="8" t="n"/>
+      <c r="Q63" s="8" t="inlineStr">
+        <is>
+          <t>MOSAIC/datasets/MFL-2026-064/raw/</t>
+        </is>
+      </c>
       <c r="R63" s="9" t="inlineStr">
         <is>
           <t>Conservation for Restoration (C4R) tool KENYA: mapping the vulnerability and priority areas for conservation and restoration of 78 native tree species. Linked to D4R</t>
@@ -7510,7 +7586,7 @@
       </c>
       <c r="B67" s="8" t="inlineStr">
         <is>
-          <t>Tree conservation and restoration priority areas</t>
+          <t>Tree conservation and restoration priority areas (Laos)</t>
         </is>
       </c>
       <c r="C67" s="8" t="inlineStr">
@@ -7564,14 +7640,22 @@
         </is>
       </c>
       <c r="M67" s="8" t="n"/>
-      <c r="N67" s="8" t="n"/>
+      <c r="N67" s="8" t="inlineStr">
+        <is>
+          <t>ex_situ_conservation.tif; expanding_protection.tif; landscape_restoration.tif; maintaining_protection.tif</t>
+        </is>
+      </c>
       <c r="O67" s="8" t="inlineStr">
         <is>
           <t>One drive</t>
         </is>
       </c>
       <c r="P67" s="8" t="n"/>
-      <c r="Q67" s="8" t="n"/>
+      <c r="Q67" s="8" t="inlineStr">
+        <is>
+          <t>MOSAIC/datasets/MFL-2026-068/raw/</t>
+        </is>
+      </c>
       <c r="R67" s="9" t="inlineStr">
         <is>
           <t>Conservation for Restoration (C4R) tool LAOS: mapping the vulnerability and priority areas for conservation and restoration of 79 native tree species. Linked to D4R</t>
@@ -7603,7 +7687,7 @@
       </c>
       <c r="B68" s="10" t="inlineStr">
         <is>
-          <t>Tree conservation and restoration priority areas</t>
+          <t>Tree conservation and restoration priority areas (Vietnam)</t>
         </is>
       </c>
       <c r="C68" s="10" t="inlineStr">
@@ -7657,14 +7741,22 @@
         </is>
       </c>
       <c r="M68" s="10" t="n"/>
-      <c r="N68" s="10" t="n"/>
+      <c r="N68" s="10" t="inlineStr">
+        <is>
+          <t>ex_situ_conservation.tif; expanding_protection.tif; landscape_restoration.tif; maintaining_protection.tif</t>
+        </is>
+      </c>
       <c r="O68" s="10" t="inlineStr">
         <is>
           <t>One drive</t>
         </is>
       </c>
       <c r="P68" s="10" t="n"/>
-      <c r="Q68" s="10" t="n"/>
+      <c r="Q68" s="10" t="inlineStr">
+        <is>
+          <t>MOSAIC/datasets/MFL-2026-069/raw/</t>
+        </is>
+      </c>
       <c r="R68" s="11" t="inlineStr">
         <is>
           <t>Conservation for Restoration (C4R) tool VIETNAM: mapping the vulnerability and priority areas for conservation and restoration of 66 native tree species. Linked to D4R</t>
@@ -7952,14 +8044,22 @@
           <t>Processed</t>
         </is>
       </c>
-      <c r="N71" s="8" t="n"/>
+      <c r="N71" s="8" t="inlineStr">
+        <is>
+          <t>Ucayali_Provinces_and_Districts.shp (complete shapefile set, 8 files)</t>
+        </is>
+      </c>
       <c r="O71" s="8" t="inlineStr">
         <is>
           <t>One Drive</t>
         </is>
       </c>
       <c r="P71" s="8" t="n"/>
-      <c r="Q71" s="8" t="n"/>
+      <c r="Q71" s="8" t="inlineStr">
+        <is>
+          <t>MOSAIC/datasets/MFL-2026-072/raw/</t>
+        </is>
+      </c>
       <c r="R71" s="9" t="inlineStr">
         <is>
           <t>Administrative boundaries for Ucayali, Peru</t>
@@ -7985,7 +8085,11 @@
           <t>https://www.datosabiertos.gob.pe/dataset/limites-departamentales</t>
         </is>
       </c>
-      <c r="W71" s="8" t="n"/>
+      <c r="W71" s="8" t="inlineStr">
+        <is>
+          <t>1.0 MB</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="10" t="inlineStr">
@@ -8053,14 +8157,22 @@
           <t>Processed</t>
         </is>
       </c>
-      <c r="N72" s="10" t="n"/>
+      <c r="N72" s="10" t="inlineStr">
+        <is>
+          <t>Ucayali_National_Protected_Natural_Areas.shp (complete shapefile set, 8 files)</t>
+        </is>
+      </c>
       <c r="O72" s="10" t="inlineStr">
         <is>
           <t>One Drive</t>
         </is>
       </c>
       <c r="P72" s="10" t="n"/>
-      <c r="Q72" s="10" t="n"/>
+      <c r="Q72" s="10" t="inlineStr">
+        <is>
+          <t>MOSAIC/datasets/MFL-2026-073/raw/</t>
+        </is>
+      </c>
       <c r="R72" s="11" t="inlineStr">
         <is>
           <t>National Protected Natural Areas clipped to  Ucayali</t>
@@ -8086,7 +8198,11 @@
           <t>https://geo.sernanp.gob.pe/visorsernanp/</t>
         </is>
       </c>
-      <c r="W72" s="10" t="n"/>
+      <c r="W72" s="10" t="inlineStr">
+        <is>
+          <t>658 KB</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="8" t="inlineStr">
@@ -8154,14 +8270,22 @@
           <t>Processed</t>
         </is>
       </c>
-      <c r="N73" s="8" t="n"/>
+      <c r="N73" s="8" t="inlineStr">
+        <is>
+          <t>Ucayali_Regional_Conservation_Areas.shp (complete shapefile set, 8 files)</t>
+        </is>
+      </c>
       <c r="O73" s="8" t="inlineStr">
         <is>
           <t>One Drive</t>
         </is>
       </c>
       <c r="P73" s="8" t="n"/>
-      <c r="Q73" s="8" t="n"/>
+      <c r="Q73" s="8" t="inlineStr">
+        <is>
+          <t>MOSAIC/datasets/MFL-2026-074/raw/</t>
+        </is>
+      </c>
       <c r="R73" s="9" t="inlineStr">
         <is>
           <t>Regional Conservation Areas clipped to Ucayali</t>
@@ -8187,7 +8311,11 @@
           <t>https://geo.sernanp.gob.pe/visorsernanp/</t>
         </is>
       </c>
-      <c r="W73" s="8" t="n"/>
+      <c r="W73" s="8" t="inlineStr">
+        <is>
+          <t>125 KB</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="10" t="inlineStr">
@@ -8255,14 +8383,22 @@
           <t>Processed</t>
         </is>
       </c>
-      <c r="N74" s="10" t="n"/>
+      <c r="N74" s="10" t="inlineStr">
+        <is>
+          <t>Ucayali_Indigenous_Territories.shp (complete shapefile set, 8 files)</t>
+        </is>
+      </c>
       <c r="O74" s="10" t="inlineStr">
         <is>
           <t>One Drive</t>
         </is>
       </c>
       <c r="P74" s="10" t="n"/>
-      <c r="Q74" s="10" t="n"/>
+      <c r="Q74" s="10" t="inlineStr">
+        <is>
+          <t>MOSAIC/datasets/MFL-2026-075/raw/</t>
+        </is>
+      </c>
       <c r="R74" s="11" t="inlineStr">
         <is>
           <t>Indigenous Territories clipped to Ucayali</t>
@@ -8288,7 +8424,11 @@
           <t>https://www.raisg.org/es/mapas/</t>
         </is>
       </c>
-      <c r="W74" s="10" t="n"/>
+      <c r="W74" s="10" t="inlineStr">
+        <is>
+          <t>5.3 MB</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="8" t="inlineStr">
@@ -8352,14 +8492,22 @@
           <t>Processed</t>
         </is>
       </c>
-      <c r="N75" s="8" t="n"/>
+      <c r="N75" s="8" t="inlineStr">
+        <is>
+          <t>Ucayali_Ecosystems_map.shp (complete shapefile set, 8 files)</t>
+        </is>
+      </c>
       <c r="O75" s="8" t="inlineStr">
         <is>
           <t>One Drive</t>
         </is>
       </c>
       <c r="P75" s="8" t="n"/>
-      <c r="Q75" s="8" t="n"/>
+      <c r="Q75" s="8" t="inlineStr">
+        <is>
+          <t>MOSAIC/datasets/MFL-2026-076/raw/</t>
+        </is>
+      </c>
       <c r="R75" s="9" t="inlineStr">
         <is>
           <t>Spatial distribution and classification of ecosystem within Ucayali department, derived from Peru´s National Ecosystem Map 2018, and aggregated by adminstrative provinces and districts level</t>
@@ -8385,7 +8533,11 @@
           <t>https://geoservidor.minam.gob.pe/recursos/intercambio-de-datos/</t>
         </is>
       </c>
-      <c r="W75" s="8" t="n"/>
+      <c r="W75" s="8" t="inlineStr">
+        <is>
+          <t>109.7 MB</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="10" t="inlineStr">
@@ -8449,14 +8601,22 @@
           <t>Processed</t>
         </is>
       </c>
-      <c r="N76" s="10" t="n"/>
+      <c r="N76" s="10" t="inlineStr">
+        <is>
+          <t>Ucayali_Human_Footprint_map.shp (complete shapefile set, 8 files)</t>
+        </is>
+      </c>
       <c r="O76" s="10" t="inlineStr">
         <is>
           <t>One Drive</t>
         </is>
       </c>
       <c r="P76" s="10" t="n"/>
-      <c r="Q76" s="10" t="n"/>
+      <c r="Q76" s="10" t="inlineStr">
+        <is>
+          <t>MOSAIC/datasets/MFL-2026-077/raw/</t>
+        </is>
+      </c>
       <c r="R76" s="11" t="inlineStr">
         <is>
           <t>Human footprint areas &gt;4 in the Ucayali department for 2012, 2015, 2018, and 2021, derived from Peru´s Human Footprint map. The original raster data was converted to vector polygons and aggregated by adminstrative provinces and districts level</t>
@@ -8482,7 +8642,11 @@
           <t>https://geoservidor.minam.gob.pe/recursos/intercambio-de-datos/</t>
         </is>
       </c>
-      <c r="W76" s="10" t="n"/>
+      <c r="W76" s="10" t="inlineStr">
+        <is>
+          <t>125.6 MB</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="8" t="inlineStr">
@@ -8546,14 +8710,22 @@
           <t>Processed</t>
         </is>
       </c>
-      <c r="N77" s="8" t="n"/>
+      <c r="N77" s="8" t="inlineStr">
+        <is>
+          <t>Ucayali_Physical_Vulnerability_map.shp (complete shapefile set, 8 files)</t>
+        </is>
+      </c>
       <c r="O77" s="8" t="inlineStr">
         <is>
           <t>One Drive</t>
         </is>
       </c>
       <c r="P77" s="8" t="n"/>
-      <c r="Q77" s="8" t="n"/>
+      <c r="Q77" s="8" t="inlineStr">
+        <is>
+          <t>MOSAIC/datasets/MFL-2026-078/raw/</t>
+        </is>
+      </c>
       <c r="R77" s="9" t="inlineStr">
         <is>
           <t>Spatial distribution of physical vulnerability levels within the Ucayali department, derived from Peru’s National Physical Vulnerability map 2011, and aggregated by administrative provinces and districts level</t>
@@ -8579,7 +8751,11 @@
           <t>https://geoservidor.minam.gob.pe/recursos/intercambio-de-datos/</t>
         </is>
       </c>
-      <c r="W77" s="8" t="n"/>
+      <c r="W77" s="8" t="inlineStr">
+        <is>
+          <t>7.8 MB</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="10" t="inlineStr">
@@ -8643,14 +8819,22 @@
           <t>Processed</t>
         </is>
       </c>
-      <c r="N78" s="10" t="n"/>
+      <c r="N78" s="10" t="inlineStr">
+        <is>
+          <t>Ucayali_Forest_NonForest2000_ForestLoss2001_2024.shp (complete shapefile set, 8 files)</t>
+        </is>
+      </c>
       <c r="O78" s="10" t="inlineStr">
         <is>
           <t>One Drive</t>
         </is>
       </c>
       <c r="P78" s="10" t="n"/>
-      <c r="Q78" s="10" t="n"/>
+      <c r="Q78" s="10" t="inlineStr">
+        <is>
+          <t>MOSAIC/datasets/MFL-2026-079/raw/</t>
+        </is>
+      </c>
       <c r="R78" s="11" t="inlineStr">
         <is>
           <t>Forest/non-forest baseline for 2000 and annual forest loss from 2001 to 2024 in Ucayali, derived from MINAM’s GEOBOSQUES forest monitoring dataset and spatially aggregated by provinces and districts.</t>
@@ -8676,7 +8860,11 @@
           <t>https://geobosques.minam.gob.pe/geobosque/view/descargas.php?122345gxxe345w34gg#download</t>
         </is>
       </c>
-      <c r="W78" s="10" t="n"/>
+      <c r="W78" s="10" t="inlineStr">
+        <is>
+          <t>175.2 MB</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="8" t="inlineStr">
@@ -8740,14 +8928,22 @@
           <t>Processed</t>
         </is>
       </c>
-      <c r="N79" s="8" t="n"/>
+      <c r="N79" s="8" t="inlineStr">
+        <is>
+          <t>Ucayali_Annual_Deforestation_2001_2024.shp (complete shapefile set, 8 files)</t>
+        </is>
+      </c>
       <c r="O79" s="8" t="inlineStr">
         <is>
           <t>One Drive</t>
         </is>
       </c>
       <c r="P79" s="8" t="n"/>
-      <c r="Q79" s="8" t="n"/>
+      <c r="Q79" s="8" t="inlineStr">
+        <is>
+          <t>MOSAIC/datasets/MFL-2026-080/raw/</t>
+        </is>
+      </c>
       <c r="R79" s="9" t="inlineStr">
         <is>
           <t>Annual forest loss from 2001-2024 in Ucayali, derived from MINAM’s GEOBOSQUES forest monitoring dataset and spatially aggregated by provinces and districts. The 2025 update published at source is not yet included in this layer.</t>
@@ -8773,7 +8969,11 @@
           <t>https://geobosques.minam.gob.pe/geobosque/view/descargas.php?122345gxxe345w34gg#download</t>
         </is>
       </c>
-      <c r="W79" s="8" t="n"/>
+      <c r="W79" s="8" t="inlineStr">
+        <is>
+          <t>143.3 MB</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="10" t="inlineStr">
@@ -8841,14 +9041,22 @@
           <t>Processed</t>
         </is>
       </c>
-      <c r="N80" s="10" t="n"/>
+      <c r="N80" s="10" t="inlineStr">
+        <is>
+          <t>Ucayali_Land_cover_Land_use.shp (complete shapefile set, 8 files)</t>
+        </is>
+      </c>
       <c r="O80" s="10" t="inlineStr">
         <is>
           <t>One Drive</t>
         </is>
       </c>
       <c r="P80" s="10" t="n"/>
-      <c r="Q80" s="10" t="n"/>
+      <c r="Q80" s="10" t="inlineStr">
+        <is>
+          <t>MOSAIC/datasets/MFL-2026-081/raw/</t>
+        </is>
+      </c>
       <c r="R80" s="11" t="inlineStr">
         <is>
           <t>Land cover and land-use classification within the Ucayali department for 2000, 2005, 2010, 2015, 2020 and 2024, derived from Mapbiomas Peru Collection 4. The original raster data was converted to vector polygons and aggregated by administrative provinces and districts level</t>
@@ -8874,7 +9082,11 @@
           <t>https://peru.mapbiomas.org/iniciativas-y-productos/cobertura-y-uso-del-suelo/cobertura/</t>
         </is>
       </c>
-      <c r="W80" s="10" t="n"/>
+      <c r="W80" s="10" t="inlineStr">
+        <is>
+          <t>520.2 MB</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="8" t="inlineStr">
@@ -8942,14 +9154,22 @@
           <t>Processed</t>
         </is>
       </c>
-      <c r="N81" s="8" t="n"/>
+      <c r="N81" s="8" t="inlineStr">
+        <is>
+          <t>Ucayali_Cumulative_Burned_2013_2024.shp (complete shapefile set, 8 files)</t>
+        </is>
+      </c>
       <c r="O81" s="8" t="inlineStr">
         <is>
           <t>One Drive</t>
         </is>
       </c>
       <c r="P81" s="8" t="n"/>
-      <c r="Q81" s="8" t="n"/>
+      <c r="Q81" s="8" t="inlineStr">
+        <is>
+          <t>MOSAIC/datasets/MFL-2026-082/raw/</t>
+        </is>
+      </c>
       <c r="R81" s="9" t="inlineStr">
         <is>
           <t>Cumulative Burned Area during 2013–2024 within the Ucayali department, derived from Mapbiomas Peru Collection 1. The original raster data was converted to vector polygons and aggregated by administrative provinces and districts level</t>
@@ -8975,7 +9195,11 @@
           <t>https://peru.mapbiomas.org/iniciativas-y-productos/fuego/mapeo-anual/</t>
         </is>
       </c>
-      <c r="W81" s="8" t="n"/>
+      <c r="W81" s="8" t="inlineStr">
+        <is>
+          <t>13.8 MB</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" s="10" t="inlineStr">

--- a/catalog/MFL_Dataset_Registry.xlsx
+++ b/catalog/MFL_Dataset_Registry.xlsx
@@ -20,7 +20,7 @@
     <definedName name="MOSAIC_Access">Reference!$I$2:$I$4</definedName>
     <definedName name="MOSAIC_Migration">Reference!$O$2:$O$3</definedName>
     <definedName name="MOSAIC_UpdFreq">Reference!$Q$2:$Q$7</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">' Registry'!$A$2:$W$96</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">' Registry'!$A$2:$W$104</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -1221,7 +1221,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W96"/>
+  <dimension ref="A1:W104"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -10744,8 +10744,880 @@
         </is>
       </c>
     </row>
+    <row r="97">
+      <c r="A97" s="8" t="inlineStr">
+        <is>
+          <t>MFL-2026-098</t>
+        </is>
+      </c>
+      <c r="B97" s="8" t="inlineStr">
+        <is>
+          <t>N'Zi Watershed living landscape boundary</t>
+        </is>
+      </c>
+      <c r="C97" s="8" t="inlineStr">
+        <is>
+          <t>Côte d'Ivoire</t>
+        </is>
+      </c>
+      <c r="D97" s="8" t="inlineStr">
+        <is>
+          <t>Boundaries / admin units</t>
+        </is>
+      </c>
+      <c r="E97" s="8" t="inlineStr">
+        <is>
+          <t>CIV-NZ — N'Zi Watershed</t>
+        </is>
+      </c>
+      <c r="F97" s="8" t="inlineStr">
+        <is>
+          <t>Vector</t>
+        </is>
+      </c>
+      <c r="G97" s="8" t="inlineStr">
+        <is>
+          <t>Landscape boundary</t>
+        </is>
+      </c>
+      <c r="H97" s="8" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="I97" s="8" t="inlineStr">
+        <is>
+          <t>Alliance Bioversity-CIAT (MOSAIC)</t>
+        </is>
+      </c>
+      <c r="J97" s="8" t="inlineStr">
+        <is>
+          <t>Lizeth Llanos (l.llanos@cgiar.org)</t>
+        </is>
+      </c>
+      <c r="K97" s="8" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="L97" s="8" t="inlineStr">
+        <is>
+          <t>Source terms (https://data.hydrosheds.org/file/technical-documentation/HydroSHEDS_TechDoc_v1_4.pdf)</t>
+        </is>
+      </c>
+      <c r="M97" s="8" t="inlineStr">
+        <is>
+          <t>Processed</t>
+        </is>
+      </c>
+      <c r="N97" s="8" t="inlineStr">
+        <is>
+          <t>CIV-NZ_NZi_Watershed_boundary_2026-10-14.zip</t>
+        </is>
+      </c>
+      <c r="O97" s="8" t="inlineStr">
+        <is>
+          <t>GitHub release boundaries-2026-10-14 (MOSAIC-mfl/catalog)</t>
+        </is>
+      </c>
+      <c r="P97" s="8" t="n"/>
+      <c r="Q97" s="8" t="n"/>
+      <c r="R97" s="9" t="inlineStr">
+        <is>
+          <t>Canonical MOSAIC delineation of the N'Zi Watershed living landscape (CIV-NZ), used to define the landscape across the catalogue. Source: HydroBASINS v1c, level 6, basin HYBAS_ID 1060982320 (PFAF_ID 145402), unmodified. HydroSHEDS version 1, World Wildlife Fund (WWF). Full-detail Shapefile and GeoPackage in the dated release boundaries-2026-10-14 of MOSAIC-mfl/catalog; a simplified outline is attached to the landscape's STAC collection.</t>
+        </is>
+      </c>
+      <c r="S97" s="8" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="T97" s="8" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="U97" s="8" t="inlineStr">
+        <is>
+          <t>Static</t>
+        </is>
+      </c>
+      <c r="V97" s="8" t="inlineStr">
+        <is>
+          <t>https://github.com/MOSAIC-mfl/catalog/releases/download/boundaries-2026-10-14/CIV-NZ_NZi_Watershed_boundary_2026-10-14.zip</t>
+        </is>
+      </c>
+      <c r="W97" s="8" t="inlineStr">
+        <is>
+          <t>19 KB</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="10" t="inlineStr">
+        <is>
+          <t>MFL-2026-099</t>
+        </is>
+      </c>
+      <c r="B98" s="10" t="inlineStr">
+        <is>
+          <t>Cumbal (Nariño) living landscape boundary</t>
+        </is>
+      </c>
+      <c r="C98" s="10" t="inlineStr">
+        <is>
+          <t>Colombia</t>
+        </is>
+      </c>
+      <c r="D98" s="10" t="inlineStr">
+        <is>
+          <t>Boundaries / admin units</t>
+        </is>
+      </c>
+      <c r="E98" s="10" t="inlineStr">
+        <is>
+          <t>COL-CUM — Cumbal (Nariño)</t>
+        </is>
+      </c>
+      <c r="F98" s="10" t="inlineStr">
+        <is>
+          <t>Vector</t>
+        </is>
+      </c>
+      <c r="G98" s="10" t="inlineStr">
+        <is>
+          <t>Landscape boundary</t>
+        </is>
+      </c>
+      <c r="H98" s="10" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="I98" s="10" t="inlineStr">
+        <is>
+          <t>Alliance Bioversity-CIAT (MOSAIC)</t>
+        </is>
+      </c>
+      <c r="J98" s="10" t="inlineStr">
+        <is>
+          <t>Lizeth Llanos (l.llanos@cgiar.org)</t>
+        </is>
+      </c>
+      <c r="K98" s="10" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="L98" s="10" t="inlineStr">
+        <is>
+          <t>No licence stated by the source</t>
+        </is>
+      </c>
+      <c r="M98" s="10" t="inlineStr">
+        <is>
+          <t>Processed</t>
+        </is>
+      </c>
+      <c r="N98" s="10" t="inlineStr">
+        <is>
+          <t>COL-CUM_Cumbal_Narino_boundary_2026-10-14.zip</t>
+        </is>
+      </c>
+      <c r="O98" s="10" t="inlineStr">
+        <is>
+          <t>GitHub release boundaries-2026-10-14 (MOSAIC-mfl/catalog)</t>
+        </is>
+      </c>
+      <c r="P98" s="10" t="n"/>
+      <c r="Q98" s="10" t="n"/>
+      <c r="R98" s="11" t="inlineStr">
+        <is>
+          <t>Canonical MOSAIC delineation of the Cumbal (Nariño) living landscape (COL-CUM), used to define the landscape across the catalogue. Source: Nine veredas of the Cumbal indigenous reserve area (Tasmag, Quilismal, Boyera, Cuaical, Cuaspud Grande, Llano de Piedras, Cuetial, Guan, San Martin-Miraflores), layer 'Cumbal_veredas_wgs84' compiled by Javier Ochoa (CIP). Original source to be confirmed. Full-detail Shapefile and GeoPackage in the dated release boundaries-2026-10-14 of MOSAIC-mfl/catalog; a simplified outline is attached to the landscape's STAC collection.</t>
+        </is>
+      </c>
+      <c r="S98" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="T98" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="U98" s="10" t="inlineStr">
+        <is>
+          <t>Static</t>
+        </is>
+      </c>
+      <c r="V98" s="10" t="inlineStr">
+        <is>
+          <t>https://github.com/MOSAIC-mfl/catalog/releases/download/boundaries-2026-10-14/COL-CUM_Cumbal_Narino_boundary_2026-10-14.zip</t>
+        </is>
+      </c>
+      <c r="W98" s="10" t="inlineStr">
+        <is>
+          <t>12 KB</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="8" t="inlineStr">
+        <is>
+          <t>MFL-2026-100</t>
+        </is>
+      </c>
+      <c r="B99" s="8" t="inlineStr">
+        <is>
+          <t>Omo-Gibe Basin living landscape boundary</t>
+        </is>
+      </c>
+      <c r="C99" s="8" t="inlineStr">
+        <is>
+          <t>Ethiopia</t>
+        </is>
+      </c>
+      <c r="D99" s="8" t="inlineStr">
+        <is>
+          <t>Boundaries / admin units</t>
+        </is>
+      </c>
+      <c r="E99" s="8" t="inlineStr">
+        <is>
+          <t>ETH-OG — Omo-Gibe Basin</t>
+        </is>
+      </c>
+      <c r="F99" s="8" t="inlineStr">
+        <is>
+          <t>Vector</t>
+        </is>
+      </c>
+      <c r="G99" s="8" t="inlineStr">
+        <is>
+          <t>Landscape boundary</t>
+        </is>
+      </c>
+      <c r="H99" s="8" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="I99" s="8" t="inlineStr">
+        <is>
+          <t>Alliance Bioversity-CIAT (MOSAIC)</t>
+        </is>
+      </c>
+      <c r="J99" s="8" t="inlineStr">
+        <is>
+          <t>Lizeth Llanos (l.llanos@cgiar.org)</t>
+        </is>
+      </c>
+      <c r="K99" s="8" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="L99" s="8" t="inlineStr">
+        <is>
+          <t>CC BY 4.0</t>
+        </is>
+      </c>
+      <c r="M99" s="8" t="inlineStr">
+        <is>
+          <t>Processed</t>
+        </is>
+      </c>
+      <c r="N99" s="8" t="inlineStr">
+        <is>
+          <t>ETH-OG_Omo-Gibe_Basin_boundary_2026-10-14.zip</t>
+        </is>
+      </c>
+      <c r="O99" s="8" t="inlineStr">
+        <is>
+          <t>GitHub release boundaries-2026-10-14 (MOSAIC-mfl/catalog)</t>
+        </is>
+      </c>
+      <c r="P99" s="8" t="n"/>
+      <c r="Q99" s="8" t="n"/>
+      <c r="R99" s="9" t="inlineStr">
+        <is>
+          <t>Canonical MOSAIC delineation of the Omo-Gibe Basin living landscape (ETH-OG), used to define the landscape across the catalogue. Source: Ethiopia River Basins (eth_basins), World Bank Group, World Bank Data Catalog dataset 0040202: Omo basin polygon (79,549 km2). Full-detail Shapefile and GeoPackage in the dated release boundaries-2026-10-14 of MOSAIC-mfl/catalog; a simplified outline is attached to the landscape's STAC collection.</t>
+        </is>
+      </c>
+      <c r="S99" s="8" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="T99" s="8" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="U99" s="8" t="inlineStr">
+        <is>
+          <t>Static</t>
+        </is>
+      </c>
+      <c r="V99" s="8" t="inlineStr">
+        <is>
+          <t>https://github.com/MOSAIC-mfl/catalog/releases/download/boundaries-2026-10-14/ETH-OG_Omo-Gibe_Basin_boundary_2026-10-14.zip</t>
+        </is>
+      </c>
+      <c r="W99" s="8" t="inlineStr">
+        <is>
+          <t>50 KB</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="10" t="inlineStr">
+        <is>
+          <t>MFL-2026-101</t>
+        </is>
+      </c>
+      <c r="B100" s="10" t="inlineStr">
+        <is>
+          <t>LEILA (Southern Kenya Rangelands) living landscape boundary</t>
+        </is>
+      </c>
+      <c r="C100" s="10" t="inlineStr">
+        <is>
+          <t>Kenya</t>
+        </is>
+      </c>
+      <c r="D100" s="10" t="inlineStr">
+        <is>
+          <t>Boundaries / admin units</t>
+        </is>
+      </c>
+      <c r="E100" s="10" t="inlineStr">
+        <is>
+          <t>KEN-LEI — LEILA (Southern Kenya Rangelands)</t>
+        </is>
+      </c>
+      <c r="F100" s="10" t="inlineStr">
+        <is>
+          <t>Vector</t>
+        </is>
+      </c>
+      <c r="G100" s="10" t="inlineStr">
+        <is>
+          <t>Landscape boundary</t>
+        </is>
+      </c>
+      <c r="H100" s="10" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="I100" s="10" t="inlineStr">
+        <is>
+          <t>Alliance Bioversity-CIAT (MOSAIC)</t>
+        </is>
+      </c>
+      <c r="J100" s="10" t="inlineStr">
+        <is>
+          <t>Lizeth Llanos (l.llanos@cgiar.org)</t>
+        </is>
+      </c>
+      <c r="K100" s="10" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="L100" s="10" t="inlineStr">
+        <is>
+          <t>Source terms (https://gadm.org/license.html)</t>
+        </is>
+      </c>
+      <c r="M100" s="10" t="inlineStr">
+        <is>
+          <t>Processed</t>
+        </is>
+      </c>
+      <c r="N100" s="10" t="inlineStr">
+        <is>
+          <t>KEN-LEI_LEILA_Southern_Kenya_Rangelands_boundary_2026-10-14.zip</t>
+        </is>
+      </c>
+      <c r="O100" s="10" t="inlineStr">
+        <is>
+          <t>GitHub release boundaries-2026-10-14 (MOSAIC-mfl/catalog)</t>
+        </is>
+      </c>
+      <c r="P100" s="10" t="n"/>
+      <c r="Q100" s="10" t="n"/>
+      <c r="R100" s="11" t="inlineStr">
+        <is>
+          <t>Canonical MOSAIC delineation of the LEILA (Southern Kenya Rangelands) living landscape (KEN-LEI), used to define the landscape across the catalogue. Source: GADM 4.1, level 1: counties Kajiado (KEN.10_1), Kiambu (KEN.13_1), Machakos (KEN.22_1) and Makueni (KEN.23_1), unmodified. Full-detail Shapefile and GeoPackage in the dated release boundaries-2026-10-14 of MOSAIC-mfl/catalog; a simplified outline is attached to the landscape's STAC collection.</t>
+        </is>
+      </c>
+      <c r="S100" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="T100" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="U100" s="10" t="inlineStr">
+        <is>
+          <t>Static</t>
+        </is>
+      </c>
+      <c r="V100" s="10" t="inlineStr">
+        <is>
+          <t>https://github.com/MOSAIC-mfl/catalog/releases/download/boundaries-2026-10-14/KEN-LEI_LEILA_Southern_Kenya_Rangelands_boundary_2026-10-14.zip</t>
+        </is>
+      </c>
+      <c r="W100" s="10" t="inlineStr">
+        <is>
+          <t>315 KB</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="8" t="inlineStr">
+        <is>
+          <t>MFL-2026-102</t>
+        </is>
+      </c>
+      <c r="B101" s="8" t="inlineStr">
+        <is>
+          <t>Lake Victoria Basin (Kenya) living landscape boundary</t>
+        </is>
+      </c>
+      <c r="C101" s="8" t="inlineStr">
+        <is>
+          <t>Kenya</t>
+        </is>
+      </c>
+      <c r="D101" s="8" t="inlineStr">
+        <is>
+          <t>Boundaries / admin units</t>
+        </is>
+      </c>
+      <c r="E101" s="8" t="inlineStr">
+        <is>
+          <t>KEN-LVB — Lake Victoria Basin (Kenya)</t>
+        </is>
+      </c>
+      <c r="F101" s="8" t="inlineStr">
+        <is>
+          <t>Vector</t>
+        </is>
+      </c>
+      <c r="G101" s="8" t="inlineStr">
+        <is>
+          <t>Landscape boundary</t>
+        </is>
+      </c>
+      <c r="H101" s="8" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="I101" s="8" t="inlineStr">
+        <is>
+          <t>Alliance Bioversity-CIAT (MOSAIC)</t>
+        </is>
+      </c>
+      <c r="J101" s="8" t="inlineStr">
+        <is>
+          <t>Lizeth Llanos (l.llanos@cgiar.org)</t>
+        </is>
+      </c>
+      <c r="K101" s="8" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="L101" s="8" t="inlineStr">
+        <is>
+          <t>Source terms (https://gadm.org/license.html)</t>
+        </is>
+      </c>
+      <c r="M101" s="8" t="inlineStr">
+        <is>
+          <t>Processed</t>
+        </is>
+      </c>
+      <c r="N101" s="8" t="inlineStr">
+        <is>
+          <t>KEN-LVB_Lake_Victoria_Basin_Kenya_boundary_2026-10-14.zip</t>
+        </is>
+      </c>
+      <c r="O101" s="8" t="inlineStr">
+        <is>
+          <t>GitHub release boundaries-2026-10-14 (MOSAIC-mfl/catalog)</t>
+        </is>
+      </c>
+      <c r="P101" s="8" t="n"/>
+      <c r="Q101" s="8" t="n"/>
+      <c r="R101" s="9" t="inlineStr">
+        <is>
+          <t>Canonical MOSAIC delineation of the Lake Victoria Basin (Kenya) living landscape (KEN-LVB), used to define the landscape across the catalogue. Source: GADM 4.1, level 1: counties Kakamega (KEN.11_1), Kisumu (KEN.17_1), Siaya (KEN.38_1) and Vihiga (KEN.45_1), unmodified. Full-detail Shapefile and GeoPackage in the dated release boundaries-2026-10-14 of MOSAIC-mfl/catalog; a simplified outline is attached to the landscape's STAC collection.</t>
+        </is>
+      </c>
+      <c r="S101" s="8" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="T101" s="8" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="U101" s="8" t="inlineStr">
+        <is>
+          <t>Static</t>
+        </is>
+      </c>
+      <c r="V101" s="8" t="inlineStr">
+        <is>
+          <t>https://github.com/MOSAIC-mfl/catalog/releases/download/boundaries-2026-10-14/KEN-LVB_Lake_Victoria_Basin_Kenya_boundary_2026-10-14.zip</t>
+        </is>
+      </c>
+      <c r="W101" s="8" t="inlineStr">
+        <is>
+          <t>117 KB</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="10" t="inlineStr">
+        <is>
+          <t>MFL-2026-103</t>
+        </is>
+      </c>
+      <c r="B102" s="10" t="inlineStr">
+        <is>
+          <t>Pucallpa – Ucayali living landscape boundary</t>
+        </is>
+      </c>
+      <c r="C102" s="10" t="inlineStr">
+        <is>
+          <t>Peru</t>
+        </is>
+      </c>
+      <c r="D102" s="10" t="inlineStr">
+        <is>
+          <t>Boundaries / admin units</t>
+        </is>
+      </c>
+      <c r="E102" s="10" t="inlineStr">
+        <is>
+          <t>PER-PCL — Pucallpa – Ucayali</t>
+        </is>
+      </c>
+      <c r="F102" s="10" t="inlineStr">
+        <is>
+          <t>Vector</t>
+        </is>
+      </c>
+      <c r="G102" s="10" t="inlineStr">
+        <is>
+          <t>Landscape boundary</t>
+        </is>
+      </c>
+      <c r="H102" s="10" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="I102" s="10" t="inlineStr">
+        <is>
+          <t>Alliance Bioversity-CIAT (MOSAIC)</t>
+        </is>
+      </c>
+      <c r="J102" s="10" t="inlineStr">
+        <is>
+          <t>Lizeth Llanos (l.llanos@cgiar.org)</t>
+        </is>
+      </c>
+      <c r="K102" s="10" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="L102" s="10" t="inlineStr">
+        <is>
+          <t>No licence stated by the source</t>
+        </is>
+      </c>
+      <c r="M102" s="10" t="inlineStr">
+        <is>
+          <t>Processed</t>
+        </is>
+      </c>
+      <c r="N102" s="10" t="inlineStr">
+        <is>
+          <t>PER-PCL_Pucallpa_Ucayali_boundary_2026-10-14.zip</t>
+        </is>
+      </c>
+      <c r="O102" s="10" t="inlineStr">
+        <is>
+          <t>GitHub release boundaries-2026-10-14 (MOSAIC-mfl/catalog)</t>
+        </is>
+      </c>
+      <c r="P102" s="10" t="n"/>
+      <c r="Q102" s="10" t="n"/>
+      <c r="R102" s="11" t="inlineStr">
+        <is>
+          <t>Canonical MOSAIC delineation of the Pucallpa – Ucayali living landscape (PER-PCL), used to define the landscape across the catalogue. Source: INEI referential census district limits (cartography of the V Censo Nacional Economico 2022; 'Distrital' layer, ide.inei.gob.pe): 11 whole districts of Coronel Portillo and Padre Abad provinces (Ucayali) and a clipped part of Calleria. Full-detail Shapefile and GeoPackage in the dated release boundaries-2026-10-14 of MOSAIC-mfl/catalog; a simplified outline is attached to the landscape's STAC collection.</t>
+        </is>
+      </c>
+      <c r="S102" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="T102" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="U102" s="10" t="inlineStr">
+        <is>
+          <t>Static</t>
+        </is>
+      </c>
+      <c r="V102" s="10" t="inlineStr">
+        <is>
+          <t>https://github.com/MOSAIC-mfl/catalog/releases/download/boundaries-2026-10-14/PER-PCL_Pucallpa_Ucayali_boundary_2026-10-14.zip</t>
+        </is>
+      </c>
+      <c r="W102" s="10" t="inlineStr">
+        <is>
+          <t>82 KB</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="8" t="inlineStr">
+        <is>
+          <t>MFL-2026-104</t>
+        </is>
+      </c>
+      <c r="B103" s="8" t="inlineStr">
+        <is>
+          <t>Fatick Department living landscape boundary</t>
+        </is>
+      </c>
+      <c r="C103" s="8" t="inlineStr">
+        <is>
+          <t>Senegal</t>
+        </is>
+      </c>
+      <c r="D103" s="8" t="inlineStr">
+        <is>
+          <t>Boundaries / admin units</t>
+        </is>
+      </c>
+      <c r="E103" s="8" t="inlineStr">
+        <is>
+          <t>SEN-FK — Fatick Department</t>
+        </is>
+      </c>
+      <c r="F103" s="8" t="inlineStr">
+        <is>
+          <t>Vector</t>
+        </is>
+      </c>
+      <c r="G103" s="8" t="inlineStr">
+        <is>
+          <t>Landscape boundary</t>
+        </is>
+      </c>
+      <c r="H103" s="8" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="I103" s="8" t="inlineStr">
+        <is>
+          <t>Alliance Bioversity-CIAT (MOSAIC)</t>
+        </is>
+      </c>
+      <c r="J103" s="8" t="inlineStr">
+        <is>
+          <t>Lizeth Llanos (l.llanos@cgiar.org)</t>
+        </is>
+      </c>
+      <c r="K103" s="8" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="L103" s="8" t="inlineStr">
+        <is>
+          <t>Source terms (https://gadm.org/license.html)</t>
+        </is>
+      </c>
+      <c r="M103" s="8" t="inlineStr">
+        <is>
+          <t>Processed</t>
+        </is>
+      </c>
+      <c r="N103" s="8" t="inlineStr">
+        <is>
+          <t>SEN-FK_Fatick_Department_boundary_2026-10-14.zip</t>
+        </is>
+      </c>
+      <c r="O103" s="8" t="inlineStr">
+        <is>
+          <t>GitHub release boundaries-2026-10-14 (MOSAIC-mfl/catalog)</t>
+        </is>
+      </c>
+      <c r="P103" s="8" t="n"/>
+      <c r="Q103" s="8" t="n"/>
+      <c r="R103" s="9" t="inlineStr">
+        <is>
+          <t>Canonical MOSAIC delineation of the Fatick Department living landscape (SEN-FK), used to define the landscape across the catalogue. Source: GADM: level 2 unit Fatick departement (GADM v2 attribute schema; geometry identical to GADM 3.6 and 4.1 SEN.3.1_1). Full-detail Shapefile and GeoPackage in the dated release boundaries-2026-10-14 of MOSAIC-mfl/catalog; a simplified outline is attached to the landscape's STAC collection.</t>
+        </is>
+      </c>
+      <c r="S103" s="8" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="T103" s="8" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="U103" s="8" t="inlineStr">
+        <is>
+          <t>Static</t>
+        </is>
+      </c>
+      <c r="V103" s="8" t="inlineStr">
+        <is>
+          <t>https://github.com/MOSAIC-mfl/catalog/releases/download/boundaries-2026-10-14/SEN-FK_Fatick_Department_boundary_2026-10-14.zip</t>
+        </is>
+      </c>
+      <c r="W103" s="8" t="inlineStr">
+        <is>
+          <t>16 KB</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="10" t="inlineStr">
+        <is>
+          <t>MFL-2026-105</t>
+        </is>
+      </c>
+      <c r="B104" s="10" t="inlineStr">
+        <is>
+          <t>Mbire – Lower Zambezi Valley living landscape boundary</t>
+        </is>
+      </c>
+      <c r="C104" s="10" t="inlineStr">
+        <is>
+          <t>Zimbabwe</t>
+        </is>
+      </c>
+      <c r="D104" s="10" t="inlineStr">
+        <is>
+          <t>Boundaries / admin units</t>
+        </is>
+      </c>
+      <c r="E104" s="10" t="inlineStr">
+        <is>
+          <t>ZWE-MB — Mbire – Lower Zambezi Valley</t>
+        </is>
+      </c>
+      <c r="F104" s="10" t="inlineStr">
+        <is>
+          <t>Vector</t>
+        </is>
+      </c>
+      <c r="G104" s="10" t="inlineStr">
+        <is>
+          <t>Landscape boundary</t>
+        </is>
+      </c>
+      <c r="H104" s="10" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="I104" s="10" t="inlineStr">
+        <is>
+          <t>Alliance Bioversity-CIAT (MOSAIC)</t>
+        </is>
+      </c>
+      <c r="J104" s="10" t="inlineStr">
+        <is>
+          <t>Lizeth Llanos (l.llanos@cgiar.org)</t>
+        </is>
+      </c>
+      <c r="K104" s="10" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="L104" s="10" t="inlineStr">
+        <is>
+          <t>Source terms (https://gadm.org/license.html)</t>
+        </is>
+      </c>
+      <c r="M104" s="10" t="inlineStr">
+        <is>
+          <t>Processed</t>
+        </is>
+      </c>
+      <c r="N104" s="10" t="inlineStr">
+        <is>
+          <t>ZWE-MB_Mbire_Lower_Zambezi_Valley_boundary_2026-10-14.zip</t>
+        </is>
+      </c>
+      <c r="O104" s="10" t="inlineStr">
+        <is>
+          <t>GitHub release boundaries-2026-10-14 (MOSAIC-mfl/catalog)</t>
+        </is>
+      </c>
+      <c r="P104" s="10" t="n"/>
+      <c r="Q104" s="10" t="n"/>
+      <c r="R104" s="11" t="inlineStr">
+        <is>
+          <t>Canonical MOSAIC delineation of the Mbire – Lower Zambezi Valley living landscape (ZWE-MB), used to define the landscape across the catalogue. Source: GADM 4.1, level 3: all 112 wards of the districts Mbire, Centenary/Muzarabani and Mount Darwin (Mashonaland Central) and Hurungwe (Mashonaland West), unmodified. Full-detail Shapefile and GeoPackage in the dated release boundaries-2026-10-14 of MOSAIC-mfl/catalog; a simplified outline is attached to the landscape's STAC collection.</t>
+        </is>
+      </c>
+      <c r="S104" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="T104" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="U104" s="10" t="inlineStr">
+        <is>
+          <t>Static</t>
+        </is>
+      </c>
+      <c r="V104" s="10" t="inlineStr">
+        <is>
+          <t>https://github.com/MOSAIC-mfl/catalog/releases/download/boundaries-2026-10-14/ZWE-MB_Mbire_Lower_Zambezi_Valley_boundary_2026-10-14.zip</t>
+        </is>
+      </c>
+      <c r="W104" s="10" t="inlineStr">
+        <is>
+          <t>185 KB</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A2:W96"/>
+  <autoFilter ref="A2:W104"/>
   <conditionalFormatting sqref="K3:K300">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
       <formula>"Open"</formula>

--- a/catalog/MFL_Dataset_Registry.xlsx
+++ b/catalog/MFL_Dataset_Registry.xlsx
@@ -1537,7 +1537,7 @@
       </c>
       <c r="K3" s="8" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Internal</t>
         </is>
       </c>
       <c r="L3" s="8" t="inlineStr">
@@ -1733,7 +1733,7 @@
       </c>
       <c r="K5" s="8" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Internal</t>
         </is>
       </c>
       <c r="L5" s="8" t="inlineStr">
@@ -3358,7 +3358,7 @@
       </c>
       <c r="K22" s="10" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Restricted</t>
         </is>
       </c>
       <c r="L22" s="10" t="inlineStr">
@@ -3532,7 +3532,7 @@
       </c>
       <c r="K24" s="10" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Restricted</t>
         </is>
       </c>
       <c r="L24" s="10" t="inlineStr">
@@ -3625,7 +3625,7 @@
       </c>
       <c r="K25" s="8" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Restricted</t>
         </is>
       </c>
       <c r="L25" s="8" t="inlineStr">
@@ -3807,7 +3807,7 @@
       </c>
       <c r="K27" s="8" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Restricted</t>
         </is>
       </c>
       <c r="L27" s="8" t="inlineStr">
@@ -3993,7 +3993,7 @@
       </c>
       <c r="K29" s="8" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Restricted</t>
         </is>
       </c>
       <c r="L29" s="8" t="inlineStr">
@@ -4090,7 +4090,7 @@
       </c>
       <c r="K30" s="10" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Restricted</t>
         </is>
       </c>
       <c r="L30" s="10" t="inlineStr">
@@ -4183,7 +4183,7 @@
       </c>
       <c r="K31" s="8" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Restricted</t>
         </is>
       </c>
       <c r="L31" s="8" t="inlineStr">
@@ -4280,7 +4280,7 @@
       </c>
       <c r="K32" s="10" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Restricted</t>
         </is>
       </c>
       <c r="L32" s="10" t="inlineStr">
@@ -4381,7 +4381,7 @@
       </c>
       <c r="K33" s="8" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Restricted</t>
         </is>
       </c>
       <c r="L33" s="8" t="inlineStr">
@@ -4482,7 +4482,7 @@
       </c>
       <c r="K34" s="10" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Restricted</t>
         </is>
       </c>
       <c r="L34" s="10" t="inlineStr">
@@ -4583,7 +4583,7 @@
       </c>
       <c r="K35" s="8" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Restricted</t>
         </is>
       </c>
       <c r="L35" s="8" t="inlineStr">
@@ -4672,7 +4672,7 @@
       </c>
       <c r="K36" s="10" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Restricted</t>
         </is>
       </c>
       <c r="L36" s="10" t="inlineStr">
@@ -4838,7 +4838,7 @@
       </c>
       <c r="K38" s="10" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Restricted</t>
         </is>
       </c>
       <c r="L38" s="10" t="inlineStr">
@@ -5016,7 +5016,7 @@
       </c>
       <c r="K40" s="10" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Restricted</t>
         </is>
       </c>
       <c r="L40" s="10" t="inlineStr">
@@ -5105,7 +5105,7 @@
       </c>
       <c r="K41" s="8" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Restricted</t>
         </is>
       </c>
       <c r="L41" s="8" t="inlineStr">
@@ -5190,7 +5190,7 @@
       </c>
       <c r="K42" s="10" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Restricted</t>
         </is>
       </c>
       <c r="L42" s="10" t="inlineStr">
@@ -5275,7 +5275,7 @@
       </c>
       <c r="K43" s="8" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Restricted</t>
         </is>
       </c>
       <c r="L43" s="8" t="inlineStr">
@@ -5364,7 +5364,7 @@
       </c>
       <c r="K44" s="10" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Restricted</t>
         </is>
       </c>
       <c r="L44" s="10" t="inlineStr">
@@ -7134,7 +7134,7 @@
       </c>
       <c r="K62" s="10" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Restricted</t>
         </is>
       </c>
       <c r="L62" s="10" t="inlineStr">
@@ -7340,7 +7340,7 @@
       </c>
       <c r="K64" s="10" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Restricted</t>
         </is>
       </c>
       <c r="L64" s="10" t="inlineStr">
@@ -7631,7 +7631,7 @@
       </c>
       <c r="K67" s="8" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Restricted</t>
         </is>
       </c>
       <c r="L67" s="8" t="inlineStr">
@@ -7732,7 +7732,7 @@
       </c>
       <c r="K68" s="10" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Restricted</t>
         </is>
       </c>
       <c r="L68" s="10" t="inlineStr">
@@ -9254,7 +9254,7 @@
       </c>
       <c r="K82" s="10" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Restricted</t>
         </is>
       </c>
       <c r="L82" s="10" t="inlineStr">

--- a/catalog/MFL_Dataset_Registry.xlsx
+++ b/catalog/MFL_Dataset_Registry.xlsx
@@ -5064,7 +5064,7 @@
       </c>
       <c r="B41" s="8" t="inlineStr">
         <is>
-          <t>District level crop area, prodcution and yield data - India</t>
+          <t>District level crop area, production and yield data - Ethiopia</t>
         </is>
       </c>
       <c r="C41" s="8" t="inlineStr">
@@ -5296,11 +5296,7 @@
       </c>
       <c r="P43" s="8" t="n"/>
       <c r="Q43" s="8" t="n"/>
-      <c r="R43" s="9" t="inlineStr">
-        <is>
-          <t>Agroecological zonations</t>
-        </is>
-      </c>
+      <c r="R43" s="9" t="n"/>
       <c r="S43" s="8" t="n"/>
       <c r="T43" s="8" t="n"/>
       <c r="U43" s="8" t="inlineStr">

--- a/catalog/MFL_Dataset_Registry.xlsx
+++ b/catalog/MFL_Dataset_Registry.xlsx
@@ -2794,7 +2794,7 @@
       </c>
       <c r="I16" s="10" t="inlineStr">
         <is>
-          <t>National government (external)</t>
+          <t>CoRE Stack (external)</t>
         </is>
       </c>
       <c r="J16" s="10" t="inlineStr">
@@ -2821,7 +2821,7 @@
       <c r="N16" s="10" t="n"/>
       <c r="O16" s="10" t="inlineStr">
         <is>
-          <t>CoreStack: Github / Google rive</t>
+          <t>CoRE Stack: public Google Earth Engine assets and Google Drive downloads, one row per layer in the CoRE Stack GEE Layers Links sheet. Map viewer: https://ee-corestackdev.projects.earthengine.app/view/core-stack-gee-app</t>
         </is>
       </c>
       <c r="P16" s="10" t="n"/>
@@ -2844,8 +2844,7 @@
       </c>
       <c r="V16" s="10" t="inlineStr">
         <is>
-          <t>https://github.com/core-stack-org/QGIS-Styles/blob/main/Tree%20Health/ccd_style.qml
-https://github.com/core-stack-org/QGIS-Styles/blob/main/Tree%20Health/canopy_height.qml</t>
+          <t>https://docs.google.com/spreadsheets/d/1xS5d7vgyjyoqqnmmajKDZBx9qS6GqyAdSbNDR62ot2Y/edit?gid=0</t>
         </is>
       </c>
       <c r="W16" s="10" t="n"/>
@@ -2893,7 +2892,7 @@
       </c>
       <c r="I17" s="8" t="inlineStr">
         <is>
-          <t>National government (external)</t>
+          <t>India-WRIS, via CoRE Stack (external)</t>
         </is>
       </c>
       <c r="J17" s="8" t="inlineStr">
@@ -2909,7 +2908,7 @@
       </c>
       <c r="L17" s="8" t="inlineStr">
         <is>
-          <t>CC BY 4.0</t>
+          <t>India-WRIS layers re-published by CoRE Stack; no licence stated by the source</t>
         </is>
       </c>
       <c r="M17" s="8" t="inlineStr">
@@ -2920,7 +2919,7 @@
       <c r="N17" s="8" t="n"/>
       <c r="O17" s="8" t="inlineStr">
         <is>
-          <t>CoreStack: Github / Google rive</t>
+          <t>CoRE Stack: public Google Earth Engine assets and Google Drive downloads, one row per layer in the CoRE Stack GEE Layers Links sheet (Waterbodies Layers group). Map viewer: https://ee-corestackdev.projects.earthengine.app/view/core-stack-gee-app</t>
         </is>
       </c>
       <c r="P17" s="8" t="n"/>
@@ -2943,7 +2942,7 @@
       </c>
       <c r="V17" s="8" t="inlineStr">
         <is>
-          <t>https://github.com/core-stack-org/QGIS-Styles/blob/main/Hydrology/Sub-Basin_style.qml</t>
+          <t>https://docs.google.com/spreadsheets/d/1xS5d7vgyjyoqqnmmajKDZBx9qS6GqyAdSbNDR62ot2Y/edit?gid=0</t>
         </is>
       </c>
       <c r="W17" s="8" t="n"/>
@@ -2991,7 +2990,7 @@
       </c>
       <c r="I18" s="10" t="inlineStr">
         <is>
-          <t>National government (external)</t>
+          <t>CoRE Stack (external)</t>
         </is>
       </c>
       <c r="J18" s="10" t="inlineStr">
@@ -3018,7 +3017,7 @@
       <c r="N18" s="10" t="n"/>
       <c r="O18" s="10" t="inlineStr">
         <is>
-          <t>CoreStack: Github / Google rive</t>
+          <t>CoRE Stack: public Google Earth Engine assets and Google Drive downloads, one row per layer in the CoRE Stack GEE Layers Links sheet. Map viewer: https://ee-corestackdev.projects.earthengine.app/view/core-stack-gee-app</t>
         </is>
       </c>
       <c r="P18" s="10" t="n"/>
@@ -3041,7 +3040,7 @@
       </c>
       <c r="V18" s="10" t="inlineStr">
         <is>
-          <t>https://github.com/core-stack-org/QGIS-Styles/blob/main/Land/LULC0_12class.qml</t>
+          <t>https://docs.google.com/spreadsheets/d/1xS5d7vgyjyoqqnmmajKDZBx9qS6GqyAdSbNDR62ot2Y/edit?gid=0</t>
         </is>
       </c>
       <c r="W18" s="10" t="n"/>

--- a/catalog/MFL_Dataset_Registry.xlsx
+++ b/catalog/MFL_Dataset_Registry.xlsx
@@ -20,7 +20,7 @@
     <definedName name="MOSAIC_Access">Reference!$I$2:$I$4</definedName>
     <definedName name="MOSAIC_Migration">Reference!$O$2:$O$3</definedName>
     <definedName name="MOSAIC_UpdFreq">Reference!$Q$2:$Q$7</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">' Registry'!$A$2:$W$104</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">' Registry'!$A$2:$W$110</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -1221,7 +1221,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W104"/>
+  <dimension ref="A1:W110"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -3048,52 +3048,53 @@
     <row r="19">
       <c r="A19" s="8" t="inlineStr">
         <is>
-          <t>MFL-2026-017</t>
+          <t>MFL-2026-016</t>
         </is>
       </c>
       <c r="B19" s="8" t="inlineStr">
         <is>
-          <t>Land Use and Land Cover - Senegal</t>
+          <t>Groundwater data - India</t>
         </is>
       </c>
       <c r="C19" s="8" t="inlineStr">
         <is>
-          <t>Senegal</t>
+          <t>India</t>
         </is>
       </c>
       <c r="D19" s="8" t="inlineStr">
         <is>
-          <t>Land cover / land use</t>
+          <t>Water / hydrology</t>
         </is>
       </c>
       <c r="E19" s="8" t="inlineStr">
         <is>
-          <t>SEN-FK — Fatick Department</t>
+          <t>IND-CH — Central India Highlands</t>
         </is>
       </c>
       <c r="F19" s="8" t="inlineStr">
         <is>
-          <t>Raster</t>
+          <t>Vector</t>
         </is>
       </c>
       <c r="G19" s="8" t="inlineStr">
         <is>
-          <t>10m</t>
+          <t>Multiple resolutions</t>
         </is>
       </c>
       <c r="H19" s="8" t="inlineStr">
         <is>
-          <t>2017-2025</t>
+          <t>2011 - 2025</t>
         </is>
       </c>
       <c r="I19" s="8" t="inlineStr">
         <is>
-          <t>ISRA-BAME</t>
+          <t>CGWB, via CoRE Stack (external)</t>
         </is>
       </c>
       <c r="J19" s="8" t="inlineStr">
         <is>
-          <t>dieyemohamadou@gmail.com</t>
+          <t>Core Stack (Open access)
+Sudharsan Malaiappan - s.maliappan@cgiar.org</t>
         </is>
       </c>
       <c r="K19" s="8" t="inlineStr">
@@ -3103,28 +3104,32 @@
       </c>
       <c r="L19" s="8" t="inlineStr">
         <is>
-          <t>CC BY 4.0</t>
+          <t>CGWB layers re-published by CoRE Stack; no licence stated in the CoRE Stack layer sheet</t>
         </is>
       </c>
       <c r="M19" s="8" t="inlineStr">
         <is>
-          <t>Validated</t>
+          <t>Processed</t>
         </is>
       </c>
       <c r="N19" s="8" t="n"/>
       <c r="O19" s="8" t="inlineStr">
         <is>
-          <t>Drive</t>
+          <t>CoRE Stack: public Google Earth Engine assets and Google Drive downloads, one row per layer in the CoRE Stack GEE Layers Links sheet (Groundwater Layers group). Map viewer: https://ee-corestackdev.projects.earthengine.app/view/core-stack-gee-app</t>
         </is>
       </c>
       <c r="P19" s="8" t="n"/>
       <c r="Q19" s="8" t="n"/>
       <c r="R19" s="9" t="inlineStr">
         <is>
-          <t>Land cover derived from Sentinel-2 imagery using machine learning classification. Moderate spatial accuracy depending on land cover type and cloud cover; small or rapid changes may not be captured. Related: Sentinel-2 imagery, global land cover datasets, NDVI products.</t>
-        </is>
-      </c>
-      <c r="S19" s="8" t="n"/>
+          <t>Groundwater levels in dug wells and bore wells, and the Stage of Groundwater Extraction from the groundwater resource assessments of 2011, 2013, 2017, 2020, 2022, 2023, 2024 and 2025. Published by the Central Ground Water Board (CGWB) and re-published by CoRE Stack. Pan-India.</t>
+        </is>
+      </c>
+      <c r="S19" s="8" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
       <c r="T19" s="8" t="inlineStr">
         <is>
           <t>2025</t>
@@ -3137,7 +3142,7 @@
       </c>
       <c r="V19" s="8" t="inlineStr">
         <is>
-          <t>https://livingatlas.arcgis.com/landcoverexplorer/#mapCenter=-14.06266%2C13.65709%2C11.00&amp;mode=step&amp;timeExtent=2017%2C2022&amp;year=2023</t>
+          <t>https://docs.google.com/spreadsheets/d/1xS5d7vgyjyoqqnmmajKDZBx9qS6GqyAdSbNDR62ot2Y/edit?gid=0</t>
         </is>
       </c>
       <c r="W19" s="8" t="n"/>
@@ -3145,12 +3150,12 @@
     <row r="20">
       <c r="A20" s="10" t="inlineStr">
         <is>
-          <t>MFL-2026-018</t>
+          <t>MFL-2026-017</t>
         </is>
       </c>
       <c r="B20" s="10" t="inlineStr">
         <is>
-          <t>Departments</t>
+          <t>Land Use and Land Cover - Senegal</t>
         </is>
       </c>
       <c r="C20" s="10" t="inlineStr">
@@ -3160,7 +3165,7 @@
       </c>
       <c r="D20" s="10" t="inlineStr">
         <is>
-          <t>Boundaries / admin units</t>
+          <t>Land cover / land use</t>
         </is>
       </c>
       <c r="E20" s="10" t="inlineStr">
@@ -3170,11 +3175,19 @@
       </c>
       <c r="F20" s="10" t="inlineStr">
         <is>
-          <t>Vector</t>
-        </is>
-      </c>
-      <c r="G20" s="10" t="n"/>
-      <c r="H20" s="10" t="n"/>
+          <t>Raster</t>
+        </is>
+      </c>
+      <c r="G20" s="10" t="inlineStr">
+        <is>
+          <t>10m</t>
+        </is>
+      </c>
+      <c r="H20" s="10" t="inlineStr">
+        <is>
+          <t>2017-2025</t>
+        </is>
+      </c>
       <c r="I20" s="10" t="inlineStr">
         <is>
           <t>ISRA-BAME</t>
@@ -3192,7 +3205,7 @@
       </c>
       <c r="L20" s="10" t="inlineStr">
         <is>
-          <t>Restricted — GADM terms (academic/non-commercial use only, no redistribution)</t>
+          <t>CC BY 4.0</t>
         </is>
       </c>
       <c r="M20" s="10" t="inlineStr">
@@ -3210,19 +3223,23 @@
       <c r="Q20" s="10" t="n"/>
       <c r="R20" s="11" t="inlineStr">
         <is>
-          <t>Official administrative boundaries of Senegal</t>
+          <t>Land cover derived from Sentinel-2 imagery using machine learning classification. Moderate spatial accuracy depending on land cover type and cloud cover; small or rapid changes may not be captured. Related: Sentinel-2 imagery, global land cover datasets, NDVI products.</t>
         </is>
       </c>
       <c r="S20" s="10" t="n"/>
-      <c r="T20" s="10" t="n"/>
+      <c r="T20" s="10" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
       <c r="U20" s="10" t="inlineStr">
         <is>
-          <t>Static</t>
+          <t>Annual</t>
         </is>
       </c>
       <c r="V20" s="10" t="inlineStr">
         <is>
-          <t>https://gadm.org/</t>
+          <t>https://livingatlas.arcgis.com/landcoverexplorer/#mapCenter=-14.06266%2C13.65709%2C11.00&amp;mode=step&amp;timeExtent=2017%2C2022&amp;year=2023</t>
         </is>
       </c>
       <c r="W20" s="10" t="n"/>
@@ -3230,12 +3247,12 @@
     <row r="21">
       <c r="A21" s="8" t="inlineStr">
         <is>
-          <t>MFL-2026-019</t>
+          <t>MFL-2026-018</t>
         </is>
       </c>
       <c r="B21" s="8" t="inlineStr">
         <is>
-          <t>Municipalities</t>
+          <t>Departments</t>
         </is>
       </c>
       <c r="C21" s="8" t="inlineStr">
@@ -3315,12 +3332,12 @@
     <row r="22">
       <c r="A22" s="10" t="inlineStr">
         <is>
-          <t>MFL-2026-020</t>
+          <t>MFL-2026-019</t>
         </is>
       </c>
       <c r="B22" s="10" t="inlineStr">
         <is>
-          <t>Localities</t>
+          <t>Municipalities</t>
         </is>
       </c>
       <c r="C22" s="10" t="inlineStr">
@@ -3357,12 +3374,12 @@
       </c>
       <c r="K22" s="10" t="inlineStr">
         <is>
-          <t>Restricted</t>
+          <t>Open</t>
         </is>
       </c>
       <c r="L22" s="10" t="inlineStr">
         <is>
-          <t>CC BY 4.0</t>
+          <t>Restricted — GADM terms (academic/non-commercial use only, no redistribution)</t>
         </is>
       </c>
       <c r="M22" s="10" t="inlineStr">
@@ -3390,18 +3407,22 @@
           <t>Static</t>
         </is>
       </c>
-      <c r="V22" s="10" t="n"/>
+      <c r="V22" s="10" t="inlineStr">
+        <is>
+          <t>https://gadm.org/</t>
+        </is>
+      </c>
       <c r="W22" s="10" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="8" t="inlineStr">
         <is>
-          <t>MFL-2026-021</t>
+          <t>MFL-2026-020</t>
         </is>
       </c>
       <c r="B23" s="8" t="inlineStr">
         <is>
-          <t>Road</t>
+          <t>Localities</t>
         </is>
       </c>
       <c r="C23" s="8" t="inlineStr">
@@ -3438,12 +3459,12 @@
       </c>
       <c r="K23" s="8" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Restricted</t>
         </is>
       </c>
       <c r="L23" s="8" t="inlineStr">
         <is>
-          <t>Restricted — GADM terms (academic/non-commercial use only, no redistribution)</t>
+          <t>CC BY 4.0</t>
         </is>
       </c>
       <c r="M23" s="8" t="inlineStr">
@@ -3471,22 +3492,18 @@
           <t>Static</t>
         </is>
       </c>
-      <c r="V23" s="8" t="inlineStr">
-        <is>
-          <t>https://gadm.org/</t>
-        </is>
-      </c>
+      <c r="V23" s="8" t="n"/>
       <c r="W23" s="8" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="10" t="inlineStr">
         <is>
-          <t>MFL-2026-022</t>
+          <t>MFL-2026-021</t>
         </is>
       </c>
       <c r="B24" s="10" t="inlineStr">
         <is>
-          <t>Land Degradation - Senegal</t>
+          <t>Road</t>
         </is>
       </c>
       <c r="C24" s="10" t="inlineStr">
@@ -3496,7 +3513,7 @@
       </c>
       <c r="D24" s="10" t="inlineStr">
         <is>
-          <t>Degradation / land health</t>
+          <t>Boundaries / admin units</t>
         </is>
       </c>
       <c r="E24" s="10" t="inlineStr">
@@ -3506,19 +3523,11 @@
       </c>
       <c r="F24" s="10" t="inlineStr">
         <is>
-          <t>Raster</t>
-        </is>
-      </c>
-      <c r="G24" s="10" t="inlineStr">
-        <is>
-          <t>500m</t>
-        </is>
-      </c>
-      <c r="H24" s="10" t="inlineStr">
-        <is>
-          <t>2000 - 2024</t>
-        </is>
-      </c>
+          <t>Vector</t>
+        </is>
+      </c>
+      <c r="G24" s="10" t="n"/>
+      <c r="H24" s="10" t="n"/>
       <c r="I24" s="10" t="inlineStr">
         <is>
           <t>ISRA-BAME</t>
@@ -3531,46 +3540,42 @@
       </c>
       <c r="K24" s="10" t="inlineStr">
         <is>
-          <t>Restricted</t>
+          <t>Open</t>
         </is>
       </c>
       <c r="L24" s="10" t="inlineStr">
         <is>
-          <t>CC BY 4.0</t>
+          <t>Restricted — GADM terms (academic/non-commercial use only, no redistribution)</t>
         </is>
       </c>
       <c r="M24" s="10" t="inlineStr">
         <is>
-          <t>Processed</t>
+          <t>Validated</t>
         </is>
       </c>
       <c r="N24" s="10" t="n"/>
       <c r="O24" s="10" t="inlineStr">
         <is>
-          <t>local</t>
+          <t>Drive</t>
         </is>
       </c>
       <c r="P24" s="10" t="n"/>
       <c r="Q24" s="10" t="n"/>
       <c r="R24" s="11" t="inlineStr">
         <is>
-          <t>Based on MODIS time-series vegetation indices (NDVI/EVI) to assess land condition. Coarse spatial resolution (250m–1km) and atmospheric/cloud effects may limit precision; short-term changes may be smoothed. Related: Landsat, Sentinel-2, soil and climate datasets. — Original landscape entry: In the Senegal region, the resolution does not allow for data at the departmental level</t>
+          <t>Official administrative boundaries of Senegal</t>
         </is>
       </c>
       <c r="S24" s="10" t="n"/>
-      <c r="T24" s="10" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
+      <c r="T24" s="10" t="n"/>
       <c r="U24" s="10" t="inlineStr">
         <is>
-          <t>Annual</t>
+          <t>Static</t>
         </is>
       </c>
       <c r="V24" s="10" t="inlineStr">
         <is>
-          <t>Plugin Trends earth</t>
+          <t>https://gadm.org/</t>
         </is>
       </c>
       <c r="W24" s="10" t="n"/>
@@ -3578,12 +3583,12 @@
     <row r="25">
       <c r="A25" s="8" t="inlineStr">
         <is>
-          <t>MFL-2026-023</t>
+          <t>MFL-2026-022</t>
         </is>
       </c>
       <c r="B25" s="8" t="inlineStr">
         <is>
-          <t>Tree mapping</t>
+          <t>Land Degradation - Senegal</t>
         </is>
       </c>
       <c r="C25" s="8" t="inlineStr">
@@ -3593,7 +3598,7 @@
       </c>
       <c r="D25" s="8" t="inlineStr">
         <is>
-          <t>Land cover / land use</t>
+          <t>Degradation / land health</t>
         </is>
       </c>
       <c r="E25" s="8" t="inlineStr">
@@ -3603,13 +3608,17 @@
       </c>
       <c r="F25" s="8" t="inlineStr">
         <is>
-          <t>Vector</t>
-        </is>
-      </c>
-      <c r="G25" s="8" t="n"/>
+          <t>Raster</t>
+        </is>
+      </c>
+      <c r="G25" s="8" t="inlineStr">
+        <is>
+          <t>500m</t>
+        </is>
+      </c>
       <c r="H25" s="8" t="inlineStr">
         <is>
-          <t>2021</t>
+          <t>2000 - 2024</t>
         </is>
       </c>
       <c r="I25" s="8" t="inlineStr">
@@ -3634,41 +3643,49 @@
       </c>
       <c r="M25" s="8" t="inlineStr">
         <is>
-          <t>Validated</t>
+          <t>Processed</t>
         </is>
       </c>
       <c r="N25" s="8" t="n"/>
       <c r="O25" s="8" t="inlineStr">
         <is>
-          <t>Drive</t>
+          <t>local</t>
         </is>
       </c>
       <c r="P25" s="8" t="n"/>
       <c r="Q25" s="8" t="n"/>
       <c r="R25" s="9" t="inlineStr">
         <is>
-          <t>Tree data are derived from Sentinel-2 imagery using image classification techniques. Limitations include infrequent updates, which may affect temporal accuracy and may not reflect recent changes. Related datasets: Sentinel-2 imagery, land cover products, vegetation indices (NDVI/EVI).</t>
+          <t>Based on MODIS time-series vegetation indices (NDVI/EVI) to assess land condition. Coarse spatial resolution (250m–1km) and atmospheric/cloud effects may limit precision; short-term changes may be smoothed. Related: Landsat, Sentinel-2, soil and climate datasets. — Original landscape entry: In the Senegal region, the resolution does not allow for data at the departmental level</t>
         </is>
       </c>
       <c r="S25" s="8" t="n"/>
       <c r="T25" s="8" t="inlineStr">
         <is>
-          <t>2021</t>
-        </is>
-      </c>
-      <c r="U25" s="8" t="n"/>
-      <c r="V25" s="8" t="n"/>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="U25" s="8" t="inlineStr">
+        <is>
+          <t>Annual</t>
+        </is>
+      </c>
+      <c r="V25" s="8" t="inlineStr">
+        <is>
+          <t>Plugin Trends earth</t>
+        </is>
+      </c>
       <c r="W25" s="8" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="10" t="inlineStr">
         <is>
-          <t>MFL-2026-024</t>
+          <t>MFL-2026-023</t>
         </is>
       </c>
       <c r="B26" s="10" t="inlineStr">
         <is>
-          <t>Rainfall data</t>
+          <t>Tree mapping</t>
         </is>
       </c>
       <c r="C26" s="10" t="inlineStr">
@@ -3678,7 +3695,7 @@
       </c>
       <c r="D26" s="10" t="inlineStr">
         <is>
-          <t>Water / hydrology</t>
+          <t>Land cover / land use</t>
         </is>
       </c>
       <c r="E26" s="10" t="inlineStr">
@@ -3688,13 +3705,13 @@
       </c>
       <c r="F26" s="10" t="inlineStr">
         <is>
-          <t>Tabular</t>
+          <t>Vector</t>
         </is>
       </c>
       <c r="G26" s="10" t="n"/>
       <c r="H26" s="10" t="inlineStr">
         <is>
-          <t>1981 – présent</t>
+          <t>2021</t>
         </is>
       </c>
       <c r="I26" s="10" t="inlineStr">
@@ -3709,7 +3726,7 @@
       </c>
       <c r="K26" s="10" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Restricted</t>
         </is>
       </c>
       <c r="L26" s="10" t="inlineStr">
@@ -3719,64 +3736,56 @@
       </c>
       <c r="M26" s="10" t="inlineStr">
         <is>
-          <t>Processed</t>
+          <t>Validated</t>
         </is>
       </c>
       <c r="N26" s="10" t="n"/>
       <c r="O26" s="10" t="inlineStr">
         <is>
-          <t>local</t>
+          <t>Drive</t>
         </is>
       </c>
       <c r="P26" s="10" t="n"/>
       <c r="Q26" s="10" t="n"/>
       <c r="R26" s="11" t="inlineStr">
         <is>
-          <t>Derived from satellite observations and climate models (reanalysis and gauge integration). Coarse spatial resolution (~0.25°–1°) and potential bias compared to ground stations; local variability may be underestimated. Related: GPM, TRMM, ERA5, meteorological station data.</t>
+          <t>Tree data are derived from Sentinel-2 imagery using image classification techniques. Limitations include infrequent updates, which may affect temporal accuracy and may not reflect recent changes. Related datasets: Sentinel-2 imagery, land cover products, vegetation indices (NDVI/EVI).</t>
         </is>
       </c>
       <c r="S26" s="10" t="n"/>
       <c r="T26" s="10" t="inlineStr">
         <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="U26" s="10" t="inlineStr">
-        <is>
-          <t>Annual</t>
-        </is>
-      </c>
-      <c r="V26" s="10" t="inlineStr">
-        <is>
-          <t>https://power.larc.nasa.gov/data-access-viewer/</t>
-        </is>
-      </c>
+          <t>2021</t>
+        </is>
+      </c>
+      <c r="U26" s="10" t="n"/>
+      <c r="V26" s="10" t="n"/>
       <c r="W26" s="10" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="8" t="inlineStr">
         <is>
-          <t>MFL-2026-025</t>
+          <t>MFL-2026-024</t>
         </is>
       </c>
       <c r="B27" s="8" t="inlineStr">
         <is>
-          <t>Crop damage mapping</t>
+          <t>Rainfall data</t>
         </is>
       </c>
       <c r="C27" s="8" t="inlineStr">
         <is>
-          <t>Zimbabwe</t>
+          <t>Senegal</t>
         </is>
       </c>
       <c r="D27" s="8" t="inlineStr">
         <is>
-          <t>Ecosystem services</t>
+          <t>Water / hydrology</t>
         </is>
       </c>
       <c r="E27" s="8" t="inlineStr">
         <is>
-          <t>ZWE-MB — Mbire – Lower Zambezi Valley</t>
+          <t>SEN-FK — Fatick Department</t>
         </is>
       </c>
       <c r="F27" s="8" t="inlineStr">
@@ -3784,68 +3793,64 @@
           <t>Tabular</t>
         </is>
       </c>
-      <c r="G27" s="8" t="inlineStr">
-        <is>
-          <t>Ward level</t>
-        </is>
-      </c>
+      <c r="G27" s="8" t="n"/>
       <c r="H27" s="8" t="inlineStr">
         <is>
-          <t>2025 -2026</t>
+          <t>1981 – présent</t>
         </is>
       </c>
       <c r="I27" s="8" t="inlineStr">
         <is>
-          <t>CIMMYT</t>
+          <t>ISRA-BAME</t>
         </is>
       </c>
       <c r="J27" s="8" t="inlineStr">
         <is>
-          <t>Telma.SIBANDA@um6p.ma</t>
+          <t>dieyemohamadou@gmail.com</t>
         </is>
       </c>
       <c r="K27" s="8" t="inlineStr">
         <is>
-          <t>Restricted</t>
+          <t>Open</t>
         </is>
       </c>
       <c r="L27" s="8" t="inlineStr">
         <is>
-          <t>CGIAR Open Access</t>
+          <t>CC BY 4.0</t>
         </is>
       </c>
       <c r="M27" s="8" t="inlineStr">
         <is>
-          <t>Raw</t>
+          <t>Processed</t>
         </is>
       </c>
       <c r="N27" s="8" t="n"/>
       <c r="O27" s="8" t="inlineStr">
         <is>
-          <t>Drive</t>
+          <t>local</t>
         </is>
       </c>
       <c r="P27" s="8" t="n"/>
       <c r="Q27" s="8" t="n"/>
       <c r="R27" s="9" t="inlineStr">
         <is>
-          <t>Ward-level crop damage data (severity and incidence) by different species — Original landscape entry: Mbire: Wards 2, 3, 9, 12 and 17</t>
+          <t>Derived from satellite observations and climate models (reanalysis and gauge integration). Coarse spatial resolution (~0.25°–1°) and potential bias compared to ground stations; local variability may be underestimated. Related: GPM, TRMM, ERA5, meteorological station data.</t>
         </is>
       </c>
       <c r="S27" s="8" t="n"/>
       <c r="T27" s="8" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="U27" s="8" t="inlineStr">
         <is>
-          <t>Seasonal</t>
+          <t>Annual</t>
         </is>
       </c>
       <c r="V27" s="8" t="inlineStr">
         <is>
-          <t>Internal Available on request</t>
+          <t>https://power.larc.nasa.gov/data-access-viewer/</t>
         </is>
       </c>
       <c r="W27" s="8" t="n"/>
@@ -3853,12 +3858,12 @@
     <row r="28">
       <c r="A28" s="10" t="inlineStr">
         <is>
-          <t>MFL-2026-026</t>
+          <t>MFL-2026-025</t>
         </is>
       </c>
       <c r="B28" s="10" t="inlineStr">
         <is>
-          <t>District/ward boundaries</t>
+          <t>Crop damage mapping</t>
         </is>
       </c>
       <c r="C28" s="10" t="inlineStr">
@@ -3868,7 +3873,7 @@
       </c>
       <c r="D28" s="10" t="inlineStr">
         <is>
-          <t>Boundaries / admin units</t>
+          <t>Ecosystem services</t>
         </is>
       </c>
       <c r="E28" s="10" t="inlineStr">
@@ -3878,15 +3883,19 @@
       </c>
       <c r="F28" s="10" t="inlineStr">
         <is>
-          <t>Vector</t>
+          <t>Tabular</t>
         </is>
       </c>
       <c r="G28" s="10" t="inlineStr">
         <is>
-          <t>Admin - MFLLs Boundary</t>
-        </is>
-      </c>
-      <c r="H28" s="10" t="n"/>
+          <t>Ward level</t>
+        </is>
+      </c>
+      <c r="H28" s="10" t="inlineStr">
+        <is>
+          <t>2025 -2026</t>
+        </is>
+      </c>
       <c r="I28" s="10" t="inlineStr">
         <is>
           <t>CIMMYT</t>
@@ -3899,17 +3908,17 @@
       </c>
       <c r="K28" s="10" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Restricted</t>
         </is>
       </c>
       <c r="L28" s="10" t="inlineStr">
         <is>
-          <t>Restricted — GADM terms (academic/non-commercial use only, no redistribution)</t>
+          <t>CGIAR Open Access</t>
         </is>
       </c>
       <c r="M28" s="10" t="inlineStr">
         <is>
-          <t>Validated</t>
+          <t>Raw</t>
         </is>
       </c>
       <c r="N28" s="10" t="n"/>
@@ -3922,19 +3931,23 @@
       <c r="Q28" s="10" t="n"/>
       <c r="R28" s="11" t="inlineStr">
         <is>
-          <t>Administrative boundaries for the Lower Zambezi Valley (Districts and wards)</t>
+          <t>Ward-level crop damage data (severity and incidence) by different species — Original landscape entry: Mbire: Wards 2, 3, 9, 12 and 17</t>
         </is>
       </c>
       <c r="S28" s="10" t="n"/>
-      <c r="T28" s="10" t="n"/>
+      <c r="T28" s="10" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
       <c r="U28" s="10" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Seasonal</t>
         </is>
       </c>
       <c r="V28" s="10" t="inlineStr">
         <is>
-          <t>https://gadm.org/</t>
+          <t>Internal Available on request</t>
         </is>
       </c>
       <c r="W28" s="10" t="n"/>
@@ -3942,12 +3955,12 @@
     <row r="29">
       <c r="A29" s="8" t="inlineStr">
         <is>
-          <t>MFL-2026-027</t>
+          <t>MFL-2026-026</t>
         </is>
       </c>
       <c r="B29" s="8" t="inlineStr">
         <is>
-          <t>LULC classification</t>
+          <t>District/ward boundaries</t>
         </is>
       </c>
       <c r="C29" s="8" t="inlineStr">
@@ -3957,7 +3970,7 @@
       </c>
       <c r="D29" s="8" t="inlineStr">
         <is>
-          <t>Land cover / land use</t>
+          <t>Boundaries / admin units</t>
         </is>
       </c>
       <c r="E29" s="8" t="inlineStr">
@@ -3967,19 +3980,15 @@
       </c>
       <c r="F29" s="8" t="inlineStr">
         <is>
-          <t>Raster</t>
+          <t>Vector</t>
         </is>
       </c>
       <c r="G29" s="8" t="inlineStr">
         <is>
-          <t>10m</t>
-        </is>
-      </c>
-      <c r="H29" s="8" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
+          <t>Admin - MFLLs Boundary</t>
+        </is>
+      </c>
+      <c r="H29" s="8" t="n"/>
       <c r="I29" s="8" t="inlineStr">
         <is>
           <t>CIMMYT</t>
@@ -3992,12 +4001,12 @@
       </c>
       <c r="K29" s="8" t="inlineStr">
         <is>
-          <t>Restricted</t>
+          <t>Open</t>
         </is>
       </c>
       <c r="L29" s="8" t="inlineStr">
         <is>
-          <t>CGIAR Open Access</t>
+          <t>Restricted — GADM terms (academic/non-commercial use only, no redistribution)</t>
         </is>
       </c>
       <c r="M29" s="8" t="inlineStr">
@@ -4015,23 +4024,19 @@
       <c r="Q29" s="8" t="n"/>
       <c r="R29" s="9" t="inlineStr">
         <is>
-          <t>Land Use and Land Cover Classification — Original landscape entry: Mbire: Wards 2, 3, 9, 12 and 17</t>
+          <t>Administrative boundaries for the Lower Zambezi Valley (Districts and wards)</t>
         </is>
       </c>
       <c r="S29" s="8" t="n"/>
-      <c r="T29" s="8" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
+      <c r="T29" s="8" t="n"/>
       <c r="U29" s="8" t="inlineStr">
         <is>
-          <t>Static</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="V29" s="8" t="inlineStr">
         <is>
-          <t>Internal Available on request</t>
+          <t>https://gadm.org/</t>
         </is>
       </c>
       <c r="W29" s="8" t="n"/>
@@ -4039,12 +4044,12 @@
     <row r="30">
       <c r="A30" s="10" t="inlineStr">
         <is>
-          <t>MFL-2026-028</t>
+          <t>MFL-2026-027</t>
         </is>
       </c>
       <c r="B30" s="10" t="inlineStr">
         <is>
-          <t>LULC classification training points</t>
+          <t>LULC classification</t>
         </is>
       </c>
       <c r="C30" s="10" t="inlineStr">
@@ -4064,7 +4069,7 @@
       </c>
       <c r="F30" s="10" t="inlineStr">
         <is>
-          <t>Tabular</t>
+          <t>Raster</t>
         </is>
       </c>
       <c r="G30" s="10" t="inlineStr">
@@ -4112,7 +4117,7 @@
       <c r="Q30" s="10" t="n"/>
       <c r="R30" s="11" t="inlineStr">
         <is>
-          <t>Land Use and Land Cover Classification training points from Sentinel 2 — Original landscape entry: Mbire: Wards 2, 3, 9, 12 and 17</t>
+          <t>Land Use and Land Cover Classification — Original landscape entry: Mbire: Wards 2, 3, 9, 12 and 17</t>
         </is>
       </c>
       <c r="S30" s="10" t="n"/>
@@ -4136,12 +4141,12 @@
     <row r="31">
       <c r="A31" s="8" t="inlineStr">
         <is>
-          <t>MFL-2026-029</t>
+          <t>MFL-2026-028</t>
         </is>
       </c>
       <c r="B31" s="8" t="inlineStr">
         <is>
-          <t>Ecosystem services mapping</t>
+          <t>LULC classification training points</t>
         </is>
       </c>
       <c r="C31" s="8" t="inlineStr">
@@ -4151,7 +4156,7 @@
       </c>
       <c r="D31" s="8" t="inlineStr">
         <is>
-          <t>Ecosystem services</t>
+          <t>Land cover / land use</t>
         </is>
       </c>
       <c r="E31" s="8" t="inlineStr">
@@ -4161,10 +4166,14 @@
       </c>
       <c r="F31" s="8" t="inlineStr">
         <is>
-          <t>Mixed</t>
-        </is>
-      </c>
-      <c r="G31" s="8" t="n"/>
+          <t>Tabular</t>
+        </is>
+      </c>
+      <c r="G31" s="8" t="inlineStr">
+        <is>
+          <t>10m</t>
+        </is>
+      </c>
       <c r="H31" s="8" t="inlineStr">
         <is>
           <t>2026</t>
@@ -4172,7 +4181,7 @@
       </c>
       <c r="I31" s="8" t="inlineStr">
         <is>
-          <t>IWMI</t>
+          <t>CIMMYT</t>
         </is>
       </c>
       <c r="J31" s="8" t="inlineStr">
@@ -4192,7 +4201,7 @@
       </c>
       <c r="M31" s="8" t="inlineStr">
         <is>
-          <t>Processed</t>
+          <t>Validated</t>
         </is>
       </c>
       <c r="N31" s="8" t="n"/>
@@ -4205,7 +4214,7 @@
       <c r="Q31" s="8" t="n"/>
       <c r="R31" s="9" t="inlineStr">
         <is>
-          <t>Ward-level ecosystem services mapping — Original landscape entry: Mbire Ward 2</t>
+          <t>Land Use and Land Cover Classification training points from Sentinel 2 — Original landscape entry: Mbire: Wards 2, 3, 9, 12 and 17</t>
         </is>
       </c>
       <c r="S31" s="8" t="n"/>
@@ -4216,7 +4225,7 @@
       </c>
       <c r="U31" s="8" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Static</t>
         </is>
       </c>
       <c r="V31" s="8" t="inlineStr">
@@ -4229,52 +4238,48 @@
     <row r="32">
       <c r="A32" s="10" t="inlineStr">
         <is>
-          <t>MFL-2026-030</t>
+          <t>MFL-2026-029</t>
         </is>
       </c>
       <c r="B32" s="10" t="inlineStr">
         <is>
-          <t>Tunisia LLs Governorate boundary for Le Kef and Siliana.</t>
+          <t>Ecosystem services mapping</t>
         </is>
       </c>
       <c r="C32" s="10" t="inlineStr">
         <is>
-          <t>Tunisia</t>
+          <t>Zimbabwe</t>
         </is>
       </c>
       <c r="D32" s="10" t="inlineStr">
         <is>
-          <t>Boundaries / admin units</t>
+          <t>Ecosystem services</t>
         </is>
       </c>
       <c r="E32" s="10" t="inlineStr">
         <is>
-          <t>TUN-NW — Northwestern Tunisia</t>
+          <t>ZWE-MB — Mbire – Lower Zambezi Valley</t>
         </is>
       </c>
       <c r="F32" s="10" t="inlineStr">
         <is>
-          <t>Vector</t>
-        </is>
-      </c>
-      <c r="G32" s="10" t="inlineStr">
-        <is>
-          <t>admin-level-1</t>
-        </is>
-      </c>
+          <t>Mixed</t>
+        </is>
+      </c>
+      <c r="G32" s="10" t="n"/>
       <c r="H32" s="10" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="I32" s="10" t="inlineStr">
         <is>
-          <t>ICARDA</t>
+          <t>IWMI</t>
         </is>
       </c>
       <c r="J32" s="10" t="inlineStr">
         <is>
-          <t>Layal Atassi - l.atassi@cgiar.org</t>
+          <t>Telma.SIBANDA@um6p.ma</t>
         </is>
       </c>
       <c r="K32" s="10" t="inlineStr">
@@ -4289,53 +4294,49 @@
       </c>
       <c r="M32" s="10" t="inlineStr">
         <is>
-          <t>Validated</t>
-        </is>
-      </c>
-      <c r="N32" s="10" t="inlineStr">
-        <is>
-          <t>Tunisia_Governorate.shp (complete shapefile set, 8 files)</t>
-        </is>
-      </c>
+          <t>Processed</t>
+        </is>
+      </c>
+      <c r="N32" s="10" t="n"/>
       <c r="O32" s="10" t="inlineStr">
         <is>
           <t>Drive</t>
         </is>
       </c>
       <c r="P32" s="10" t="n"/>
-      <c r="Q32" s="10" t="inlineStr">
-        <is>
-          <t>MOSAIC/datasets/MFL-2026-030/raw/</t>
-        </is>
-      </c>
+      <c r="Q32" s="10" t="n"/>
       <c r="R32" s="11" t="inlineStr">
         <is>
-          <t>Administrative boundaries for Tunisia</t>
+          <t>Ward-level ecosystem services mapping — Original landscape entry: Mbire Ward 2</t>
         </is>
       </c>
       <c r="S32" s="10" t="n"/>
-      <c r="T32" s="10" t="n"/>
-      <c r="U32" s="10" t="n"/>
+      <c r="T32" s="10" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="U32" s="10" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
       <c r="V32" s="10" t="inlineStr">
         <is>
-          <t>www.geoboundaries.org</t>
-        </is>
-      </c>
-      <c r="W32" s="10" t="inlineStr">
-        <is>
-          <t>571 KB</t>
-        </is>
-      </c>
+          <t>Internal Available on request</t>
+        </is>
+      </c>
+      <c r="W32" s="10" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="8" t="inlineStr">
         <is>
-          <t>MFL-2026-031</t>
+          <t>MFL-2026-030</t>
         </is>
       </c>
       <c r="B33" s="8" t="inlineStr">
         <is>
-          <t>Tunisia LLs Sector boundary containing Es Sers, Gaafour, El Krib, Makthar, and Kesra.</t>
+          <t>Tunisia LLs Governorate boundary for Le Kef and Siliana.</t>
         </is>
       </c>
       <c r="C33" s="8" t="inlineStr">
@@ -4360,7 +4361,7 @@
       </c>
       <c r="G33" s="8" t="inlineStr">
         <is>
-          <t>admin-level-2</t>
+          <t>admin-level-1</t>
         </is>
       </c>
       <c r="H33" s="8" t="inlineStr">
@@ -4395,7 +4396,7 @@
       </c>
       <c r="N33" s="8" t="inlineStr">
         <is>
-          <t>Tunisia_Sector.shp (complete shapefile set, 8 files)</t>
+          <t>Tunisia_Governorate.shp (complete shapefile set, 8 files)</t>
         </is>
       </c>
       <c r="O33" s="8" t="inlineStr">
@@ -4406,7 +4407,7 @@
       <c r="P33" s="8" t="n"/>
       <c r="Q33" s="8" t="inlineStr">
         <is>
-          <t>MOSAIC/datasets/MFL-2026-031/raw/</t>
+          <t>MOSAIC/datasets/MFL-2026-030/raw/</t>
         </is>
       </c>
       <c r="R33" s="9" t="inlineStr">
@@ -4424,19 +4425,19 @@
       </c>
       <c r="W33" s="8" t="inlineStr">
         <is>
-          <t>692 KB</t>
+          <t>571 KB</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="10" t="inlineStr">
         <is>
-          <t>MFL-2026-032</t>
+          <t>MFL-2026-031</t>
         </is>
       </c>
       <c r="B34" s="10" t="inlineStr">
         <is>
-          <t>Tunisia LLs boundary for the six communities containing Sers, Elles, El Ahouez Sud, Hammam Biadha Sud, Chouarnia, and Kesra.</t>
+          <t>Tunisia LLs Sector boundary containing Es Sers, Gaafour, El Krib, Makthar, and Kesra.</t>
         </is>
       </c>
       <c r="C34" s="10" t="inlineStr">
@@ -4461,7 +4462,7 @@
       </c>
       <c r="G34" s="10" t="inlineStr">
         <is>
-          <t>admin-level-3</t>
+          <t>admin-level-2</t>
         </is>
       </c>
       <c r="H34" s="10" t="inlineStr">
@@ -4496,7 +4497,7 @@
       </c>
       <c r="N34" s="10" t="inlineStr">
         <is>
-          <t>Tunisia_ALL.shp (complete shapefile set, 8 files)</t>
+          <t>Tunisia_Sector.shp (complete shapefile set, 8 files)</t>
         </is>
       </c>
       <c r="O34" s="10" t="inlineStr">
@@ -4507,7 +4508,7 @@
       <c r="P34" s="10" t="n"/>
       <c r="Q34" s="10" t="inlineStr">
         <is>
-          <t>MOSAIC/datasets/MFL-2026-032/raw/</t>
+          <t>MOSAIC/datasets/MFL-2026-031/raw/</t>
         </is>
       </c>
       <c r="R34" s="11" t="inlineStr">
@@ -4525,19 +4526,19 @@
       </c>
       <c r="W34" s="10" t="inlineStr">
         <is>
-          <t>723 KB</t>
+          <t>692 KB</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="8" t="inlineStr">
         <is>
-          <t>MFL-2026-033</t>
+          <t>MFL-2026-032</t>
         </is>
       </c>
       <c r="B35" s="8" t="inlineStr">
         <is>
-          <t>Tunisia Land use land cover for Le Kef and Siliana.</t>
+          <t>Tunisia LLs boundary for the six communities containing Sers, Elles, El Ahouez Sud, Hammam Biadha Sud, Chouarnia, and Kesra.</t>
         </is>
       </c>
       <c r="C35" s="8" t="inlineStr">
@@ -4547,7 +4548,7 @@
       </c>
       <c r="D35" s="8" t="inlineStr">
         <is>
-          <t>Land cover / land use</t>
+          <t>Boundaries / admin units</t>
         </is>
       </c>
       <c r="E35" s="8" t="inlineStr">
@@ -4562,12 +4563,12 @@
       </c>
       <c r="G35" s="8" t="inlineStr">
         <is>
-          <t>10 m</t>
+          <t>admin-level-3</t>
         </is>
       </c>
       <c r="H35" s="8" t="inlineStr">
         <is>
-          <t>2021</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="I35" s="8" t="inlineStr">
@@ -4577,7 +4578,7 @@
       </c>
       <c r="J35" s="8" t="inlineStr">
         <is>
-          <t>Ayman Frija -  a.frija@cgiar.org</t>
+          <t>Layal Atassi - l.atassi@cgiar.org</t>
         </is>
       </c>
       <c r="K35" s="8" t="inlineStr">
@@ -4595,42 +4596,50 @@
           <t>Validated</t>
         </is>
       </c>
-      <c r="N35" s="8" t="n"/>
+      <c r="N35" s="8" t="inlineStr">
+        <is>
+          <t>Tunisia_ALL.shp (complete shapefile set, 8 files)</t>
+        </is>
+      </c>
       <c r="O35" s="8" t="inlineStr">
         <is>
           <t>Drive</t>
         </is>
       </c>
       <c r="P35" s="8" t="n"/>
-      <c r="Q35" s="8" t="n"/>
+      <c r="Q35" s="8" t="inlineStr">
+        <is>
+          <t>MOSAIC/datasets/MFL-2026-032/raw/</t>
+        </is>
+      </c>
       <c r="R35" s="9" t="inlineStr">
         <is>
-          <t>Land Use and Land Cover Classification</t>
+          <t>Administrative boundaries for Tunisia</t>
         </is>
       </c>
       <c r="S35" s="8" t="n"/>
-      <c r="T35" s="8" t="inlineStr">
-        <is>
-          <t>2021</t>
-        </is>
-      </c>
+      <c r="T35" s="8" t="n"/>
       <c r="U35" s="8" t="n"/>
       <c r="V35" s="8" t="inlineStr">
         <is>
-          <t>Internal Available on request</t>
-        </is>
-      </c>
-      <c r="W35" s="8" t="n"/>
+          <t>www.geoboundaries.org</t>
+        </is>
+      </c>
+      <c r="W35" s="8" t="inlineStr">
+        <is>
+          <t>723 KB</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="10" t="inlineStr">
         <is>
-          <t>MFL-2026-034</t>
+          <t>MFL-2026-033</t>
         </is>
       </c>
       <c r="B36" s="10" t="inlineStr">
         <is>
-          <t>Tunisia Agricultural soil for Le Kef and Siliana.</t>
+          <t>Tunisia Land use land cover for Le Kef and Siliana.</t>
         </is>
       </c>
       <c r="C36" s="10" t="inlineStr">
@@ -4640,7 +4649,7 @@
       </c>
       <c r="D36" s="10" t="inlineStr">
         <is>
-          <t>Degradation / land health</t>
+          <t>Land cover / land use</t>
         </is>
       </c>
       <c r="E36" s="10" t="inlineStr">
@@ -4653,7 +4662,11 @@
           <t>Vector</t>
         </is>
       </c>
-      <c r="G36" s="10" t="n"/>
+      <c r="G36" s="10" t="inlineStr">
+        <is>
+          <t>10 m</t>
+        </is>
+      </c>
       <c r="H36" s="10" t="inlineStr">
         <is>
           <t>2021</t>
@@ -4694,7 +4707,7 @@
       <c r="Q36" s="10" t="n"/>
       <c r="R36" s="11" t="inlineStr">
         <is>
-          <t>Agricultural soil map classification</t>
+          <t>Land Use and Land Cover Classification</t>
         </is>
       </c>
       <c r="S36" s="10" t="n"/>
@@ -4714,12 +4727,12 @@
     <row r="37">
       <c r="A37" s="8" t="inlineStr">
         <is>
-          <t>MFL-2026-035</t>
+          <t>MFL-2026-034</t>
         </is>
       </c>
       <c r="B37" s="8" t="inlineStr">
         <is>
-          <t>Agroecological and socioeconomic datasets</t>
+          <t>Tunisia Agricultural soil for Le Kef and Siliana.</t>
         </is>
       </c>
       <c r="C37" s="8" t="inlineStr">
@@ -4729,7 +4742,7 @@
       </c>
       <c r="D37" s="8" t="inlineStr">
         <is>
-          <t>Socio-economic / livelihoods</t>
+          <t>Degradation / land health</t>
         </is>
       </c>
       <c r="E37" s="8" t="inlineStr">
@@ -4739,13 +4752,13 @@
       </c>
       <c r="F37" s="8" t="inlineStr">
         <is>
-          <t>Tabular</t>
+          <t>Vector</t>
         </is>
       </c>
       <c r="G37" s="8" t="n"/>
       <c r="H37" s="8" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2021</t>
         </is>
       </c>
       <c r="I37" s="8" t="inlineStr">
@@ -4758,9 +4771,21 @@
           <t>Ayman Frija -  a.frija@cgiar.org</t>
         </is>
       </c>
-      <c r="K37" s="8" t="n"/>
-      <c r="L37" s="8" t="n"/>
-      <c r="M37" s="8" t="n"/>
+      <c r="K37" s="8" t="inlineStr">
+        <is>
+          <t>Restricted</t>
+        </is>
+      </c>
+      <c r="L37" s="8" t="inlineStr">
+        <is>
+          <t>CGIAR Open Access</t>
+        </is>
+      </c>
+      <c r="M37" s="8" t="inlineStr">
+        <is>
+          <t>Validated</t>
+        </is>
+      </c>
       <c r="N37" s="8" t="n"/>
       <c r="O37" s="8" t="inlineStr">
         <is>
@@ -4771,16 +4796,16 @@
       <c r="Q37" s="8" t="n"/>
       <c r="R37" s="9" t="inlineStr">
         <is>
-          <t>Survay collecting evidence of the holistic impact of agroecology</t>
+          <t>Agricultural soil map classification</t>
         </is>
       </c>
       <c r="S37" s="8" t="n"/>
-      <c r="T37" s="8" t="n"/>
-      <c r="U37" s="8" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="T37" s="8" t="inlineStr">
+        <is>
+          <t>2021</t>
+        </is>
+      </c>
+      <c r="U37" s="8" t="n"/>
       <c r="V37" s="8" t="inlineStr">
         <is>
           <t>Internal Available on request</t>
@@ -4791,17 +4816,17 @@
     <row r="38">
       <c r="A38" s="10" t="inlineStr">
         <is>
-          <t>MFL-2026-036</t>
+          <t>MFL-2026-035</t>
         </is>
       </c>
       <c r="B38" s="10" t="inlineStr">
         <is>
-          <t>Agricultural production system</t>
+          <t>Agroecological and socioeconomic datasets</t>
         </is>
       </c>
       <c r="C38" s="10" t="inlineStr">
         <is>
-          <t>Ethiopia</t>
+          <t>Tunisia</t>
         </is>
       </c>
       <c r="D38" s="10" t="inlineStr">
@@ -4811,45 +4836,33 @@
       </c>
       <c r="E38" s="10" t="inlineStr">
         <is>
-          <t>ETH-OG — Omo-Gibe Basin</t>
+          <t>TUN-NW — Northwestern Tunisia</t>
         </is>
       </c>
       <c r="F38" s="10" t="inlineStr">
         <is>
-          <t>Vector</t>
+          <t>Tabular</t>
         </is>
       </c>
       <c r="G38" s="10" t="n"/>
       <c r="H38" s="10" t="inlineStr">
         <is>
-          <t>2018</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="I38" s="10" t="inlineStr">
         <is>
-          <t>NASA / USGS (external)</t>
+          <t>ICARDA</t>
         </is>
       </c>
       <c r="J38" s="10" t="inlineStr">
         <is>
-          <t>Degefie Tibebe- d.tibebe@cgiar.org</t>
-        </is>
-      </c>
-      <c r="K38" s="10" t="inlineStr">
-        <is>
-          <t>Restricted</t>
-        </is>
-      </c>
-      <c r="L38" s="10" t="inlineStr">
-        <is>
-          <t>Restricted — contact data owner</t>
-        </is>
-      </c>
-      <c r="M38" s="10" t="inlineStr">
-        <is>
-          <t>Raw</t>
-        </is>
-      </c>
+          <t>Ayman Frija -  a.frija@cgiar.org</t>
+        </is>
+      </c>
+      <c r="K38" s="10" t="n"/>
+      <c r="L38" s="10" t="n"/>
+      <c r="M38" s="10" t="n"/>
       <c r="N38" s="10" t="n"/>
       <c r="O38" s="10" t="inlineStr">
         <is>
@@ -4860,12 +4873,16 @@
       <c r="Q38" s="10" t="n"/>
       <c r="R38" s="11" t="inlineStr">
         <is>
-          <t>Survey</t>
+          <t>Survay collecting evidence of the holistic impact of agroecology</t>
         </is>
       </c>
       <c r="S38" s="10" t="n"/>
       <c r="T38" s="10" t="n"/>
-      <c r="U38" s="10" t="n"/>
+      <c r="U38" s="10" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
       <c r="V38" s="10" t="inlineStr">
         <is>
           <t>Internal Available on request</t>
@@ -4876,12 +4893,12 @@
     <row r="39">
       <c r="A39" s="8" t="inlineStr">
         <is>
-          <t>MFL-2026-037</t>
+          <t>MFL-2026-036</t>
         </is>
       </c>
       <c r="B39" s="8" t="inlineStr">
         <is>
-          <t>Land use/cover</t>
+          <t>Agricultural production system</t>
         </is>
       </c>
       <c r="C39" s="8" t="inlineStr">
@@ -4891,7 +4908,7 @@
       </c>
       <c r="D39" s="8" t="inlineStr">
         <is>
-          <t>Land cover / land use</t>
+          <t>Socio-economic / livelihoods</t>
         </is>
       </c>
       <c r="E39" s="8" t="inlineStr">
@@ -4901,20 +4918,20 @@
       </c>
       <c r="F39" s="8" t="inlineStr">
         <is>
-          <t>Raster</t>
-        </is>
-      </c>
-      <c r="G39" s="8" t="inlineStr">
-        <is>
-          <t>30 m</t>
-        </is>
-      </c>
+          <t>Vector</t>
+        </is>
+      </c>
+      <c r="G39" s="8" t="n"/>
       <c r="H39" s="8" t="inlineStr">
         <is>
-          <t>2021</t>
-        </is>
-      </c>
-      <c r="I39" s="8" t="n"/>
+          <t>2018</t>
+        </is>
+      </c>
+      <c r="I39" s="8" t="inlineStr">
+        <is>
+          <t>NASA / USGS (external)</t>
+        </is>
+      </c>
       <c r="J39" s="8" t="inlineStr">
         <is>
           <t>Degefie Tibebe- d.tibebe@cgiar.org</t>
@@ -4932,7 +4949,7 @@
       </c>
       <c r="M39" s="8" t="inlineStr">
         <is>
-          <t>Validated</t>
+          <t>Raw</t>
         </is>
       </c>
       <c r="N39" s="8" t="n"/>
@@ -4945,16 +4962,12 @@
       <c r="Q39" s="8" t="n"/>
       <c r="R39" s="9" t="inlineStr">
         <is>
-          <t>Land Use and Land Cover Classification</t>
+          <t>Survey</t>
         </is>
       </c>
       <c r="S39" s="8" t="n"/>
       <c r="T39" s="8" t="n"/>
-      <c r="U39" s="8" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="U39" s="8" t="n"/>
       <c r="V39" s="8" t="inlineStr">
         <is>
           <t>Internal Available on request</t>
@@ -4965,12 +4978,12 @@
     <row r="40">
       <c r="A40" s="10" t="inlineStr">
         <is>
-          <t>MFL-2026-038</t>
+          <t>MFL-2026-037</t>
         </is>
       </c>
       <c r="B40" s="10" t="inlineStr">
         <is>
-          <t>Soil resource</t>
+          <t>Land use/cover</t>
         </is>
       </c>
       <c r="C40" s="10" t="inlineStr">
@@ -4980,7 +4993,7 @@
       </c>
       <c r="D40" s="10" t="inlineStr">
         <is>
-          <t>Degradation / land health</t>
+          <t>Land cover / land use</t>
         </is>
       </c>
       <c r="E40" s="10" t="inlineStr">
@@ -4995,19 +5008,15 @@
       </c>
       <c r="G40" s="10" t="inlineStr">
         <is>
-          <t>250 m</t>
+          <t>30 m</t>
         </is>
       </c>
       <c r="H40" s="10" t="inlineStr">
         <is>
-          <t>2024</t>
-        </is>
-      </c>
-      <c r="I40" s="10" t="inlineStr">
-        <is>
-          <t>Alliance Bioversity-CIAT</t>
-        </is>
-      </c>
+          <t>2021</t>
+        </is>
+      </c>
+      <c r="I40" s="10" t="n"/>
       <c r="J40" s="10" t="inlineStr">
         <is>
           <t>Degefie Tibebe- d.tibebe@cgiar.org</t>
@@ -5038,7 +5047,7 @@
       <c r="Q40" s="10" t="n"/>
       <c r="R40" s="11" t="inlineStr">
         <is>
-          <t>Digital soil mapping</t>
+          <t>Land Use and Land Cover Classification</t>
         </is>
       </c>
       <c r="S40" s="10" t="n"/>
@@ -5058,12 +5067,12 @@
     <row r="41">
       <c r="A41" s="8" t="inlineStr">
         <is>
-          <t>MFL-2026-039</t>
+          <t>MFL-2026-038</t>
         </is>
       </c>
       <c r="B41" s="8" t="inlineStr">
         <is>
-          <t>District level crop area, production and yield data - Ethiopia</t>
+          <t>Soil resource</t>
         </is>
       </c>
       <c r="C41" s="8" t="inlineStr">
@@ -5073,7 +5082,7 @@
       </c>
       <c r="D41" s="8" t="inlineStr">
         <is>
-          <t>Agrobiodiversity / crops</t>
+          <t>Degradation / land health</t>
         </is>
       </c>
       <c r="E41" s="8" t="inlineStr">
@@ -5083,18 +5092,22 @@
       </c>
       <c r="F41" s="8" t="inlineStr">
         <is>
-          <t>Tabular</t>
-        </is>
-      </c>
-      <c r="G41" s="8" t="n"/>
+          <t>Raster</t>
+        </is>
+      </c>
+      <c r="G41" s="8" t="inlineStr">
+        <is>
+          <t>250 m</t>
+        </is>
+      </c>
       <c r="H41" s="8" t="inlineStr">
         <is>
-          <t>1991-2020</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="I41" s="8" t="inlineStr">
         <is>
-          <t>National government (external)</t>
+          <t>Alliance Bioversity-CIAT</t>
         </is>
       </c>
       <c r="J41" s="8" t="inlineStr">
@@ -5109,7 +5122,7 @@
       </c>
       <c r="L41" s="8" t="inlineStr">
         <is>
-          <t>CC BY 4.0</t>
+          <t>Restricted — contact data owner</t>
         </is>
       </c>
       <c r="M41" s="8" t="inlineStr">
@@ -5127,14 +5140,14 @@
       <c r="Q41" s="8" t="n"/>
       <c r="R41" s="9" t="inlineStr">
         <is>
-          <t>District level crop area, production and yield.</t>
+          <t>Digital soil mapping</t>
         </is>
       </c>
       <c r="S41" s="8" t="n"/>
       <c r="T41" s="8" t="n"/>
       <c r="U41" s="8" t="inlineStr">
         <is>
-          <t>Annual</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="V41" s="8" t="inlineStr">
@@ -5147,12 +5160,12 @@
     <row r="42">
       <c r="A42" s="10" t="inlineStr">
         <is>
-          <t>MFL-2026-040</t>
+          <t>MFL-2026-039</t>
         </is>
       </c>
       <c r="B42" s="10" t="inlineStr">
         <is>
-          <t>Agroecological zones</t>
+          <t>District level crop area, production and yield data - Ethiopia</t>
         </is>
       </c>
       <c r="C42" s="10" t="inlineStr">
@@ -5160,7 +5173,11 @@
           <t>Ethiopia</t>
         </is>
       </c>
-      <c r="D42" s="10" t="n"/>
+      <c r="D42" s="10" t="inlineStr">
+        <is>
+          <t>Agrobiodiversity / crops</t>
+        </is>
+      </c>
       <c r="E42" s="10" t="inlineStr">
         <is>
           <t>ETH-OG — Omo-Gibe Basin</t>
@@ -5168,13 +5185,13 @@
       </c>
       <c r="F42" s="10" t="inlineStr">
         <is>
-          <t>Vector</t>
+          <t>Tabular</t>
         </is>
       </c>
       <c r="G42" s="10" t="n"/>
       <c r="H42" s="10" t="inlineStr">
         <is>
-          <t>2005</t>
+          <t>1991-2020</t>
         </is>
       </c>
       <c r="I42" s="10" t="inlineStr">
@@ -5212,12 +5229,16 @@
       <c r="Q42" s="10" t="n"/>
       <c r="R42" s="11" t="inlineStr">
         <is>
-          <t>Agroecological zonations</t>
+          <t>District level crop area, production and yield.</t>
         </is>
       </c>
       <c r="S42" s="10" t="n"/>
       <c r="T42" s="10" t="n"/>
-      <c r="U42" s="10" t="n"/>
+      <c r="U42" s="10" t="inlineStr">
+        <is>
+          <t>Annual</t>
+        </is>
+      </c>
       <c r="V42" s="10" t="inlineStr">
         <is>
           <t>Internal Available on request</t>
@@ -5228,12 +5249,12 @@
     <row r="43">
       <c r="A43" s="8" t="inlineStr">
         <is>
-          <t>MFL-2026-041</t>
+          <t>MFL-2026-040</t>
         </is>
       </c>
       <c r="B43" s="8" t="inlineStr">
         <is>
-          <t>Experimental CSA practices</t>
+          <t>Agroecological zones</t>
         </is>
       </c>
       <c r="C43" s="8" t="inlineStr">
@@ -5241,11 +5262,7 @@
           <t>Ethiopia</t>
         </is>
       </c>
-      <c r="D43" s="8" t="inlineStr">
-        <is>
-          <t>Biodiversity / ecosystems</t>
-        </is>
-      </c>
+      <c r="D43" s="8" t="n"/>
       <c r="E43" s="8" t="inlineStr">
         <is>
           <t>ETH-OG — Omo-Gibe Basin</t>
@@ -5253,18 +5270,18 @@
       </c>
       <c r="F43" s="8" t="inlineStr">
         <is>
-          <t>Tabular</t>
+          <t>Vector</t>
         </is>
       </c>
       <c r="G43" s="8" t="n"/>
       <c r="H43" s="8" t="inlineStr">
         <is>
-          <t>2000-2020</t>
+          <t>2005</t>
         </is>
       </c>
       <c r="I43" s="8" t="inlineStr">
         <is>
-          <t>Alliance Bioversity-CIAT</t>
+          <t>National government (external)</t>
         </is>
       </c>
       <c r="J43" s="8" t="inlineStr">
@@ -5295,14 +5312,14 @@
       </c>
       <c r="P43" s="8" t="n"/>
       <c r="Q43" s="8" t="n"/>
-      <c r="R43" s="9" t="n"/>
+      <c r="R43" s="9" t="inlineStr">
+        <is>
+          <t>Agroecological zonations</t>
+        </is>
+      </c>
       <c r="S43" s="8" t="n"/>
       <c r="T43" s="8" t="n"/>
-      <c r="U43" s="8" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="U43" s="8" t="n"/>
       <c r="V43" s="8" t="inlineStr">
         <is>
           <t>Internal Available on request</t>
@@ -5313,12 +5330,12 @@
     <row r="44">
       <c r="A44" s="10" t="inlineStr">
         <is>
-          <t>MFL-2026-042</t>
+          <t>MFL-2026-041</t>
         </is>
       </c>
       <c r="B44" s="10" t="inlineStr">
         <is>
-          <t>Erosion map</t>
+          <t>Experimental CSA practices</t>
         </is>
       </c>
       <c r="C44" s="10" t="inlineStr">
@@ -5328,7 +5345,7 @@
       </c>
       <c r="D44" s="10" t="inlineStr">
         <is>
-          <t>Degradation / land health</t>
+          <t>Biodiversity / ecosystems</t>
         </is>
       </c>
       <c r="E44" s="10" t="inlineStr">
@@ -5338,18 +5355,18 @@
       </c>
       <c r="F44" s="10" t="inlineStr">
         <is>
-          <t>Raster</t>
+          <t>Tabular</t>
         </is>
       </c>
       <c r="G44" s="10" t="n"/>
       <c r="H44" s="10" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>2000-2020</t>
         </is>
       </c>
       <c r="I44" s="10" t="inlineStr">
         <is>
-          <t>National government (external)</t>
+          <t>Alliance Bioversity-CIAT</t>
         </is>
       </c>
       <c r="J44" s="10" t="inlineStr">
@@ -5380,16 +5397,12 @@
       </c>
       <c r="P44" s="10" t="n"/>
       <c r="Q44" s="10" t="n"/>
-      <c r="R44" s="11" t="inlineStr">
-        <is>
-          <t>Emprical modellling</t>
-        </is>
-      </c>
+      <c r="R44" s="11" t="n"/>
       <c r="S44" s="10" t="n"/>
       <c r="T44" s="10" t="n"/>
       <c r="U44" s="10" t="inlineStr">
         <is>
-          <t>Static</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="V44" s="10" t="inlineStr">
@@ -5402,62 +5415,58 @@
     <row r="45">
       <c r="A45" s="8" t="inlineStr">
         <is>
-          <t>MFL-2026-044</t>
+          <t>MFL-2026-042</t>
         </is>
       </c>
       <c r="B45" s="8" t="inlineStr">
         <is>
-          <t>District/Region boundaries</t>
+          <t>Erosion map</t>
         </is>
       </c>
       <c r="C45" s="8" t="inlineStr">
         <is>
-          <t>Côte d'Ivoire</t>
+          <t>Ethiopia</t>
         </is>
       </c>
       <c r="D45" s="8" t="inlineStr">
         <is>
-          <t>Boundaries / admin units</t>
+          <t>Degradation / land health</t>
         </is>
       </c>
       <c r="E45" s="8" t="inlineStr">
         <is>
-          <t>CIV-NZ — N'Zi Watershed</t>
+          <t>ETH-OG — Omo-Gibe Basin</t>
         </is>
       </c>
       <c r="F45" s="8" t="inlineStr">
         <is>
-          <t>Vector</t>
-        </is>
-      </c>
-      <c r="G45" s="8" t="inlineStr">
-        <is>
-          <t>admin-level-0 to admin-level-4 (GADM 4.1)</t>
-        </is>
-      </c>
+          <t>Raster</t>
+        </is>
+      </c>
+      <c r="G45" s="8" t="n"/>
       <c r="H45" s="8" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="I45" s="8" t="inlineStr">
         <is>
-          <t>AfricaRice</t>
+          <t>National government (external)</t>
         </is>
       </c>
       <c r="J45" s="8" t="inlineStr">
         <is>
-          <t>Louis Kouadio (a.kouadio2@cgiar.org)</t>
+          <t>Degefie Tibebe- d.tibebe@cgiar.org</t>
         </is>
       </c>
       <c r="K45" s="8" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Restricted</t>
         </is>
       </c>
       <c r="L45" s="8" t="inlineStr">
         <is>
-          <t>Restricted — GADM terms (academic/non-commercial use only, no redistribution)</t>
+          <t>CC BY 4.0</t>
         </is>
       </c>
       <c r="M45" s="8" t="inlineStr">
@@ -5465,58 +5474,42 @@
           <t>Validated</t>
         </is>
       </c>
-      <c r="N45" s="8" t="inlineStr">
-        <is>
-          <t>gadm41_CIV_0.shp; gadm41_CIV_1.shp; gadm41_CIV_2.shp; gadm41_CIV_3.shp; gadm41_CIV_4.shp (five complete shapefile sets, 25 files)</t>
-        </is>
-      </c>
+      <c r="N45" s="8" t="n"/>
       <c r="O45" s="8" t="inlineStr">
         <is>
           <t>Drive</t>
         </is>
       </c>
       <c r="P45" s="8" t="n"/>
-      <c r="Q45" s="8" t="inlineStr">
-        <is>
-          <t>MOSAIC/datasets/MFL-2026-044/raw/</t>
-        </is>
-      </c>
+      <c r="Q45" s="8" t="n"/>
       <c r="R45" s="9" t="inlineStr">
         <is>
-          <t>GADM 4.1 administrative boundaries for Côte d'Ivoire, levels 0 to 4: the country; 12 districts and 2 autonomous districts; 31 regions plus the 2 autonomous districts; 113 departments; and 191 sub-prefectures. Country-wide, not clipped to the N'Zi landscape. Unmodified from GADM; download from gadm.org. GADM's licence does not allow redistribution, so MOSAIC keeps only an internal quality-control copy.</t>
+          <t>Emprical modellling</t>
         </is>
       </c>
       <c r="S45" s="8" t="n"/>
-      <c r="T45" s="8" t="inlineStr">
-        <is>
-          <t>2022</t>
-        </is>
-      </c>
+      <c r="T45" s="8" t="n"/>
       <c r="U45" s="8" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Static</t>
         </is>
       </c>
       <c r="V45" s="8" t="inlineStr">
         <is>
-          <t>https://gadm.org/download_country.html</t>
-        </is>
-      </c>
-      <c r="W45" s="8" t="inlineStr">
-        <is>
-          <t>3.5 MB</t>
-        </is>
-      </c>
+          <t>Internal Available on request</t>
+        </is>
+      </c>
+      <c r="W45" s="8" t="n"/>
     </row>
     <row r="46">
       <c r="A46" s="10" t="inlineStr">
         <is>
-          <t>MFL-2026-045</t>
+          <t>MFL-2026-044</t>
         </is>
       </c>
       <c r="B46" s="10" t="inlineStr">
         <is>
-          <t>Agroecological zones</t>
+          <t>District/Region boundaries</t>
         </is>
       </c>
       <c r="C46" s="10" t="inlineStr">
@@ -5524,7 +5517,11 @@
           <t>Côte d'Ivoire</t>
         </is>
       </c>
-      <c r="D46" s="10" t="n"/>
+      <c r="D46" s="10" t="inlineStr">
+        <is>
+          <t>Boundaries / admin units</t>
+        </is>
+      </c>
       <c r="E46" s="10" t="inlineStr">
         <is>
           <t>CIV-NZ — N'Zi Watershed</t>
@@ -5532,23 +5529,27 @@
       </c>
       <c r="F46" s="10" t="inlineStr">
         <is>
-          <t>Raster</t>
-        </is>
-      </c>
-      <c r="G46" s="10" t="n"/>
+          <t>Vector</t>
+        </is>
+      </c>
+      <c r="G46" s="10" t="inlineStr">
+        <is>
+          <t>admin-level-0 to admin-level-4 (GADM 4.1)</t>
+        </is>
+      </c>
       <c r="H46" s="10" t="inlineStr">
         <is>
-          <t>2017</t>
+          <t>2022</t>
         </is>
       </c>
       <c r="I46" s="10" t="inlineStr">
         <is>
-          <t>IFPRI</t>
+          <t>AfricaRice</t>
         </is>
       </c>
       <c r="J46" s="10" t="inlineStr">
         <is>
-          <t>Justin Djagba (j.djagba@cgiar.org)</t>
+          <t>Louis Kouadio (a.kouadio2@cgiar.org)</t>
         </is>
       </c>
       <c r="K46" s="10" t="inlineStr">
@@ -5558,7 +5559,7 @@
       </c>
       <c r="L46" s="10" t="inlineStr">
         <is>
-          <t>Other (specify in notes)</t>
+          <t>Restricted — GADM terms (academic/non-commercial use only, no redistribution)</t>
         </is>
       </c>
       <c r="M46" s="10" t="inlineStr">
@@ -5566,46 +5567,58 @@
           <t>Validated</t>
         </is>
       </c>
-      <c r="N46" s="10" t="n"/>
+      <c r="N46" s="10" t="inlineStr">
+        <is>
+          <t>gadm41_CIV_0.shp; gadm41_CIV_1.shp; gadm41_CIV_2.shp; gadm41_CIV_3.shp; gadm41_CIV_4.shp (five complete shapefile sets, 25 files)</t>
+        </is>
+      </c>
       <c r="O46" s="10" t="inlineStr">
         <is>
           <t>Drive</t>
         </is>
       </c>
       <c r="P46" s="10" t="n"/>
-      <c r="Q46" s="10" t="n"/>
+      <c r="Q46" s="10" t="inlineStr">
+        <is>
+          <t>MOSAIC/datasets/MFL-2026-044/raw/</t>
+        </is>
+      </c>
       <c r="R46" s="11" t="inlineStr">
         <is>
-          <t>Agroecological zones</t>
+          <t>GADM 4.1 administrative boundaries for Côte d'Ivoire, levels 0 to 4: the country; 12 districts and 2 autonomous districts; 31 regions plus the 2 autonomous districts; 113 departments; and 191 sub-prefectures. Country-wide, not clipped to the N'Zi landscape. Unmodified from GADM; download from gadm.org. GADM's licence does not allow redistribution, so MOSAIC keeps only an internal quality-control copy.</t>
         </is>
       </c>
       <c r="S46" s="10" t="n"/>
       <c r="T46" s="10" t="inlineStr">
         <is>
-          <t>2017</t>
+          <t>2022</t>
         </is>
       </c>
       <c r="U46" s="10" t="inlineStr">
         <is>
-          <t>Static</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="V46" s="10" t="inlineStr">
         <is>
-          <t>HarvestChoice, International Food Policy Research Institute (IFPRI); University of Minnesota, 2017, "CELL5M: A Multidisciplinary Geospatial Database for Africa South of the Sahara", https://doi.org/10.7910/DVN/G4TBLF, Harvard Dataverse, V5</t>
-        </is>
-      </c>
-      <c r="W46" s="10" t="n"/>
+          <t>https://gadm.org/download_country.html</t>
+        </is>
+      </c>
+      <c r="W46" s="10" t="inlineStr">
+        <is>
+          <t>3.5 MB</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="8" t="inlineStr">
         <is>
-          <t>MFL-2026-046</t>
+          <t>MFL-2026-045</t>
         </is>
       </c>
       <c r="B47" s="8" t="inlineStr">
         <is>
-          <t>Climate station data (NHMS synoptic stations)</t>
+          <t>Agroecological zones</t>
         </is>
       </c>
       <c r="C47" s="8" t="inlineStr">
@@ -5613,11 +5626,7 @@
           <t>Côte d'Ivoire</t>
         </is>
       </c>
-      <c r="D47" s="8" t="inlineStr">
-        <is>
-          <t>Water / hydrology</t>
-        </is>
-      </c>
+      <c r="D47" s="8" t="n"/>
       <c r="E47" s="8" t="inlineStr">
         <is>
           <t>CIV-NZ — N'Zi Watershed</t>
@@ -5625,27 +5634,23 @@
       </c>
       <c r="F47" s="8" t="inlineStr">
         <is>
-          <t>Tabular</t>
-        </is>
-      </c>
-      <c r="G47" s="8" t="inlineStr">
-        <is>
-          <t>Climate station observations</t>
-        </is>
-      </c>
+          <t>Raster</t>
+        </is>
+      </c>
+      <c r="G47" s="8" t="n"/>
       <c r="H47" s="8" t="inlineStr">
         <is>
-          <t>1980-2010</t>
+          <t>2017</t>
         </is>
       </c>
       <c r="I47" s="8" t="inlineStr">
         <is>
-          <t>AfricaRice</t>
+          <t>IFPRI</t>
         </is>
       </c>
       <c r="J47" s="8" t="inlineStr">
         <is>
-          <t>Louis Kouadio (a.kouadio2@cgiar.org)</t>
+          <t>Justin Djagba (j.djagba@cgiar.org)</t>
         </is>
       </c>
       <c r="K47" s="8" t="inlineStr">
@@ -5655,7 +5660,7 @@
       </c>
       <c r="L47" s="8" t="inlineStr">
         <is>
-          <t>ARCWeather usage terms: non-commercial, educational, research or personal use only, with citation. The portal states that Côte d'Ivoire climate data is distributed by Sodexam; no licence stated by the rights holder</t>
+          <t>Other (specify in notes)</t>
         </is>
       </c>
       <c r="M47" s="8" t="inlineStr">
@@ -5663,31 +5668,23 @@
           <t>Validated</t>
         </is>
       </c>
-      <c r="N47" s="8" t="inlineStr">
-        <is>
-          <t>synoptic_stations_daily.xlsx (one sheet per station - Bouake, Korhogo, Ferkessedougou)</t>
-        </is>
-      </c>
+      <c r="N47" s="8" t="n"/>
       <c r="O47" s="8" t="inlineStr">
         <is>
-          <t>server and drive</t>
+          <t>Drive</t>
         </is>
       </c>
       <c r="P47" s="8" t="n"/>
-      <c r="Q47" s="8" t="inlineStr">
-        <is>
-          <t>MOSAIC/datasets/MFL-2026-046/raw/</t>
-        </is>
-      </c>
+      <c r="Q47" s="8" t="n"/>
       <c r="R47" s="9" t="inlineStr">
         <is>
-          <t>Daily weather data for three synoptic stations in and around the N'Zi watershed, served by AfricaRice's ARCWeather portal: Bouaké and Ferkessédougou from 1980 to 2010, Korhogo from 1994 to 2001. Korhogo holds fewer variables, and its dew point is estimated from the minimum temperature. AfricaRice's own M'Bé research-station data from 2014 onward is a separate record, MFL-2026-084.</t>
+          <t>Agroecological zones</t>
         </is>
       </c>
       <c r="S47" s="8" t="n"/>
       <c r="T47" s="8" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2017</t>
         </is>
       </c>
       <c r="U47" s="8" t="inlineStr">
@@ -5697,24 +5694,20 @@
       </c>
       <c r="V47" s="8" t="inlineStr">
         <is>
-          <t>https://arcweather.africarice.org/en/downloads</t>
-        </is>
-      </c>
-      <c r="W47" s="8" t="inlineStr">
-        <is>
-          <t>3.5 MB</t>
-        </is>
-      </c>
+          <t>HarvestChoice, International Food Policy Research Institute (IFPRI); University of Minnesota, 2017, "CELL5M: A Multidisciplinary Geospatial Database for Africa South of the Sahara", https://doi.org/10.7910/DVN/G4TBLF, Harvard Dataverse, V5</t>
+        </is>
+      </c>
+      <c r="W47" s="8" t="n"/>
     </row>
     <row r="48">
       <c r="A48" s="10" t="inlineStr">
         <is>
-          <t>MFL-2026-048</t>
+          <t>MFL-2026-046</t>
         </is>
       </c>
       <c r="B48" s="10" t="inlineStr">
         <is>
-          <t>DSSAT soil profiles for Côte d'Ivoire (CI.SOL)</t>
+          <t>Climate station data (NHMS synoptic stations)</t>
         </is>
       </c>
       <c r="C48" s="10" t="inlineStr">
@@ -5724,12 +5717,12 @@
       </c>
       <c r="D48" s="10" t="inlineStr">
         <is>
-          <t>Degradation / land health</t>
+          <t>Water / hydrology</t>
         </is>
       </c>
       <c r="E48" s="10" t="inlineStr">
         <is>
-          <t>NATIONAL — Country-wide coverage</t>
+          <t>CIV-NZ — N'Zi Watershed</t>
         </is>
       </c>
       <c r="F48" s="10" t="inlineStr">
@@ -5739,12 +5732,12 @@
       </c>
       <c r="G48" s="10" t="inlineStr">
         <is>
-          <t>5-min resolution</t>
+          <t>Climate station observations</t>
         </is>
       </c>
       <c r="H48" s="10" t="inlineStr">
         <is>
-          <t>2015</t>
+          <t>1980-2010</t>
         </is>
       </c>
       <c r="I48" s="10" t="inlineStr">
@@ -5764,7 +5757,7 @@
       </c>
       <c r="L48" s="10" t="inlineStr">
         <is>
-          <t>CC BY 4.0</t>
+          <t>ARCWeather usage terms: non-commercial, educational, research or personal use only, with citation. The portal states that Côte d'Ivoire climate data is distributed by Sodexam; no licence stated by the rights holder</t>
         </is>
       </c>
       <c r="M48" s="10" t="inlineStr">
@@ -5774,7 +5767,7 @@
       </c>
       <c r="N48" s="10" t="inlineStr">
         <is>
-          <t>CI.SOL</t>
+          <t>synoptic_stations_daily.xlsx (one sheet per station - Bouake, Korhogo, Ferkessedougou)</t>
         </is>
       </c>
       <c r="O48" s="10" t="inlineStr">
@@ -5785,18 +5778,18 @@
       <c r="P48" s="10" t="n"/>
       <c r="Q48" s="10" t="inlineStr">
         <is>
-          <t>MOSAIC/datasets/MFL-2026-048/raw/</t>
+          <t>MOSAIC/datasets/MFL-2026-046/raw/</t>
         </is>
       </c>
       <c r="R48" s="11" t="inlineStr">
         <is>
-          <t>DSSAT soil profile file for Côte d'Ivoire (CI.SOL): 3,823 soil profiles on a 5-arc-minute grid covering the whole country, 425 of them inside the N'Zi landscape. It is the unmodified Côte d'Ivoire file of the Global High-Resolution Soil Profile Database for Crop Modeling Applications (IRI, MSU and HarvestChoice/IFPRI, 2015), published on the IFPRI Dataverse.</t>
+          <t>Daily weather data for three synoptic stations in and around the N'Zi watershed, served by AfricaRice's ARCWeather portal: Bouaké and Ferkessédougou from 1980 to 2010, Korhogo from 1994 to 2001. Korhogo holds fewer variables, and its dew point is estimated from the minimum temperature. AfricaRice's own M'Bé research-station data from 2014 onward is a separate record, MFL-2026-084.</t>
         </is>
       </c>
       <c r="S48" s="10" t="n"/>
       <c r="T48" s="10" t="inlineStr">
         <is>
-          <t>2015</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="U48" s="10" t="inlineStr">
@@ -5806,74 +5799,74 @@
       </c>
       <c r="V48" s="10" t="inlineStr">
         <is>
-          <t>https://doi.org/10.7910/DVN/1PEEY0</t>
+          <t>https://arcweather.africarice.org/en/downloads</t>
         </is>
       </c>
       <c r="W48" s="10" t="inlineStr">
         <is>
-          <t>9.3 MB</t>
+          <t>3.5 MB</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="8" t="inlineStr">
         <is>
-          <t>MFL-2026-050</t>
+          <t>MFL-2026-048</t>
         </is>
       </c>
       <c r="B49" s="8" t="inlineStr">
         <is>
-          <t>watershed boundary</t>
+          <t>DSSAT soil profiles for Côte d'Ivoire (CI.SOL)</t>
         </is>
       </c>
       <c r="C49" s="8" t="inlineStr">
         <is>
-          <t>Laos</t>
+          <t>Côte d'Ivoire</t>
         </is>
       </c>
       <c r="D49" s="8" t="inlineStr">
         <is>
-          <t>Boundaries / admin units</t>
+          <t>Degradation / land health</t>
         </is>
       </c>
       <c r="E49" s="8" t="inlineStr">
         <is>
-          <t>MEK-3S — 3S Basins (Sekong, Sesan, Srepok)</t>
+          <t>NATIONAL — Country-wide coverage</t>
         </is>
       </c>
       <c r="F49" s="8" t="inlineStr">
         <is>
-          <t>Vector</t>
+          <t>Tabular</t>
         </is>
       </c>
       <c r="G49" s="8" t="inlineStr">
         <is>
-          <t>basin and country levels</t>
+          <t>5-min resolution</t>
         </is>
       </c>
       <c r="H49" s="8" t="inlineStr">
         <is>
-          <t>present</t>
+          <t>2015</t>
         </is>
       </c>
       <c r="I49" s="8" t="inlineStr">
         <is>
-          <t>IWMI</t>
+          <t>AfricaRice</t>
         </is>
       </c>
       <c r="J49" s="8" t="inlineStr">
         <is>
-          <t>s.douangsavanh@cgiar.org</t>
+          <t>Louis Kouadio (a.kouadio2@cgiar.org)</t>
         </is>
       </c>
       <c r="K49" s="8" t="inlineStr">
         <is>
-          <t>Internal</t>
+          <t>Open</t>
         </is>
       </c>
       <c r="L49" s="8" t="inlineStr">
         <is>
-          <t>Restricted — contact data owner</t>
+          <t>CC BY 4.0</t>
         </is>
       </c>
       <c r="M49" s="8" t="inlineStr">
@@ -5881,46 +5874,58 @@
           <t>Validated</t>
         </is>
       </c>
-      <c r="N49" s="8" t="n"/>
+      <c r="N49" s="8" t="inlineStr">
+        <is>
+          <t>CI.SOL</t>
+        </is>
+      </c>
       <c r="O49" s="8" t="inlineStr">
         <is>
           <t>server and drive</t>
         </is>
       </c>
       <c r="P49" s="8" t="n"/>
-      <c r="Q49" s="8" t="n"/>
+      <c r="Q49" s="8" t="inlineStr">
+        <is>
+          <t>MOSAIC/datasets/MFL-2026-048/raw/</t>
+        </is>
+      </c>
       <c r="R49" s="9" t="inlineStr">
         <is>
-          <t>MRC produced the data</t>
+          <t>DSSAT soil profile file for Côte d'Ivoire (CI.SOL): 3,823 soil profiles on a 5-arc-minute grid covering the whole country, 425 of them inside the N'Zi landscape. It is the unmodified Côte d'Ivoire file of the Global High-Resolution Soil Profile Database for Crop Modeling Applications (IRI, MSU and HarvestChoice/IFPRI, 2015), published on the IFPRI Dataverse.</t>
         </is>
       </c>
       <c r="S49" s="8" t="n"/>
       <c r="T49" s="8" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>2015</t>
         </is>
       </c>
       <c r="U49" s="8" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Static</t>
         </is>
       </c>
       <c r="V49" s="8" t="inlineStr">
         <is>
-          <t>MRC website</t>
-        </is>
-      </c>
-      <c r="W49" s="8" t="n"/>
+          <t>https://doi.org/10.7910/DVN/1PEEY0</t>
+        </is>
+      </c>
+      <c r="W49" s="8" t="inlineStr">
+        <is>
+          <t>9.3 MB</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="10" t="inlineStr">
         <is>
-          <t>MFL-2026-051</t>
+          <t>MFL-2026-050</t>
         </is>
       </c>
       <c r="B50" s="10" t="inlineStr">
         <is>
-          <t>river network</t>
+          <t>watershed boundary</t>
         </is>
       </c>
       <c r="C50" s="10" t="inlineStr">
@@ -5930,7 +5935,7 @@
       </c>
       <c r="D50" s="10" t="inlineStr">
         <is>
-          <t>Water / hydrology</t>
+          <t>Boundaries / admin units</t>
         </is>
       </c>
       <c r="E50" s="10" t="inlineStr">
@@ -6012,12 +6017,12 @@
     <row r="51">
       <c r="A51" s="8" t="inlineStr">
         <is>
-          <t>MFL-2026-052</t>
+          <t>MFL-2026-051</t>
         </is>
       </c>
       <c r="B51" s="8" t="inlineStr">
         <is>
-          <t>LULC classification</t>
+          <t>river network</t>
         </is>
       </c>
       <c r="C51" s="8" t="inlineStr">
@@ -6027,7 +6032,7 @@
       </c>
       <c r="D51" s="8" t="inlineStr">
         <is>
-          <t>Land cover / land use</t>
+          <t>Water / hydrology</t>
         </is>
       </c>
       <c r="E51" s="8" t="inlineStr">
@@ -6091,7 +6096,7 @@
       <c r="S51" s="8" t="n"/>
       <c r="T51" s="8" t="inlineStr">
         <is>
-          <t>2020</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="U51" s="8" t="inlineStr">
@@ -6109,12 +6114,12 @@
     <row r="52">
       <c r="A52" s="10" t="inlineStr">
         <is>
-          <t>MFL-2026-053</t>
+          <t>MFL-2026-052</t>
         </is>
       </c>
       <c r="B52" s="10" t="inlineStr">
         <is>
-          <t>Sekong River Basin Management Plan</t>
+          <t>LULC classification</t>
         </is>
       </c>
       <c r="C52" s="10" t="inlineStr">
@@ -6124,27 +6129,27 @@
       </c>
       <c r="D52" s="10" t="inlineStr">
         <is>
-          <t>Socio-economic / livelihoods</t>
+          <t>Land cover / land use</t>
         </is>
       </c>
       <c r="E52" s="10" t="inlineStr">
         <is>
-          <t>NATIONAL — Country-wide coverage</t>
+          <t>MEK-3S — 3S Basins (Sekong, Sesan, Srepok)</t>
         </is>
       </c>
       <c r="F52" s="10" t="inlineStr">
         <is>
-          <t>Mixed</t>
+          <t>Vector</t>
         </is>
       </c>
       <c r="G52" s="10" t="inlineStr">
         <is>
-          <t>report-country and basin level</t>
+          <t>basin and country levels</t>
         </is>
       </c>
       <c r="H52" s="10" t="inlineStr">
         <is>
-          <t>2021-2025</t>
+          <t>present</t>
         </is>
       </c>
       <c r="I52" s="10" t="inlineStr">
@@ -6182,13 +6187,13 @@
       <c r="Q52" s="10" t="n"/>
       <c r="R52" s="11" t="inlineStr">
         <is>
-          <t>Ministry of Agriculture and Environment (MOAE), Lao PDR</t>
+          <t>MRC produced the data</t>
         </is>
       </c>
       <c r="S52" s="10" t="n"/>
       <c r="T52" s="10" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>2020</t>
         </is>
       </c>
       <c r="U52" s="10" t="inlineStr">
@@ -6198,7 +6203,7 @@
       </c>
       <c r="V52" s="10" t="inlineStr">
         <is>
-          <t>website-MOAE</t>
+          <t>MRC website</t>
         </is>
       </c>
       <c r="W52" s="10" t="n"/>
@@ -6206,12 +6211,12 @@
     <row r="53">
       <c r="A53" s="8" t="inlineStr">
         <is>
-          <t>MFL-2026-054</t>
+          <t>MFL-2026-053</t>
         </is>
       </c>
       <c r="B53" s="8" t="inlineStr">
         <is>
-          <t>soil classification</t>
+          <t>Sekong River Basin Management Plan</t>
         </is>
       </c>
       <c r="C53" s="8" t="inlineStr">
@@ -6221,7 +6226,7 @@
       </c>
       <c r="D53" s="8" t="inlineStr">
         <is>
-          <t>Land cover / land use</t>
+          <t>Socio-economic / livelihoods</t>
         </is>
       </c>
       <c r="E53" s="8" t="inlineStr">
@@ -6231,17 +6236,17 @@
       </c>
       <c r="F53" s="8" t="inlineStr">
         <is>
-          <t>Vector</t>
+          <t>Mixed</t>
         </is>
       </c>
       <c r="G53" s="8" t="inlineStr">
         <is>
-          <t>basin and country levels</t>
+          <t>report-country and basin level</t>
         </is>
       </c>
       <c r="H53" s="8" t="inlineStr">
         <is>
-          <t>present</t>
+          <t>2021-2025</t>
         </is>
       </c>
       <c r="I53" s="8" t="inlineStr">
@@ -6303,22 +6308,22 @@
     <row r="54">
       <c r="A54" s="10" t="inlineStr">
         <is>
-          <t>MFL-2026-055</t>
+          <t>MFL-2026-054</t>
         </is>
       </c>
       <c r="B54" s="10" t="inlineStr">
         <is>
-          <t>Crop fields (2025) - focus on NUS crops</t>
+          <t>soil classification</t>
         </is>
       </c>
       <c r="C54" s="10" t="inlineStr">
         <is>
-          <t>Peru</t>
+          <t>Laos</t>
         </is>
       </c>
       <c r="D54" s="10" t="inlineStr">
         <is>
-          <t>Agrobiodiversity / crops</t>
+          <t>Land cover / land use</t>
         </is>
       </c>
       <c r="E54" s="10" t="inlineStr">
@@ -6333,22 +6338,22 @@
       </c>
       <c r="G54" s="10" t="inlineStr">
         <is>
-          <t>Pucallpa Aguaytia Corridor (Andean Amazon Landscape)</t>
+          <t>basin and country levels</t>
         </is>
       </c>
       <c r="H54" s="10" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>present</t>
         </is>
       </c>
       <c r="I54" s="10" t="inlineStr">
         <is>
-          <t>CIP</t>
+          <t>IWMI</t>
         </is>
       </c>
       <c r="J54" s="10" t="inlineStr">
         <is>
-          <t>javier.ochoa@cgiar.org</t>
+          <t>s.douangsavanh@cgiar.org</t>
         </is>
       </c>
       <c r="K54" s="10" t="inlineStr">
@@ -6369,14 +6374,14 @@
       <c r="N54" s="10" t="n"/>
       <c r="O54" s="10" t="inlineStr">
         <is>
-          <t>CIP Dataverse</t>
+          <t>server and drive</t>
         </is>
       </c>
       <c r="P54" s="10" t="n"/>
       <c r="Q54" s="10" t="n"/>
       <c r="R54" s="11" t="inlineStr">
         <is>
-          <t>Amazonian tubers classified as Neglected and Underutilized Crop Species (NUS crops) in each farmers field, accurately documenting the characteristics of these species in situ. This process generated a comprehensive dataset comprising seven different crops: cassava (Manihot esculenta), sweet potato (Ipomoea batatas), aerial potato (Dioscorea bulbifera L.), achipa or chuin (Pachyrhizus tuberosus), pituca (Colocasia spp., Xanthosoma spp.), dale-dale (Calathea allouia), and sacha papa (Dioscorea bulbifera). Overall, the study captured the main characteristics of 683 varieties/404 species recorded across 273 mapped plots from 221 farmer households. The dataset is organized into: A) Household information, B) Field information and land-use history, C) Species names, D) Variety names, and E) Community collection points of NUS crops</t>
+          <t>Ministry of Agriculture and Environment (MOAE), Lao PDR</t>
         </is>
       </c>
       <c r="S54" s="10" t="n"/>
@@ -6392,7 +6397,7 @@
       </c>
       <c r="V54" s="10" t="inlineStr">
         <is>
-          <t>https://data.cipotato.org/</t>
+          <t>website-MOAE</t>
         </is>
       </c>
       <c r="W54" s="10" t="n"/>
@@ -6400,17 +6405,17 @@
     <row r="55">
       <c r="A55" s="8" t="inlineStr">
         <is>
-          <t>MFL-2026-056</t>
+          <t>MFL-2026-055</t>
         </is>
       </c>
       <c r="B55" s="8" t="inlineStr">
         <is>
-          <t>Crop fields (2023)  focus on 	Potatoes, Oca, Mashua and andean fruit trees</t>
+          <t>Crop fields (2025) - focus on NUS crops</t>
         </is>
       </c>
       <c r="C55" s="8" t="inlineStr">
         <is>
-          <t>Colombia</t>
+          <t>Peru</t>
         </is>
       </c>
       <c r="D55" s="8" t="inlineStr">
@@ -6430,12 +6435,12 @@
       </c>
       <c r="G55" s="8" t="inlineStr">
         <is>
-          <t>Cumbal (Andean Amazon Landscape)</t>
+          <t>Pucallpa Aguaytia Corridor (Andean Amazon Landscape)</t>
         </is>
       </c>
       <c r="H55" s="8" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="I55" s="8" t="inlineStr">
@@ -6473,7 +6478,7 @@
       <c r="Q55" s="8" t="n"/>
       <c r="R55" s="9" t="inlineStr">
         <is>
-          <t>A total of 206 farmers in Cumbal, Colombia, were surveyed utilizing ArcGIS Survey 123. Each farmer's field was physically visited, and the 'Participatory Mapping of Farmers' Fields' tool was employed to delineate polygons for each 'shagra', accurately determining their respective areas. This process captured the characteristics of 557 mapped plots across 206 farmers' households. The resultant comprehensive dataset comprises five distinct databases: A) Preliminary Information, B) Shagra Information, C) Land Use Over the Years, and D) Variety Names. These datasets have been individualized and standardized using the common identifiers 'GlobalID Household' and 'GlobalID Shagra'.</t>
+          <t>Amazonian tubers classified as Neglected and Underutilized Crop Species (NUS crops) in each farmers field, accurately documenting the characteristics of these species in situ. This process generated a comprehensive dataset comprising seven different crops: cassava (Manihot esculenta), sweet potato (Ipomoea batatas), aerial potato (Dioscorea bulbifera L.), achipa or chuin (Pachyrhizus tuberosus), pituca (Colocasia spp., Xanthosoma spp.), dale-dale (Calathea allouia), and sacha papa (Dioscorea bulbifera). Overall, the study captured the main characteristics of 683 varieties/404 species recorded across 273 mapped plots from 221 farmer households. The dataset is organized into: A) Household information, B) Field information and land-use history, C) Species names, D) Variety names, and E) Community collection points of NUS crops</t>
         </is>
       </c>
       <c r="S55" s="8" t="n"/>
@@ -6497,17 +6502,17 @@
     <row r="56">
       <c r="A56" s="10" t="inlineStr">
         <is>
-          <t>MFL-2026-057</t>
+          <t>MFL-2026-056</t>
         </is>
       </c>
       <c r="B56" s="10" t="inlineStr">
         <is>
-          <t>Crop fields (2023)  focus on Banana, Pumpkins, Taro, Mustard</t>
+          <t>Crop fields (2023)  focus on 	Potatoes, Oca, Mashua and andean fruit trees</t>
         </is>
       </c>
       <c r="C56" s="10" t="inlineStr">
         <is>
-          <t>Vietnam</t>
+          <t>Colombia</t>
         </is>
       </c>
       <c r="D56" s="10" t="inlineStr">
@@ -6527,7 +6532,7 @@
       </c>
       <c r="G56" s="10" t="inlineStr">
         <is>
-          <t>Son La  and Lao Cai (Vietnam)</t>
+          <t>Cumbal (Andean Amazon Landscape)</t>
         </is>
       </c>
       <c r="H56" s="10" t="inlineStr">
@@ -6570,7 +6575,7 @@
       <c r="Q56" s="10" t="n"/>
       <c r="R56" s="11" t="inlineStr">
         <is>
-          <t>A total of 200 farmers in Vietnam, were surveyed utilizing ArcGIS Survey 123. Each farmer's field was physically visited, and the 'Participatory Mapping of Farmers' Fields' tool was employed to delineate polygons for each 'parcel', accurately determining their respective areas. This process captured the characteristics of 773 mapped plots across 200 farmers' households. The resultant comprehensive dataset comprises five distinct databases: A) Preliminary Information, B) Plot Information, C) Plot and Land Use, D) Crop Information, E) Variety Names. These datasets have been individualized and standardized using the common identifiers 'GlobalID Household' and 'GlobalID Plot'.</t>
+          <t>A total of 206 farmers in Cumbal, Colombia, were surveyed utilizing ArcGIS Survey 123. Each farmer's field was physically visited, and the 'Participatory Mapping of Farmers' Fields' tool was employed to delineate polygons for each 'shagra', accurately determining their respective areas. This process captured the characteristics of 557 mapped plots across 206 farmers' households. The resultant comprehensive dataset comprises five distinct databases: A) Preliminary Information, B) Shagra Information, C) Land Use Over the Years, and D) Variety Names. These datasets have been individualized and standardized using the common identifiers 'GlobalID Household' and 'GlobalID Shagra'.</t>
         </is>
       </c>
       <c r="S56" s="10" t="n"/>
@@ -6594,62 +6599,62 @@
     <row r="57">
       <c r="A57" s="8" t="inlineStr">
         <is>
-          <t>MFL-2026-058</t>
+          <t>MFL-2026-057</t>
         </is>
       </c>
       <c r="B57" s="8" t="inlineStr">
         <is>
-          <t>Forest cover in Cambodia (2015-2023)</t>
+          <t>Crop fields (2023)  focus on Banana, Pumpkins, Taro, Mustard</t>
         </is>
       </c>
       <c r="C57" s="8" t="inlineStr">
         <is>
-          <t>Cambodia</t>
+          <t>Vietnam</t>
         </is>
       </c>
       <c r="D57" s="8" t="inlineStr">
         <is>
-          <t>Land cover / land use</t>
+          <t>Agrobiodiversity / crops</t>
         </is>
       </c>
       <c r="E57" s="8" t="inlineStr">
         <is>
-          <t>MEK-3S — 3S Basins (Sekong, Sesan, Srepok)</t>
+          <t>NATIONAL — Country-wide coverage</t>
         </is>
       </c>
       <c r="F57" s="8" t="inlineStr">
         <is>
-          <t>Raster</t>
+          <t>Vector</t>
         </is>
       </c>
       <c r="G57" s="8" t="inlineStr">
         <is>
-          <t>30m</t>
+          <t>Son La  and Lao Cai (Vietnam)</t>
         </is>
       </c>
       <c r="H57" s="8" t="inlineStr">
         <is>
-          <t>2015-2023</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="I57" s="8" t="inlineStr">
         <is>
-          <t>WorldFish</t>
+          <t>CIP</t>
         </is>
       </c>
       <c r="J57" s="8" t="inlineStr">
         <is>
-          <t>Shwu Jiau Teoh (s.teoh@cgiar.org)</t>
+          <t>javier.ochoa@cgiar.org</t>
         </is>
       </c>
       <c r="K57" s="8" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Internal</t>
         </is>
       </c>
       <c r="L57" s="8" t="inlineStr">
         <is>
-          <t>Other (specify in notes)</t>
+          <t>Restricted — contact data owner</t>
         </is>
       </c>
       <c r="M57" s="8" t="inlineStr">
@@ -6660,14 +6665,14 @@
       <c r="N57" s="8" t="n"/>
       <c r="O57" s="8" t="inlineStr">
         <is>
-          <t>local drive</t>
+          <t>CIP Dataverse</t>
         </is>
       </c>
       <c r="P57" s="8" t="n"/>
       <c r="Q57" s="8" t="n"/>
       <c r="R57" s="9" t="inlineStr">
         <is>
-          <t>Cambodia's annual forest cover developed through the USAID's Cambodia Supporting Forests and Biodiversity (USAID SFB) project</t>
+          <t>A total of 200 farmers in Vietnam, were surveyed utilizing ArcGIS Survey 123. Each farmer's field was physically visited, and the 'Participatory Mapping of Farmers' Fields' tool was employed to delineate polygons for each 'parcel', accurately determining their respective areas. This process captured the characteristics of 773 mapped plots across 200 farmers' households. The resultant comprehensive dataset comprises five distinct databases: A) Preliminary Information, B) Plot Information, C) Plot and Land Use, D) Crop Information, E) Variety Names. These datasets have been individualized and standardized using the common identifiers 'GlobalID Household' and 'GlobalID Plot'.</t>
         </is>
       </c>
       <c r="S57" s="8" t="n"/>
@@ -6683,7 +6688,7 @@
       </c>
       <c r="V57" s="8" t="inlineStr">
         <is>
-          <t>https://data.opendevelopmentmekong.net/map/forest-cove-2015-present</t>
+          <t>https://data.cipotato.org/</t>
         </is>
       </c>
       <c r="W57" s="8" t="n"/>
@@ -6691,12 +6696,12 @@
     <row r="58">
       <c r="A58" s="10" t="inlineStr">
         <is>
-          <t>MFL-2026-059</t>
+          <t>MFL-2026-058</t>
         </is>
       </c>
       <c r="B58" s="10" t="inlineStr">
         <is>
-          <t>Community fisheries</t>
+          <t>Forest cover in Cambodia (2015-2023)</t>
         </is>
       </c>
       <c r="C58" s="10" t="inlineStr">
@@ -6706,7 +6711,7 @@
       </c>
       <c r="D58" s="10" t="inlineStr">
         <is>
-          <t>Socio-economic / livelihoods</t>
+          <t>Land cover / land use</t>
         </is>
       </c>
       <c r="E58" s="10" t="inlineStr">
@@ -6716,17 +6721,17 @@
       </c>
       <c r="F58" s="10" t="inlineStr">
         <is>
-          <t>Vector</t>
+          <t>Raster</t>
         </is>
       </c>
       <c r="G58" s="10" t="inlineStr">
         <is>
-          <t>village level</t>
+          <t>30m</t>
         </is>
       </c>
       <c r="H58" s="10" t="inlineStr">
         <is>
-          <t>2011</t>
+          <t>2015-2023</t>
         </is>
       </c>
       <c r="I58" s="10" t="inlineStr">
@@ -6746,7 +6751,7 @@
       </c>
       <c r="L58" s="10" t="inlineStr">
         <is>
-          <t>CC BY 4.0</t>
+          <t>Other (specify in notes)</t>
         </is>
       </c>
       <c r="M58" s="10" t="inlineStr">
@@ -6764,7 +6769,7 @@
       <c r="Q58" s="10" t="n"/>
       <c r="R58" s="11" t="inlineStr">
         <is>
-          <t>provides geographic boundaries, size and the number of villages covered by each community fishery</t>
+          <t>Cambodia's annual forest cover developed through the USAID's Cambodia Supporting Forests and Biodiversity (USAID SFB) project</t>
         </is>
       </c>
       <c r="S58" s="10" t="n"/>
@@ -6780,7 +6785,7 @@
       </c>
       <c r="V58" s="10" t="inlineStr">
         <is>
-          <t>https://data.opendevelopmentcambodia.net/en/dataset/community-fisheries-map-for-cambodia-2011</t>
+          <t>https://data.opendevelopmentmekong.net/map/forest-cove-2015-present</t>
         </is>
       </c>
       <c r="W58" s="10" t="n"/>
@@ -6788,12 +6793,12 @@
     <row r="59">
       <c r="A59" s="8" t="inlineStr">
         <is>
-          <t>MFL-2026-060</t>
+          <t>MFL-2026-059</t>
         </is>
       </c>
       <c r="B59" s="8" t="inlineStr">
         <is>
-          <t>Marine fisheries management area</t>
+          <t>Community fisheries</t>
         </is>
       </c>
       <c r="C59" s="8" t="inlineStr">
@@ -6803,7 +6808,7 @@
       </c>
       <c r="D59" s="8" t="inlineStr">
         <is>
-          <t>Biodiversity / ecosystems</t>
+          <t>Socio-economic / livelihoods</t>
         </is>
       </c>
       <c r="E59" s="8" t="inlineStr">
@@ -6818,12 +6823,12 @@
       </c>
       <c r="G59" s="8" t="inlineStr">
         <is>
-          <t>boundary level</t>
+          <t>village level</t>
         </is>
       </c>
       <c r="H59" s="8" t="inlineStr">
         <is>
-          <t>2018</t>
+          <t>2011</t>
         </is>
       </c>
       <c r="I59" s="8" t="inlineStr">
@@ -6861,7 +6866,7 @@
       <c r="Q59" s="8" t="n"/>
       <c r="R59" s="9" t="inlineStr">
         <is>
-          <t>Marine fisheries management area to enhance the protection of the marine biodiversity and fisheries livelihood within​ Archipelago in marine areas, divided into 6 classifications such as community fisheries, conservation areas, fisheries refugias, multiple use areas, protected area, and recreational areas.</t>
+          <t>provides geographic boundaries, size and the number of villages covered by each community fishery</t>
         </is>
       </c>
       <c r="S59" s="8" t="n"/>
@@ -6877,7 +6882,7 @@
       </c>
       <c r="V59" s="8" t="inlineStr">
         <is>
-          <t>https://data.opendevelopmentcambodia.net/en/dataset/marine-fisheries-management-area</t>
+          <t>https://data.opendevelopmentcambodia.net/en/dataset/community-fisheries-map-for-cambodia-2011</t>
         </is>
       </c>
       <c r="W59" s="8" t="n"/>
@@ -6885,12 +6890,12 @@
     <row r="60">
       <c r="A60" s="10" t="inlineStr">
         <is>
-          <t>MFL-2026-061</t>
+          <t>MFL-2026-060</t>
         </is>
       </c>
       <c r="B60" s="10" t="inlineStr">
         <is>
-          <t>Fish dependency</t>
+          <t>Marine fisheries management area</t>
         </is>
       </c>
       <c r="C60" s="10" t="inlineStr">
@@ -6900,7 +6905,7 @@
       </c>
       <c r="D60" s="10" t="inlineStr">
         <is>
-          <t>Socio-economic / livelihoods</t>
+          <t>Biodiversity / ecosystems</t>
         </is>
       </c>
       <c r="E60" s="10" t="inlineStr">
@@ -6915,12 +6920,12 @@
       </c>
       <c r="G60" s="10" t="inlineStr">
         <is>
-          <t>commune level (admin-level-3)</t>
+          <t>boundary level</t>
         </is>
       </c>
       <c r="H60" s="10" t="inlineStr">
         <is>
-          <t>2015</t>
+          <t>2018</t>
         </is>
       </c>
       <c r="I60" s="10" t="inlineStr">
@@ -6958,7 +6963,7 @@
       <c r="Q60" s="10" t="n"/>
       <c r="R60" s="11" t="inlineStr">
         <is>
-          <t>Fsh dependency rate based on the communal statistics</t>
+          <t>Marine fisheries management area to enhance the protection of the marine biodiversity and fisheries livelihood within​ Archipelago in marine areas, divided into 6 classifications such as community fisheries, conservation areas, fisheries refugias, multiple use areas, protected area, and recreational areas.</t>
         </is>
       </c>
       <c r="S60" s="10" t="n"/>
@@ -6974,7 +6979,7 @@
       </c>
       <c r="V60" s="10" t="inlineStr">
         <is>
-          <t>https://data.opendevelopmentcambodia.net/en/dataset/map_fish_dependency</t>
+          <t>https://data.opendevelopmentcambodia.net/en/dataset/marine-fisheries-management-area</t>
         </is>
       </c>
       <c r="W60" s="10" t="n"/>
@@ -6982,12 +6987,12 @@
     <row r="61">
       <c r="A61" s="8" t="inlineStr">
         <is>
-          <t>MFL-2026-062</t>
+          <t>MFL-2026-061</t>
         </is>
       </c>
       <c r="B61" s="8" t="inlineStr">
         <is>
-          <t>Rice ecosystem</t>
+          <t>Fish dependency</t>
         </is>
       </c>
       <c r="C61" s="8" t="inlineStr">
@@ -6997,7 +7002,7 @@
       </c>
       <c r="D61" s="8" t="inlineStr">
         <is>
-          <t>Agrobiodiversity / crops</t>
+          <t>Socio-economic / livelihoods</t>
         </is>
       </c>
       <c r="E61" s="8" t="inlineStr">
@@ -7012,7 +7017,7 @@
       </c>
       <c r="G61" s="8" t="inlineStr">
         <is>
-          <t>boundary level</t>
+          <t>commune level (admin-level-3)</t>
         </is>
       </c>
       <c r="H61" s="8" t="inlineStr">
@@ -7055,7 +7060,7 @@
       <c r="Q61" s="8" t="n"/>
       <c r="R61" s="9" t="inlineStr">
         <is>
-          <t>locations of rice in 4 categories: Rainfed upland rice, Recession rice, Deep water/floating rice, Rainfed lowland rice</t>
+          <t>Fsh dependency rate based on the communal statistics</t>
         </is>
       </c>
       <c r="S61" s="8" t="n"/>
@@ -7071,7 +7076,7 @@
       </c>
       <c r="V61" s="8" t="inlineStr">
         <is>
-          <t>https://data.opendevelopmentcambodia.net/en/dataset/map-rice-ecosystem</t>
+          <t>https://data.opendevelopmentcambodia.net/en/dataset/map_fish_dependency</t>
         </is>
       </c>
       <c r="W61" s="8" t="n"/>
@@ -7079,57 +7084,57 @@
     <row r="62">
       <c r="A62" s="10" t="inlineStr">
         <is>
-          <t>MFL-2026-063</t>
+          <t>MFL-2026-062</t>
         </is>
       </c>
       <c r="B62" s="10" t="inlineStr">
         <is>
-          <t>India's open natural ecosystem</t>
+          <t>Rice ecosystem</t>
         </is>
       </c>
       <c r="C62" s="10" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>Cambodia</t>
         </is>
       </c>
       <c r="D62" s="10" t="inlineStr">
         <is>
-          <t>Ecosystem condition</t>
+          <t>Agrobiodiversity / crops</t>
         </is>
       </c>
       <c r="E62" s="10" t="inlineStr">
         <is>
-          <t>IND-CH — Central India Highlands</t>
+          <t>MEK-3S — 3S Basins (Sekong, Sesan, Srepok)</t>
         </is>
       </c>
       <c r="F62" s="10" t="inlineStr">
         <is>
-          <t>Raster</t>
+          <t>Vector</t>
         </is>
       </c>
       <c r="G62" s="10" t="inlineStr">
         <is>
-          <t>10m</t>
+          <t>boundary level</t>
         </is>
       </c>
       <c r="H62" s="10" t="inlineStr">
         <is>
-          <t>2018-2024</t>
+          <t>2015</t>
         </is>
       </c>
       <c r="I62" s="10" t="inlineStr">
         <is>
-          <t>Alliance Bioversity-CIAT</t>
+          <t>WorldFish</t>
         </is>
       </c>
       <c r="J62" s="10" t="inlineStr">
         <is>
-          <t>Smitha Krishnan (s.krishnan@cgiar.org)</t>
+          <t>Shwu Jiau Teoh (s.teoh@cgiar.org)</t>
         </is>
       </c>
       <c r="K62" s="10" t="inlineStr">
         <is>
-          <t>Restricted</t>
+          <t>Open</t>
         </is>
       </c>
       <c r="L62" s="10" t="inlineStr">
@@ -7139,36 +7144,36 @@
       </c>
       <c r="M62" s="10" t="inlineStr">
         <is>
-          <t>Processed</t>
+          <t>Validated</t>
         </is>
       </c>
       <c r="N62" s="10" t="n"/>
       <c r="O62" s="10" t="inlineStr">
         <is>
-          <t>ATREE -Server - GEE</t>
+          <t>local drive</t>
         </is>
       </c>
       <c r="P62" s="10" t="n"/>
       <c r="Q62" s="10" t="n"/>
       <c r="R62" s="11" t="inlineStr">
         <is>
-          <t>India's Open Natural Ecosystems at a 10-m scale,</t>
+          <t>locations of rice in 4 categories: Rainfed upland rice, Recession rice, Deep water/floating rice, Rainfed lowland rice</t>
         </is>
       </c>
       <c r="S62" s="10" t="n"/>
       <c r="T62" s="10" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="U62" s="10" t="inlineStr">
         <is>
-          <t>Static</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="V62" s="10" t="inlineStr">
         <is>
-          <t>open-natural-ecosystems</t>
+          <t>https://data.opendevelopmentcambodia.net/en/dataset/map-rice-ecosystem</t>
         </is>
       </c>
       <c r="W62" s="10" t="n"/>
@@ -7176,27 +7181,27 @@
     <row r="63">
       <c r="A63" s="8" t="inlineStr">
         <is>
-          <t>MFL-2026-064</t>
+          <t>MFL-2026-063</t>
         </is>
       </c>
       <c r="B63" s="8" t="inlineStr">
         <is>
-          <t>Tree conservation and restoration priority areas (Kenya)</t>
+          <t>India's open natural ecosystem</t>
         </is>
       </c>
       <c r="C63" s="8" t="inlineStr">
         <is>
-          <t>Kenya</t>
+          <t>India</t>
         </is>
       </c>
       <c r="D63" s="8" t="inlineStr">
         <is>
-          <t>Decision-support outputs</t>
+          <t>Ecosystem condition</t>
         </is>
       </c>
       <c r="E63" s="8" t="inlineStr">
         <is>
-          <t>NATIONAL — Country-wide coverage</t>
+          <t>IND-CH — Central India Highlands</t>
         </is>
       </c>
       <c r="F63" s="8" t="inlineStr">
@@ -7206,12 +7211,12 @@
       </c>
       <c r="G63" s="8" t="inlineStr">
         <is>
-          <t>1000m</t>
+          <t>10m</t>
         </is>
       </c>
       <c r="H63" s="8" t="inlineStr">
         <is>
-          <t>2017-2025</t>
+          <t>2018-2024</t>
         </is>
       </c>
       <c r="I63" s="8" t="inlineStr">
@@ -7221,43 +7226,35 @@
       </c>
       <c r="J63" s="8" t="inlineStr">
         <is>
-          <t>Hannes Gaisberger, h.gaisberger@cgiar.org</t>
+          <t>Smitha Krishnan (s.krishnan@cgiar.org)</t>
         </is>
       </c>
       <c r="K63" s="8" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Restricted</t>
         </is>
       </c>
       <c r="L63" s="8" t="inlineStr">
         <is>
-          <t>CGIAR Open Access</t>
+          <t>CC BY 4.0</t>
         </is>
       </c>
       <c r="M63" s="8" t="inlineStr">
         <is>
-          <t>Validated</t>
-        </is>
-      </c>
-      <c r="N63" s="8" t="inlineStr">
-        <is>
-          <t>ex_situ_conservation.tif; expanding_protection.tif; landscape_restoration.tif; maintaining_protection.tif</t>
-        </is>
-      </c>
+          <t>Processed</t>
+        </is>
+      </c>
+      <c r="N63" s="8" t="n"/>
       <c r="O63" s="8" t="inlineStr">
         <is>
-          <t>Dataverse repository</t>
+          <t>ATREE -Server - GEE</t>
         </is>
       </c>
       <c r="P63" s="8" t="n"/>
-      <c r="Q63" s="8" t="inlineStr">
-        <is>
-          <t>MOSAIC/datasets/MFL-2026-064/raw/</t>
-        </is>
-      </c>
+      <c r="Q63" s="8" t="n"/>
       <c r="R63" s="9" t="inlineStr">
         <is>
-          <t>Conservation for Restoration (C4R) tool KENYA: mapping the vulnerability and priority areas for conservation and restoration of 78 native tree species. Linked to D4R</t>
+          <t>India's Open Natural Ecosystems at a 10-m scale,</t>
         </is>
       </c>
       <c r="S63" s="8" t="n"/>
@@ -7268,74 +7265,70 @@
       </c>
       <c r="U63" s="8" t="inlineStr">
         <is>
-          <t>On-demand</t>
+          <t>Static</t>
         </is>
       </c>
       <c r="V63" s="8" t="inlineStr">
         <is>
-          <t>https://dataverse.harvard.edu/citation?persistentId=doi:10.7910/DVN/2ZQTB2</t>
-        </is>
-      </c>
-      <c r="W63" s="8" t="inlineStr">
-        <is>
-          <t>220 MB</t>
-        </is>
-      </c>
+          <t>open-natural-ecosystems</t>
+        </is>
+      </c>
+      <c r="W63" s="8" t="n"/>
     </row>
     <row r="64">
       <c r="A64" s="10" t="inlineStr">
         <is>
-          <t>MFL-2026-065</t>
+          <t>MFL-2026-064</t>
         </is>
       </c>
       <c r="B64" s="10" t="inlineStr">
         <is>
-          <t>Soil health status and texture</t>
+          <t>Tree conservation and restoration priority areas (Kenya)</t>
         </is>
       </c>
       <c r="C64" s="10" t="inlineStr">
         <is>
-          <t>Zimbabwe</t>
+          <t>Kenya</t>
         </is>
       </c>
       <c r="D64" s="10" t="inlineStr">
         <is>
-          <t>Degradation / land health</t>
+          <t>Decision-support outputs</t>
         </is>
       </c>
       <c r="E64" s="10" t="inlineStr">
         <is>
-          <t>ZWE-MB — Mbire – Lower Zambezi Valley</t>
+          <t>NATIONAL — Country-wide coverage</t>
         </is>
       </c>
       <c r="F64" s="10" t="inlineStr">
         <is>
-          <t>Tabular</t>
+          <t>Raster</t>
         </is>
       </c>
       <c r="G64" s="10" t="inlineStr">
         <is>
-          <t>Ward level</t>
+          <t>1000m</t>
         </is>
       </c>
       <c r="H64" s="10" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2017-2025</t>
         </is>
       </c>
       <c r="I64" s="10" t="inlineStr">
         <is>
-          <t>CIMMYT</t>
+          <t>Alliance Bioversity-CIAT</t>
         </is>
       </c>
       <c r="J64" s="10" t="inlineStr">
         <is>
-          <t>Telma.SIBANDA@um6p.ma</t>
+          <t>Hannes Gaisberger, h.gaisberger@cgiar.org</t>
         </is>
       </c>
       <c r="K64" s="10" t="inlineStr">
         <is>
-          <t>Restricted</t>
+          <t>Open</t>
         </is>
       </c>
       <c r="L64" s="10" t="inlineStr">
@@ -7345,54 +7338,66 @@
       </c>
       <c r="M64" s="10" t="inlineStr">
         <is>
-          <t>Processed</t>
-        </is>
-      </c>
-      <c r="N64" s="10" t="n"/>
+          <t>Validated</t>
+        </is>
+      </c>
+      <c r="N64" s="10" t="inlineStr">
+        <is>
+          <t>ex_situ_conservation.tif; expanding_protection.tif; landscape_restoration.tif; maintaining_protection.tif</t>
+        </is>
+      </c>
       <c r="O64" s="10" t="inlineStr">
         <is>
-          <t>Drive</t>
+          <t>Dataverse repository</t>
         </is>
       </c>
       <c r="P64" s="10" t="n"/>
-      <c r="Q64" s="10" t="n"/>
+      <c r="Q64" s="10" t="inlineStr">
+        <is>
+          <t>MOSAIC/datasets/MFL-2026-064/raw/</t>
+        </is>
+      </c>
       <c r="R64" s="11" t="inlineStr">
         <is>
-          <t>Ward-level soil texture, nitrogen, and carbon content data — Original landscape entry: Mbire: Wards 2 and 3</t>
+          <t>Conservation for Restoration (C4R) tool KENYA: mapping the vulnerability and priority areas for conservation and restoration of 78 native tree species. Linked to D4R</t>
         </is>
       </c>
       <c r="S64" s="10" t="n"/>
       <c r="T64" s="10" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="U64" s="10" t="inlineStr">
         <is>
-          <t>Static</t>
+          <t>On-demand</t>
         </is>
       </c>
       <c r="V64" s="10" t="inlineStr">
         <is>
-          <t>Internal Available on request</t>
-        </is>
-      </c>
-      <c r="W64" s="10" t="n"/>
+          <t>https://dataverse.harvard.edu/citation?persistentId=doi:10.7910/DVN/2ZQTB2</t>
+        </is>
+      </c>
+      <c r="W64" s="10" t="inlineStr">
+        <is>
+          <t>220 MB</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="8" t="inlineStr">
         <is>
-          <t>MFL-2026-066</t>
+          <t>MFL-2026-065</t>
         </is>
       </c>
       <c r="B65" s="8" t="inlineStr">
         <is>
-          <t>iSDAsoil soil properties for the N'Zi watershed (0-20 and 20-50 cm)</t>
+          <t>Soil health status and texture</t>
         </is>
       </c>
       <c r="C65" s="8" t="inlineStr">
         <is>
-          <t>Côte d'Ivoire</t>
+          <t>Zimbabwe</t>
         </is>
       </c>
       <c r="D65" s="8" t="inlineStr">
@@ -7402,76 +7407,76 @@
       </c>
       <c r="E65" s="8" t="inlineStr">
         <is>
-          <t>CIV-NZ — N'Zi Watershed</t>
+          <t>ZWE-MB — Mbire – Lower Zambezi Valley</t>
         </is>
       </c>
       <c r="F65" s="8" t="inlineStr">
         <is>
-          <t>Raster</t>
+          <t>Tabular</t>
         </is>
       </c>
       <c r="G65" s="8" t="inlineStr">
         <is>
-          <t>30 m</t>
+          <t>Ward level</t>
         </is>
       </c>
       <c r="H65" s="8" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="I65" s="8" t="inlineStr">
         <is>
-          <t>AfricaRice</t>
+          <t>CIMMYT</t>
         </is>
       </c>
       <c r="J65" s="8" t="inlineStr">
         <is>
-          <t>Louis Kouadio (a.kouadio2@cgiar.org)</t>
+          <t>Telma.SIBANDA@um6p.ma</t>
         </is>
       </c>
       <c r="K65" s="8" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Restricted</t>
         </is>
       </c>
       <c r="L65" s="8" t="inlineStr">
         <is>
-          <t>CC BY 4.0</t>
+          <t>CGIAR Open Access</t>
         </is>
       </c>
       <c r="M65" s="8" t="inlineStr">
         <is>
-          <t>Validated</t>
+          <t>Processed</t>
         </is>
       </c>
       <c r="N65" s="8" t="n"/>
       <c r="O65" s="8" t="inlineStr">
         <is>
-          <t>server and drive</t>
+          <t>Drive</t>
         </is>
       </c>
       <c r="P65" s="8" t="n"/>
       <c r="Q65" s="8" t="n"/>
       <c r="R65" s="9" t="inlineStr">
         <is>
-          <t>Fifteen soil properties from iSDAsoil (iSDA), extracted by AfricaRice for the N'Zi watershed at about 30 m, at 0-20 and 20-50 cm: bulk density, calcium, cation exchange capacity, clay, iron, potassium, magnesium, total nitrogen, phosphorus, pH, sulphur, sand, silt, soil organic carbon and zinc, in physical units. The public source is iSDAsoil for Africa.</t>
+          <t>Ward-level soil texture, nitrogen, and carbon content data — Original landscape entry: Mbire: Wards 2 and 3</t>
         </is>
       </c>
       <c r="S65" s="8" t="n"/>
       <c r="T65" s="8" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="U65" s="8" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Static</t>
         </is>
       </c>
       <c r="V65" s="8" t="inlineStr">
         <is>
-          <t>https://www.isda-africa.com/isdasoil/</t>
+          <t>Internal Available on request</t>
         </is>
       </c>
       <c r="W65" s="8" t="n"/>
@@ -7479,12 +7484,12 @@
     <row r="66">
       <c r="A66" s="10" t="inlineStr">
         <is>
-          <t>MFL-2026-067</t>
+          <t>MFL-2026-066</t>
         </is>
       </c>
       <c r="B66" s="10" t="inlineStr">
         <is>
-          <t>Gridded climate data (CHIRPS and AgERA5)</t>
+          <t>iSDAsoil soil properties for the N'Zi watershed (0-20 and 20-50 cm)</t>
         </is>
       </c>
       <c r="C66" s="10" t="inlineStr">
@@ -7494,7 +7499,7 @@
       </c>
       <c r="D66" s="10" t="inlineStr">
         <is>
-          <t>Water / hydrology</t>
+          <t>Degradation / land health</t>
         </is>
       </c>
       <c r="E66" s="10" t="inlineStr">
@@ -7504,17 +7509,17 @@
       </c>
       <c r="F66" s="10" t="inlineStr">
         <is>
-          <t>Tabular</t>
+          <t>Raster</t>
         </is>
       </c>
       <c r="G66" s="10" t="inlineStr">
         <is>
-          <t>0.05° × 0.05° and 0.1° x 0.1°, depending on the products</t>
+          <t>30 m</t>
         </is>
       </c>
       <c r="H66" s="10" t="inlineStr">
         <is>
-          <t>1979 - present</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="I66" s="10" t="inlineStr">
@@ -7552,7 +7557,7 @@
       <c r="Q66" s="10" t="n"/>
       <c r="R66" s="11" t="inlineStr">
         <is>
-          <t>Gridded daily climate data from CHIRPS and ERA5 climate reanalysis</t>
+          <t>Fifteen soil properties from iSDAsoil (iSDA), extracted by AfricaRice for the N'Zi watershed at about 30 m, at 0-20 and 20-50 cm: bulk density, calcium, cation exchange capacity, clay, iron, potassium, magnesium, total nitrogen, phosphorus, pH, sulphur, sand, silt, soil organic carbon and zinc, in physical units. The public source is iSDAsoil for Africa.</t>
         </is>
       </c>
       <c r="S66" s="10" t="n"/>
@@ -7563,12 +7568,12 @@
       </c>
       <c r="U66" s="10" t="inlineStr">
         <is>
-          <t>Seasonal</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="V66" s="10" t="inlineStr">
         <is>
-          <t>CHIRPS data ( https://doi.org/10.15780/G2JQ0P). ERA5 AgERA5 v2.0 (https://doi.org/10.24381/f9c1f09d)</t>
+          <t>https://www.isda-africa.com/isdasoil/</t>
         </is>
       </c>
       <c r="W66" s="10" t="n"/>
@@ -7576,118 +7581,114 @@
     <row r="67">
       <c r="A67" s="8" t="inlineStr">
         <is>
-          <t>MFL-2026-068</t>
+          <t>MFL-2026-067</t>
         </is>
       </c>
       <c r="B67" s="8" t="inlineStr">
         <is>
-          <t>Tree conservation and restoration priority areas (Laos)</t>
+          <t>Gridded climate data (CHIRPS and AgERA5)</t>
         </is>
       </c>
       <c r="C67" s="8" t="inlineStr">
         <is>
-          <t>Laos</t>
+          <t>Côte d'Ivoire</t>
         </is>
       </c>
       <c r="D67" s="8" t="inlineStr">
         <is>
-          <t>Decision-support outputs</t>
+          <t>Water / hydrology</t>
         </is>
       </c>
       <c r="E67" s="8" t="inlineStr">
         <is>
-          <t>NATIONAL — Country-wide coverage</t>
+          <t>CIV-NZ — N'Zi Watershed</t>
         </is>
       </c>
       <c r="F67" s="8" t="inlineStr">
         <is>
-          <t>Raster</t>
+          <t>Tabular</t>
         </is>
       </c>
       <c r="G67" s="8" t="inlineStr">
         <is>
-          <t>1000m</t>
+          <t>0.05° × 0.05° and 0.1° x 0.1°, depending on the products</t>
         </is>
       </c>
       <c r="H67" s="8" t="inlineStr">
         <is>
-          <t>2017-2025</t>
+          <t>1979 - present</t>
         </is>
       </c>
       <c r="I67" s="8" t="inlineStr">
         <is>
-          <t>Alliance Bioversity-CIAT</t>
+          <t>AfricaRice</t>
         </is>
       </c>
       <c r="J67" s="8" t="inlineStr">
         <is>
-          <t>Hannes Gaisberger, h.gaisberger@cgiar.org</t>
+          <t>Louis Kouadio (a.kouadio2@cgiar.org)</t>
         </is>
       </c>
       <c r="K67" s="8" t="inlineStr">
         <is>
-          <t>Restricted</t>
+          <t>Open</t>
         </is>
       </c>
       <c r="L67" s="8" t="inlineStr">
         <is>
-          <t>CGIAR Open Access</t>
-        </is>
-      </c>
-      <c r="M67" s="8" t="n"/>
-      <c r="N67" s="8" t="inlineStr">
-        <is>
-          <t>ex_situ_conservation.tif; expanding_protection.tif; landscape_restoration.tif; maintaining_protection.tif</t>
-        </is>
-      </c>
+          <t>CC BY 4.0</t>
+        </is>
+      </c>
+      <c r="M67" s="8" t="inlineStr">
+        <is>
+          <t>Validated</t>
+        </is>
+      </c>
+      <c r="N67" s="8" t="n"/>
       <c r="O67" s="8" t="inlineStr">
         <is>
-          <t>One drive</t>
+          <t>server and drive</t>
         </is>
       </c>
       <c r="P67" s="8" t="n"/>
-      <c r="Q67" s="8" t="inlineStr">
-        <is>
-          <t>MOSAIC/datasets/MFL-2026-068/raw/</t>
-        </is>
-      </c>
+      <c r="Q67" s="8" t="n"/>
       <c r="R67" s="9" t="inlineStr">
         <is>
-          <t>Conservation for Restoration (C4R) tool LAOS: mapping the vulnerability and priority areas for conservation and restoration of 79 native tree species. Linked to D4R</t>
+          <t>Gridded daily climate data from CHIRPS and ERA5 climate reanalysis</t>
         </is>
       </c>
       <c r="S67" s="8" t="n"/>
       <c r="T67" s="8" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="U67" s="8" t="inlineStr">
         <is>
-          <t>On-demand</t>
-        </is>
-      </c>
-      <c r="V67" s="8" t="n"/>
-      <c r="W67" s="8" t="inlineStr">
-        <is>
-          <t>250 MB</t>
-        </is>
-      </c>
+          <t>Seasonal</t>
+        </is>
+      </c>
+      <c r="V67" s="8" t="inlineStr">
+        <is>
+          <t>CHIRPS data ( https://doi.org/10.15780/G2JQ0P). ERA5 AgERA5 v2.0 (https://doi.org/10.24381/f9c1f09d)</t>
+        </is>
+      </c>
+      <c r="W67" s="8" t="n"/>
     </row>
     <row r="68">
       <c r="A68" s="10" t="inlineStr">
         <is>
-          <t>MFL-2026-069</t>
+          <t>MFL-2026-068</t>
         </is>
       </c>
       <c r="B68" s="10" t="inlineStr">
         <is>
-          <t>Tree conservation and restoration priority areas (Vietnam)</t>
+          <t>Tree conservation and restoration priority areas (Laos)</t>
         </is>
       </c>
       <c r="C68" s="10" t="inlineStr">
         <is>
-          <t>Vietnam</t>
+          <t>Laos</t>
         </is>
       </c>
       <c r="D68" s="10" t="inlineStr">
@@ -7749,12 +7750,12 @@
       <c r="P68" s="10" t="n"/>
       <c r="Q68" s="10" t="inlineStr">
         <is>
-          <t>MOSAIC/datasets/MFL-2026-069/raw/</t>
+          <t>MOSAIC/datasets/MFL-2026-068/raw/</t>
         </is>
       </c>
       <c r="R68" s="11" t="inlineStr">
         <is>
-          <t>Conservation for Restoration (C4R) tool VIETNAM: mapping the vulnerability and priority areas for conservation and restoration of 66 native tree species. Linked to D4R</t>
+          <t>Conservation for Restoration (C4R) tool LAOS: mapping the vulnerability and priority areas for conservation and restoration of 79 native tree species. Linked to D4R</t>
         </is>
       </c>
       <c r="S68" s="10" t="n"/>
@@ -7778,36 +7779,44 @@
     <row r="69">
       <c r="A69" s="8" t="inlineStr">
         <is>
-          <t>MFL-2026-070</t>
+          <t>MFL-2026-069</t>
         </is>
       </c>
       <c r="B69" s="8" t="inlineStr">
         <is>
-          <t>Coding Matrix: Ecosystem Services in Tropical Cattle Systems — A Systematic Literature Review across Five Thematic Streams</t>
+          <t>Tree conservation and restoration priority areas (Vietnam)</t>
         </is>
       </c>
       <c r="C69" s="8" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>Vietnam</t>
         </is>
       </c>
       <c r="D69" s="8" t="inlineStr">
         <is>
-          <t>Ecosystem services</t>
+          <t>Decision-support outputs</t>
         </is>
       </c>
       <c r="E69" s="8" t="inlineStr">
         <is>
-          <t>GLOBAL — Global / cross-landscape</t>
+          <t>NATIONAL — Country-wide coverage</t>
         </is>
       </c>
       <c r="F69" s="8" t="inlineStr">
         <is>
-          <t>Tabular</t>
-        </is>
-      </c>
-      <c r="G69" s="8" t="n"/>
-      <c r="H69" s="8" t="n"/>
+          <t>Raster</t>
+        </is>
+      </c>
+      <c r="G69" s="8" t="inlineStr">
+        <is>
+          <t>1000m</t>
+        </is>
+      </c>
+      <c r="H69" s="8" t="inlineStr">
+        <is>
+          <t>2017-2025</t>
+        </is>
+      </c>
       <c r="I69" s="8" t="inlineStr">
         <is>
           <t>Alliance Bioversity-CIAT</t>
@@ -7815,82 +7824,78 @@
       </c>
       <c r="J69" s="8" t="inlineStr">
         <is>
-          <t>Stefan Burkart (s.burkart@cgiar.org)</t>
+          <t>Hannes Gaisberger, h.gaisberger@cgiar.org</t>
         </is>
       </c>
       <c r="K69" s="8" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Restricted</t>
         </is>
       </c>
       <c r="L69" s="8" t="inlineStr">
         <is>
-          <t>CC BY 4.0</t>
+          <t>CGIAR Open Access</t>
         </is>
       </c>
       <c r="M69" s="8" t="n"/>
       <c r="N69" s="8" t="inlineStr">
         <is>
-          <t>.xlsx</t>
+          <t>ex_situ_conservation.tif; expanding_protection.tif; landscape_restoration.tif; maintaining_protection.tif</t>
         </is>
       </c>
       <c r="O69" s="8" t="inlineStr">
         <is>
-          <t>Harvard Dataverse</t>
+          <t>One drive</t>
         </is>
       </c>
       <c r="P69" s="8" t="n"/>
-      <c r="Q69" s="8" t="n"/>
+      <c r="Q69" s="8" t="inlineStr">
+        <is>
+          <t>MOSAIC/datasets/MFL-2026-069/raw/</t>
+        </is>
+      </c>
       <c r="R69" s="9" t="inlineStr">
         <is>
-          <t>Workbook documenting ~549 coded study entries from a systematic literature review on ecosystem services in tropical and subtropical cattle systems, coded consistently across five thematic streams for cross-paper comparison and filtering. Studies may appear in multiple streams.</t>
-        </is>
-      </c>
-      <c r="S69" s="8" t="inlineStr">
-        <is>
-          <t>2026-08-03</t>
-        </is>
-      </c>
+          <t>Conservation for Restoration (C4R) tool VIETNAM: mapping the vulnerability and priority areas for conservation and restoration of 66 native tree species. Linked to D4R</t>
+        </is>
+      </c>
+      <c r="S69" s="8" t="n"/>
       <c r="T69" s="8" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="U69" s="8" t="inlineStr">
         <is>
-          <t>Static</t>
-        </is>
-      </c>
-      <c r="V69" s="8" t="inlineStr">
-        <is>
-          <t>https://doi.org/10.7910/DVN/XD96CL</t>
-        </is>
-      </c>
+          <t>On-demand</t>
+        </is>
+      </c>
+      <c r="V69" s="8" t="n"/>
       <c r="W69" s="8" t="inlineStr">
         <is>
-          <t>586 KB</t>
+          <t>250 MB</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="10" t="inlineStr">
         <is>
-          <t>MFL-2026-071</t>
+          <t>MFL-2026-070</t>
         </is>
       </c>
       <c r="B70" s="10" t="inlineStr">
         <is>
-          <t>Urochloa hybrid adoption in Latin America and the Caribbean 2001-2024: An analysis of the land use, social, economic, and environmental impacts in 27 countries</t>
+          <t>Coding Matrix: Ecosystem Services in Tropical Cattle Systems — A Systematic Literature Review across Five Thematic Streams</t>
         </is>
       </c>
       <c r="C70" s="10" t="inlineStr">
         <is>
-          <t>Latin America and the Caribbean</t>
+          <t>Global</t>
         </is>
       </c>
       <c r="D70" s="10" t="inlineStr">
         <is>
-          <t>Agrobiodiversity / crops</t>
+          <t>Ecosystem services</t>
         </is>
       </c>
       <c r="E70" s="10" t="inlineStr">
@@ -7904,11 +7909,7 @@
         </is>
       </c>
       <c r="G70" s="10" t="n"/>
-      <c r="H70" s="10" t="inlineStr">
-        <is>
-          <t>2001-2024</t>
-        </is>
-      </c>
+      <c r="H70" s="10" t="n"/>
       <c r="I70" s="10" t="inlineStr">
         <is>
           <t>Alliance Bioversity-CIAT</t>
@@ -7926,13 +7927,13 @@
       </c>
       <c r="L70" s="10" t="inlineStr">
         <is>
-          <t>CC0 1.0</t>
+          <t>CC BY 4.0</t>
         </is>
       </c>
       <c r="M70" s="10" t="n"/>
       <c r="N70" s="10" t="inlineStr">
         <is>
-          <t>1_hybrid_calculation_determinist_LAC.xlsx; 2_environmental calculation_determinist_LAC.xlsx</t>
+          <t>.xlsx</t>
         </is>
       </c>
       <c r="O70" s="10" t="inlineStr">
@@ -7944,7 +7945,7 @@
       <c r="Q70" s="10" t="n"/>
       <c r="R70" s="11" t="inlineStr">
         <is>
-          <t>Analysis of interspecific Urochloa forage-grass hybrid adoption across 27 Latin American and Caribbean countries, 2001-2024. Estimates over 1.09 million adopting farmers on 1.62 million cumulative hectares, projects cumulative forage value of US$47-62 billion by 2033, and estimates potential greenhouse gas emission reductions of 16.9-56.3 Mt CO2-eq by that timeframe.</t>
+          <t>Workbook documenting ~549 coded study entries from a systematic literature review on ecosystem services in tropical and subtropical cattle systems, coded consistently across five thematic streams for cross-paper comparison and filtering. Studies may appear in multiple streams.</t>
         </is>
       </c>
       <c r="S70" s="10" t="inlineStr">
@@ -7964,54 +7965,50 @@
       </c>
       <c r="V70" s="10" t="inlineStr">
         <is>
-          <t>https://doi.org/10.7910/DVN/L86VZ9</t>
+          <t>https://doi.org/10.7910/DVN/XD96CL</t>
         </is>
       </c>
       <c r="W70" s="10" t="inlineStr">
         <is>
-          <t>104.2 KB (2 files)</t>
+          <t>586 KB</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="8" t="inlineStr">
         <is>
-          <t>MFL-2026-072</t>
+          <t>MFL-2026-071</t>
         </is>
       </c>
       <c r="B71" s="8" t="inlineStr">
         <is>
-          <t>Provinces and Districts</t>
+          <t>Urochloa hybrid adoption in Latin America and the Caribbean 2001-2024: An analysis of the land use, social, economic, and environmental impacts in 27 countries</t>
         </is>
       </c>
       <c r="C71" s="8" t="inlineStr">
         <is>
-          <t>Peru</t>
+          <t>Latin America and the Caribbean</t>
         </is>
       </c>
       <c r="D71" s="8" t="inlineStr">
         <is>
-          <t>Boundaries / admin units</t>
+          <t>Agrobiodiversity / crops</t>
         </is>
       </c>
       <c r="E71" s="8" t="inlineStr">
         <is>
-          <t>PER-PCL — Pucallpa – Ucayali</t>
+          <t>GLOBAL — Global / cross-landscape</t>
         </is>
       </c>
       <c r="F71" s="8" t="inlineStr">
         <is>
-          <t>Vector</t>
-        </is>
-      </c>
-      <c r="G71" s="8" t="inlineStr">
-        <is>
-          <t>Admin level 2 and 3</t>
-        </is>
-      </c>
+          <t>Tabular</t>
+        </is>
+      </c>
+      <c r="G71" s="8" t="n"/>
       <c r="H71" s="8" t="inlineStr">
         <is>
-          <t>Current boundaries</t>
+          <t>2001-2024</t>
         </is>
       </c>
       <c r="I71" s="8" t="inlineStr">
@@ -8021,7 +8018,7 @@
       </c>
       <c r="J71" s="8" t="inlineStr">
         <is>
-          <t>Beatriz Rodríguez (b.rodriguez@cgiar.org)</t>
+          <t>Stefan Burkart (s.burkart@cgiar.org)</t>
         </is>
       </c>
       <c r="K71" s="8" t="inlineStr">
@@ -8031,70 +8028,62 @@
       </c>
       <c r="L71" s="8" t="inlineStr">
         <is>
-          <t>Free download from the Peruvian government source (MINAM/GEOBOSQUES, SERNANP, INEI); no formal license stated</t>
-        </is>
-      </c>
-      <c r="M71" s="8" t="inlineStr">
-        <is>
-          <t>Processed</t>
-        </is>
-      </c>
+          <t>CC0 1.0</t>
+        </is>
+      </c>
+      <c r="M71" s="8" t="n"/>
       <c r="N71" s="8" t="inlineStr">
         <is>
-          <t>Ucayali_Provinces_and_Districts.shp (complete shapefile set, 8 files)</t>
+          <t>1_hybrid_calculation_determinist_LAC.xlsx; 2_environmental calculation_determinist_LAC.xlsx</t>
         </is>
       </c>
       <c r="O71" s="8" t="inlineStr">
         <is>
-          <t>One Drive</t>
+          <t>Harvard Dataverse</t>
         </is>
       </c>
       <c r="P71" s="8" t="n"/>
-      <c r="Q71" s="8" t="inlineStr">
-        <is>
-          <t>MOSAIC/datasets/MFL-2026-072/raw/</t>
-        </is>
-      </c>
+      <c r="Q71" s="8" t="n"/>
       <c r="R71" s="9" t="inlineStr">
         <is>
-          <t>Administrative boundaries for Ucayali, Peru</t>
+          <t>Analysis of interspecific Urochloa forage-grass hybrid adoption across 27 Latin American and Caribbean countries, 2001-2024. Estimates over 1.09 million adopting farmers on 1.62 million cumulative hectares, projects cumulative forage value of US$47-62 billion by 2033, and estimates potential greenhouse gas emission reductions of 16.9-56.3 Mt CO2-eq by that timeframe.</t>
         </is>
       </c>
       <c r="S71" s="8" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="T71" s="8" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="U71" s="8" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Static</t>
         </is>
       </c>
       <c r="V71" s="8" t="inlineStr">
         <is>
-          <t>https://www.datosabiertos.gob.pe/dataset/limites-departamentales</t>
+          <t>https://doi.org/10.7910/DVN/L86VZ9</t>
         </is>
       </c>
       <c r="W71" s="8" t="inlineStr">
         <is>
-          <t>1.0 MB</t>
+          <t>104.2 KB (2 files)</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="10" t="inlineStr">
         <is>
-          <t>MFL-2026-073</t>
+          <t>MFL-2026-072</t>
         </is>
       </c>
       <c r="B72" s="10" t="inlineStr">
         <is>
-          <t>National Protected Natural Areas</t>
+          <t>Provinces and Districts</t>
         </is>
       </c>
       <c r="C72" s="10" t="inlineStr">
@@ -8119,12 +8108,12 @@
       </c>
       <c r="G72" s="10" t="inlineStr">
         <is>
-          <t>Boundary level</t>
+          <t>Admin level 2 and 3</t>
         </is>
       </c>
       <c r="H72" s="10" t="inlineStr">
         <is>
-          <t>Current</t>
+          <t>Current boundaries</t>
         </is>
       </c>
       <c r="I72" s="10" t="inlineStr">
@@ -8154,7 +8143,7 @@
       </c>
       <c r="N72" s="10" t="inlineStr">
         <is>
-          <t>Ucayali_National_Protected_Natural_Areas.shp (complete shapefile set, 8 files)</t>
+          <t>Ucayali_Provinces_and_Districts.shp (complete shapefile set, 8 files)</t>
         </is>
       </c>
       <c r="O72" s="10" t="inlineStr">
@@ -8165,12 +8154,12 @@
       <c r="P72" s="10" t="n"/>
       <c r="Q72" s="10" t="inlineStr">
         <is>
-          <t>MOSAIC/datasets/MFL-2026-073/raw/</t>
+          <t>MOSAIC/datasets/MFL-2026-072/raw/</t>
         </is>
       </c>
       <c r="R72" s="11" t="inlineStr">
         <is>
-          <t>National Protected Natural Areas clipped to  Ucayali</t>
+          <t>Administrative boundaries for Ucayali, Peru</t>
         </is>
       </c>
       <c r="S72" s="10" t="inlineStr">
@@ -8190,24 +8179,24 @@
       </c>
       <c r="V72" s="10" t="inlineStr">
         <is>
-          <t>https://geo.sernanp.gob.pe/visorsernanp/</t>
+          <t>https://www.datosabiertos.gob.pe/dataset/limites-departamentales</t>
         </is>
       </c>
       <c r="W72" s="10" t="inlineStr">
         <is>
-          <t>658 KB</t>
+          <t>1.0 MB</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="8" t="inlineStr">
         <is>
-          <t>MFL-2026-074</t>
+          <t>MFL-2026-073</t>
         </is>
       </c>
       <c r="B73" s="8" t="inlineStr">
         <is>
-          <t>Regional Conservation Areas</t>
+          <t>National Protected Natural Areas</t>
         </is>
       </c>
       <c r="C73" s="8" t="inlineStr">
@@ -8267,7 +8256,7 @@
       </c>
       <c r="N73" s="8" t="inlineStr">
         <is>
-          <t>Ucayali_Regional_Conservation_Areas.shp (complete shapefile set, 8 files)</t>
+          <t>Ucayali_National_Protected_Natural_Areas.shp (complete shapefile set, 8 files)</t>
         </is>
       </c>
       <c r="O73" s="8" t="inlineStr">
@@ -8278,12 +8267,12 @@
       <c r="P73" s="8" t="n"/>
       <c r="Q73" s="8" t="inlineStr">
         <is>
-          <t>MOSAIC/datasets/MFL-2026-074/raw/</t>
+          <t>MOSAIC/datasets/MFL-2026-073/raw/</t>
         </is>
       </c>
       <c r="R73" s="9" t="inlineStr">
         <is>
-          <t>Regional Conservation Areas clipped to Ucayali</t>
+          <t>National Protected Natural Areas clipped to  Ucayali</t>
         </is>
       </c>
       <c r="S73" s="8" t="inlineStr">
@@ -8308,19 +8297,19 @@
       </c>
       <c r="W73" s="8" t="inlineStr">
         <is>
-          <t>125 KB</t>
+          <t>658 KB</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="10" t="inlineStr">
         <is>
-          <t>MFL-2026-075</t>
+          <t>MFL-2026-074</t>
         </is>
       </c>
       <c r="B74" s="10" t="inlineStr">
         <is>
-          <t>Indigenous Territories</t>
+          <t>Regional Conservation Areas</t>
         </is>
       </c>
       <c r="C74" s="10" t="inlineStr">
@@ -8350,7 +8339,7 @@
       </c>
       <c r="H74" s="10" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>Current</t>
         </is>
       </c>
       <c r="I74" s="10" t="inlineStr">
@@ -8370,7 +8359,7 @@
       </c>
       <c r="L74" s="10" t="inlineStr">
         <is>
-          <t>Free download from RAISG; no formal license stated</t>
+          <t>Free download from the Peruvian government source (MINAM/GEOBOSQUES, SERNANP, INEI); no formal license stated</t>
         </is>
       </c>
       <c r="M74" s="10" t="inlineStr">
@@ -8380,7 +8369,7 @@
       </c>
       <c r="N74" s="10" t="inlineStr">
         <is>
-          <t>Ucayali_Indigenous_Territories.shp (complete shapefile set, 8 files)</t>
+          <t>Ucayali_Regional_Conservation_Areas.shp (complete shapefile set, 8 files)</t>
         </is>
       </c>
       <c r="O74" s="10" t="inlineStr">
@@ -8391,12 +8380,12 @@
       <c r="P74" s="10" t="n"/>
       <c r="Q74" s="10" t="inlineStr">
         <is>
-          <t>MOSAIC/datasets/MFL-2026-075/raw/</t>
+          <t>MOSAIC/datasets/MFL-2026-074/raw/</t>
         </is>
       </c>
       <c r="R74" s="11" t="inlineStr">
         <is>
-          <t>Indigenous Territories clipped to Ucayali</t>
+          <t>Regional Conservation Areas clipped to Ucayali</t>
         </is>
       </c>
       <c r="S74" s="10" t="inlineStr">
@@ -8416,24 +8405,24 @@
       </c>
       <c r="V74" s="10" t="inlineStr">
         <is>
-          <t>https://www.raisg.org/es/mapas/</t>
+          <t>https://geo.sernanp.gob.pe/visorsernanp/</t>
         </is>
       </c>
       <c r="W74" s="10" t="inlineStr">
         <is>
-          <t>5.3 MB</t>
+          <t>125 KB</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="8" t="inlineStr">
         <is>
-          <t>MFL-2026-076</t>
+          <t>MFL-2026-075</t>
         </is>
       </c>
       <c r="B75" s="8" t="inlineStr">
         <is>
-          <t>National Ecosystem Map</t>
+          <t>Indigenous Territories</t>
         </is>
       </c>
       <c r="C75" s="8" t="inlineStr">
@@ -8443,7 +8432,7 @@
       </c>
       <c r="D75" s="8" t="inlineStr">
         <is>
-          <t>Biodiversity / ecosystems</t>
+          <t>Boundaries / admin units</t>
         </is>
       </c>
       <c r="E75" s="8" t="inlineStr">
@@ -8456,10 +8445,14 @@
           <t>Vector</t>
         </is>
       </c>
-      <c r="G75" s="8" t="n"/>
+      <c r="G75" s="8" t="inlineStr">
+        <is>
+          <t>Boundary level</t>
+        </is>
+      </c>
       <c r="H75" s="8" t="inlineStr">
         <is>
-          <t>2018</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="I75" s="8" t="inlineStr">
@@ -8479,7 +8472,7 @@
       </c>
       <c r="L75" s="8" t="inlineStr">
         <is>
-          <t>Free download from the Peruvian government source (MINAM/GEOBOSQUES, SERNANP, INEI); no formal license stated</t>
+          <t>Free download from RAISG; no formal license stated</t>
         </is>
       </c>
       <c r="M75" s="8" t="inlineStr">
@@ -8489,7 +8482,7 @@
       </c>
       <c r="N75" s="8" t="inlineStr">
         <is>
-          <t>Ucayali_Ecosystems_map.shp (complete shapefile set, 8 files)</t>
+          <t>Ucayali_Indigenous_Territories.shp (complete shapefile set, 8 files)</t>
         </is>
       </c>
       <c r="O75" s="8" t="inlineStr">
@@ -8500,12 +8493,12 @@
       <c r="P75" s="8" t="n"/>
       <c r="Q75" s="8" t="inlineStr">
         <is>
-          <t>MOSAIC/datasets/MFL-2026-076/raw/</t>
+          <t>MOSAIC/datasets/MFL-2026-075/raw/</t>
         </is>
       </c>
       <c r="R75" s="9" t="inlineStr">
         <is>
-          <t>Spatial distribution and classification of ecosystem within Ucayali department, derived from Peru´s National Ecosystem Map 2018, and aggregated by adminstrative provinces and districts level</t>
+          <t>Indigenous Territories clipped to Ucayali</t>
         </is>
       </c>
       <c r="S75" s="8" t="inlineStr">
@@ -8525,24 +8518,24 @@
       </c>
       <c r="V75" s="8" t="inlineStr">
         <is>
-          <t>https://geoservidor.minam.gob.pe/recursos/intercambio-de-datos/</t>
+          <t>https://www.raisg.org/es/mapas/</t>
         </is>
       </c>
       <c r="W75" s="8" t="inlineStr">
         <is>
-          <t>109.7 MB</t>
+          <t>5.3 MB</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="10" t="inlineStr">
         <is>
-          <t>MFL-2026-077</t>
+          <t>MFL-2026-076</t>
         </is>
       </c>
       <c r="B76" s="10" t="inlineStr">
         <is>
-          <t>Human Footprint map</t>
+          <t>National Ecosystem Map</t>
         </is>
       </c>
       <c r="C76" s="10" t="inlineStr">
@@ -8552,7 +8545,7 @@
       </c>
       <c r="D76" s="10" t="inlineStr">
         <is>
-          <t>Pressures / drivers</t>
+          <t>Biodiversity / ecosystems</t>
         </is>
       </c>
       <c r="E76" s="10" t="inlineStr">
@@ -8568,7 +8561,7 @@
       <c r="G76" s="10" t="n"/>
       <c r="H76" s="10" t="inlineStr">
         <is>
-          <t>2012, 2015, 2018, 2021</t>
+          <t>2018</t>
         </is>
       </c>
       <c r="I76" s="10" t="inlineStr">
@@ -8598,7 +8591,7 @@
       </c>
       <c r="N76" s="10" t="inlineStr">
         <is>
-          <t>Ucayali_Human_Footprint_map.shp (complete shapefile set, 8 files)</t>
+          <t>Ucayali_Ecosystems_map.shp (complete shapefile set, 8 files)</t>
         </is>
       </c>
       <c r="O76" s="10" t="inlineStr">
@@ -8609,12 +8602,12 @@
       <c r="P76" s="10" t="n"/>
       <c r="Q76" s="10" t="inlineStr">
         <is>
-          <t>MOSAIC/datasets/MFL-2026-077/raw/</t>
+          <t>MOSAIC/datasets/MFL-2026-076/raw/</t>
         </is>
       </c>
       <c r="R76" s="11" t="inlineStr">
         <is>
-          <t>Human footprint areas &gt;4 in the Ucayali department for 2012, 2015, 2018, and 2021, derived from Peru´s Human Footprint map. The original raster data was converted to vector polygons and aggregated by adminstrative provinces and districts level</t>
+          <t>Spatial distribution and classification of ecosystem within Ucayali department, derived from Peru´s National Ecosystem Map 2018, and aggregated by adminstrative provinces and districts level</t>
         </is>
       </c>
       <c r="S76" s="10" t="inlineStr">
@@ -8639,19 +8632,19 @@
       </c>
       <c r="W76" s="10" t="inlineStr">
         <is>
-          <t>125.6 MB</t>
+          <t>109.7 MB</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="8" t="inlineStr">
         <is>
-          <t>MFL-2026-078</t>
+          <t>MFL-2026-077</t>
         </is>
       </c>
       <c r="B77" s="8" t="inlineStr">
         <is>
-          <t>Physical Vulnerability map</t>
+          <t>Human Footprint map</t>
         </is>
       </c>
       <c r="C77" s="8" t="inlineStr">
@@ -8677,7 +8670,7 @@
       <c r="G77" s="8" t="n"/>
       <c r="H77" s="8" t="inlineStr">
         <is>
-          <t>2011</t>
+          <t>2012, 2015, 2018, 2021</t>
         </is>
       </c>
       <c r="I77" s="8" t="inlineStr">
@@ -8707,7 +8700,7 @@
       </c>
       <c r="N77" s="8" t="inlineStr">
         <is>
-          <t>Ucayali_Physical_Vulnerability_map.shp (complete shapefile set, 8 files)</t>
+          <t>Ucayali_Human_Footprint_map.shp (complete shapefile set, 8 files)</t>
         </is>
       </c>
       <c r="O77" s="8" t="inlineStr">
@@ -8718,12 +8711,12 @@
       <c r="P77" s="8" t="n"/>
       <c r="Q77" s="8" t="inlineStr">
         <is>
-          <t>MOSAIC/datasets/MFL-2026-078/raw/</t>
+          <t>MOSAIC/datasets/MFL-2026-077/raw/</t>
         </is>
       </c>
       <c r="R77" s="9" t="inlineStr">
         <is>
-          <t>Spatial distribution of physical vulnerability levels within the Ucayali department, derived from Peru’s National Physical Vulnerability map 2011, and aggregated by administrative provinces and districts level</t>
+          <t>Human footprint areas &gt;4 in the Ucayali department for 2012, 2015, 2018, and 2021, derived from Peru´s Human Footprint map. The original raster data was converted to vector polygons and aggregated by adminstrative provinces and districts level</t>
         </is>
       </c>
       <c r="S77" s="8" t="inlineStr">
@@ -8748,19 +8741,19 @@
       </c>
       <c r="W77" s="8" t="inlineStr">
         <is>
-          <t>7.8 MB</t>
+          <t>125.6 MB</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="10" t="inlineStr">
         <is>
-          <t>MFL-2026-079</t>
+          <t>MFL-2026-078</t>
         </is>
       </c>
       <c r="B78" s="10" t="inlineStr">
         <is>
-          <t>Forest/Non-forest 2000/Forest loss 2001-2024</t>
+          <t>Physical Vulnerability map</t>
         </is>
       </c>
       <c r="C78" s="10" t="inlineStr">
@@ -8786,7 +8779,7 @@
       <c r="G78" s="10" t="n"/>
       <c r="H78" s="10" t="inlineStr">
         <is>
-          <t>2000-2024</t>
+          <t>2011</t>
         </is>
       </c>
       <c r="I78" s="10" t="inlineStr">
@@ -8816,7 +8809,7 @@
       </c>
       <c r="N78" s="10" t="inlineStr">
         <is>
-          <t>Ucayali_Forest_NonForest2000_ForestLoss2001_2024.shp (complete shapefile set, 8 files)</t>
+          <t>Ucayali_Physical_Vulnerability_map.shp (complete shapefile set, 8 files)</t>
         </is>
       </c>
       <c r="O78" s="10" t="inlineStr">
@@ -8827,12 +8820,12 @@
       <c r="P78" s="10" t="n"/>
       <c r="Q78" s="10" t="inlineStr">
         <is>
-          <t>MOSAIC/datasets/MFL-2026-079/raw/</t>
+          <t>MOSAIC/datasets/MFL-2026-078/raw/</t>
         </is>
       </c>
       <c r="R78" s="11" t="inlineStr">
         <is>
-          <t>Forest/non-forest baseline for 2000 and annual forest loss from 2001 to 2024 in Ucayali, derived from MINAM’s GEOBOSQUES forest monitoring dataset and spatially aggregated by provinces and districts.</t>
+          <t>Spatial distribution of physical vulnerability levels within the Ucayali department, derived from Peru’s National Physical Vulnerability map 2011, and aggregated by administrative provinces and districts level</t>
         </is>
       </c>
       <c r="S78" s="10" t="inlineStr">
@@ -8842,7 +8835,7 @@
       </c>
       <c r="T78" s="10" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="U78" s="10" t="inlineStr">
@@ -8852,24 +8845,24 @@
       </c>
       <c r="V78" s="10" t="inlineStr">
         <is>
-          <t>https://geobosques.minam.gob.pe/geobosque/view/descargas.php?122345gxxe345w34gg#download</t>
+          <t>https://geoservidor.minam.gob.pe/recursos/intercambio-de-datos/</t>
         </is>
       </c>
       <c r="W78" s="10" t="inlineStr">
         <is>
-          <t>175.2 MB</t>
+          <t>7.8 MB</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="8" t="inlineStr">
         <is>
-          <t>MFL-2026-080</t>
+          <t>MFL-2026-079</t>
         </is>
       </c>
       <c r="B79" s="8" t="inlineStr">
         <is>
-          <t>Annual deforestation</t>
+          <t>Forest/Non-forest 2000/Forest loss 2001-2024</t>
         </is>
       </c>
       <c r="C79" s="8" t="inlineStr">
@@ -8895,7 +8888,7 @@
       <c r="G79" s="8" t="n"/>
       <c r="H79" s="8" t="inlineStr">
         <is>
-          <t>2001-2024</t>
+          <t>2000-2024</t>
         </is>
       </c>
       <c r="I79" s="8" t="inlineStr">
@@ -8925,7 +8918,7 @@
       </c>
       <c r="N79" s="8" t="inlineStr">
         <is>
-          <t>Ucayali_Annual_Deforestation_2001_2024.shp (complete shapefile set, 8 files)</t>
+          <t>Ucayali_Forest_NonForest2000_ForestLoss2001_2024.shp (complete shapefile set, 8 files)</t>
         </is>
       </c>
       <c r="O79" s="8" t="inlineStr">
@@ -8936,12 +8929,12 @@
       <c r="P79" s="8" t="n"/>
       <c r="Q79" s="8" t="inlineStr">
         <is>
-          <t>MOSAIC/datasets/MFL-2026-080/raw/</t>
+          <t>MOSAIC/datasets/MFL-2026-079/raw/</t>
         </is>
       </c>
       <c r="R79" s="9" t="inlineStr">
         <is>
-          <t>Annual forest loss from 2001-2024 in Ucayali, derived from MINAM’s GEOBOSQUES forest monitoring dataset and spatially aggregated by provinces and districts. The 2025 update published at source is not yet included in this layer.</t>
+          <t>Forest/non-forest baseline for 2000 and annual forest loss from 2001 to 2024 in Ucayali, derived from MINAM’s GEOBOSQUES forest monitoring dataset and spatially aggregated by provinces and districts.</t>
         </is>
       </c>
       <c r="S79" s="8" t="inlineStr">
@@ -8966,19 +8959,19 @@
       </c>
       <c r="W79" s="8" t="inlineStr">
         <is>
-          <t>143.3 MB</t>
+          <t>175.2 MB</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="10" t="inlineStr">
         <is>
-          <t>MFL-2026-081</t>
+          <t>MFL-2026-080</t>
         </is>
       </c>
       <c r="B80" s="10" t="inlineStr">
         <is>
-          <t>Land Cover and Land Use</t>
+          <t>Annual deforestation</t>
         </is>
       </c>
       <c r="C80" s="10" t="inlineStr">
@@ -8988,7 +8981,7 @@
       </c>
       <c r="D80" s="10" t="inlineStr">
         <is>
-          <t>Land cover / land use</t>
+          <t>Pressures / drivers</t>
         </is>
       </c>
       <c r="E80" s="10" t="inlineStr">
@@ -9001,14 +8994,10 @@
           <t>Vector</t>
         </is>
       </c>
-      <c r="G80" s="10" t="inlineStr">
-        <is>
-          <t>30 m (original dataset)</t>
-        </is>
-      </c>
+      <c r="G80" s="10" t="n"/>
       <c r="H80" s="10" t="inlineStr">
         <is>
-          <t>2000, 2005, 2010, 2015, 2020, 2024</t>
+          <t>2001-2024</t>
         </is>
       </c>
       <c r="I80" s="10" t="inlineStr">
@@ -9028,7 +9017,7 @@
       </c>
       <c r="L80" s="10" t="inlineStr">
         <is>
-          <t>CC BY 4.0</t>
+          <t>Free download from the Peruvian government source (MINAM/GEOBOSQUES, SERNANP, INEI); no formal license stated</t>
         </is>
       </c>
       <c r="M80" s="10" t="inlineStr">
@@ -9038,7 +9027,7 @@
       </c>
       <c r="N80" s="10" t="inlineStr">
         <is>
-          <t>Ucayali_Land_cover_Land_use.shp (complete shapefile set, 8 files)</t>
+          <t>Ucayali_Annual_Deforestation_2001_2024.shp (complete shapefile set, 8 files)</t>
         </is>
       </c>
       <c r="O80" s="10" t="inlineStr">
@@ -9049,12 +9038,12 @@
       <c r="P80" s="10" t="n"/>
       <c r="Q80" s="10" t="inlineStr">
         <is>
-          <t>MOSAIC/datasets/MFL-2026-081/raw/</t>
+          <t>MOSAIC/datasets/MFL-2026-080/raw/</t>
         </is>
       </c>
       <c r="R80" s="11" t="inlineStr">
         <is>
-          <t>Land cover and land-use classification within the Ucayali department for 2000, 2005, 2010, 2015, 2020 and 2024, derived from Mapbiomas Peru Collection 4. The original raster data was converted to vector polygons and aggregated by administrative provinces and districts level</t>
+          <t>Annual forest loss from 2001-2024 in Ucayali, derived from MINAM’s GEOBOSQUES forest monitoring dataset and spatially aggregated by provinces and districts. The 2025 update published at source is not yet included in this layer.</t>
         </is>
       </c>
       <c r="S80" s="10" t="inlineStr">
@@ -9074,24 +9063,24 @@
       </c>
       <c r="V80" s="10" t="inlineStr">
         <is>
-          <t>https://peru.mapbiomas.org/iniciativas-y-productos/cobertura-y-uso-del-suelo/cobertura/</t>
+          <t>https://geobosques.minam.gob.pe/geobosque/view/descargas.php?122345gxxe345w34gg#download</t>
         </is>
       </c>
       <c r="W80" s="10" t="inlineStr">
         <is>
-          <t>520.2 MB</t>
+          <t>143.3 MB</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="8" t="inlineStr">
         <is>
-          <t>MFL-2026-082</t>
+          <t>MFL-2026-081</t>
         </is>
       </c>
       <c r="B81" s="8" t="inlineStr">
         <is>
-          <t>Accumulated Burned Area 2013-2024</t>
+          <t>Land Cover and Land Use</t>
         </is>
       </c>
       <c r="C81" s="8" t="inlineStr">
@@ -9101,7 +9090,7 @@
       </c>
       <c r="D81" s="8" t="inlineStr">
         <is>
-          <t>Pressures / drivers</t>
+          <t>Land cover / land use</t>
         </is>
       </c>
       <c r="E81" s="8" t="inlineStr">
@@ -9121,7 +9110,7 @@
       </c>
       <c r="H81" s="8" t="inlineStr">
         <is>
-          <t>2013-2024</t>
+          <t>2000, 2005, 2010, 2015, 2020, 2024</t>
         </is>
       </c>
       <c r="I81" s="8" t="inlineStr">
@@ -9151,7 +9140,7 @@
       </c>
       <c r="N81" s="8" t="inlineStr">
         <is>
-          <t>Ucayali_Cumulative_Burned_2013_2024.shp (complete shapefile set, 8 files)</t>
+          <t>Ucayali_Land_cover_Land_use.shp (complete shapefile set, 8 files)</t>
         </is>
       </c>
       <c r="O81" s="8" t="inlineStr">
@@ -9162,12 +9151,12 @@
       <c r="P81" s="8" t="n"/>
       <c r="Q81" s="8" t="inlineStr">
         <is>
-          <t>MOSAIC/datasets/MFL-2026-082/raw/</t>
+          <t>MOSAIC/datasets/MFL-2026-081/raw/</t>
         </is>
       </c>
       <c r="R81" s="9" t="inlineStr">
         <is>
-          <t>Cumulative Burned Area during 2013–2024 within the Ucayali department, derived from Mapbiomas Peru Collection 1. The original raster data was converted to vector polygons and aggregated by administrative provinces and districts level</t>
+          <t>Land cover and land-use classification within the Ucayali department for 2000, 2005, 2010, 2015, 2020 and 2024, derived from Mapbiomas Peru Collection 4. The original raster data was converted to vector polygons and aggregated by administrative provinces and districts level</t>
         </is>
       </c>
       <c r="S81" s="8" t="inlineStr">
@@ -9177,7 +9166,7 @@
       </c>
       <c r="T81" s="8" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="U81" s="8" t="inlineStr">
@@ -9187,97 +9176,105 @@
       </c>
       <c r="V81" s="8" t="inlineStr">
         <is>
-          <t>https://peru.mapbiomas.org/iniciativas-y-productos/fuego/mapeo-anual/</t>
+          <t>https://peru.mapbiomas.org/iniciativas-y-productos/cobertura-y-uso-del-suelo/cobertura/</t>
         </is>
       </c>
       <c r="W81" s="8" t="inlineStr">
         <is>
-          <t>13.8 MB</t>
+          <t>520.2 MB</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="10" t="inlineStr">
         <is>
-          <t>MFL-2026-083</t>
+          <t>MFL-2026-082</t>
         </is>
       </c>
       <c r="B82" s="10" t="inlineStr">
         <is>
-          <t>Crop type map</t>
+          <t>Accumulated Burned Area 2013-2024</t>
         </is>
       </c>
       <c r="C82" s="10" t="inlineStr">
         <is>
-          <t>Kenya</t>
+          <t>Peru</t>
         </is>
       </c>
       <c r="D82" s="10" t="inlineStr">
         <is>
-          <t>Ecosystem condition</t>
+          <t>Pressures / drivers</t>
         </is>
       </c>
       <c r="E82" s="10" t="inlineStr">
         <is>
-          <t>KEN-LVB — Lake Victoria Basin (Kenya)</t>
+          <t>PER-PCL — Pucallpa – Ucayali</t>
         </is>
       </c>
       <c r="F82" s="10" t="inlineStr">
         <is>
-          <t>Raster</t>
+          <t>Vector</t>
         </is>
       </c>
       <c r="G82" s="10" t="inlineStr">
         <is>
-          <t>10m</t>
+          <t>30 m (original dataset)</t>
         </is>
       </c>
       <c r="H82" s="10" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>2013-2024</t>
         </is>
       </c>
       <c r="I82" s="10" t="inlineStr">
         <is>
-          <t>IFPRI</t>
+          <t>Alliance Bioversity-CIAT</t>
         </is>
       </c>
       <c r="J82" s="10" t="inlineStr">
         <is>
-          <t>z.guo@cgiar.org</t>
+          <t>Beatriz Rodríguez (b.rodriguez@cgiar.org)</t>
         </is>
       </c>
       <c r="K82" s="10" t="inlineStr">
         <is>
-          <t>Restricted</t>
+          <t>Open</t>
         </is>
       </c>
       <c r="L82" s="10" t="inlineStr">
         <is>
-          <t>CGIAR Open Access</t>
+          <t>CC BY 4.0</t>
         </is>
       </c>
       <c r="M82" s="10" t="inlineStr">
         <is>
-          <t>Validated</t>
-        </is>
-      </c>
-      <c r="N82" s="10" t="n"/>
+          <t>Processed</t>
+        </is>
+      </c>
+      <c r="N82" s="10" t="inlineStr">
+        <is>
+          <t>Ucayali_Cumulative_Burned_2013_2024.shp (complete shapefile set, 8 files)</t>
+        </is>
+      </c>
       <c r="O82" s="10" t="inlineStr">
         <is>
-          <t>One drive</t>
+          <t>One Drive</t>
         </is>
       </c>
       <c r="P82" s="10" t="n"/>
-      <c r="Q82" s="10" t="n"/>
+      <c r="Q82" s="10" t="inlineStr">
+        <is>
+          <t>MOSAIC/datasets/MFL-2026-082/raw/</t>
+        </is>
+      </c>
       <c r="R82" s="11" t="inlineStr">
         <is>
-          <t>Major crop type maps in Nandi county, Kenya</t>
+          <t>Cumulative Burned Area during 2013–2024 within the Ucayali department, derived from Mapbiomas Peru Collection 1. The original raster data was converted to vector polygons and aggregated by administrative provinces and districts level</t>
         </is>
       </c>
       <c r="S82" s="10" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="T82" s="10" t="inlineStr">
@@ -9290,88 +9287,104 @@
           <t>Unknown</t>
         </is>
       </c>
-      <c r="V82" s="10" t="n"/>
-      <c r="W82" s="10" t="n"/>
+      <c r="V82" s="10" t="inlineStr">
+        <is>
+          <t>https://peru.mapbiomas.org/iniciativas-y-productos/fuego/mapeo-anual/</t>
+        </is>
+      </c>
+      <c r="W82" s="10" t="inlineStr">
+        <is>
+          <t>13.8 MB</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="8" t="inlineStr">
         <is>
-          <t>MFL-2026-084</t>
+          <t>MFL-2026-083</t>
         </is>
       </c>
       <c r="B83" s="8" t="inlineStr">
         <is>
-          <t>Climate data AfricaRice M'Bé Research Station</t>
+          <t>Crop type map</t>
         </is>
       </c>
       <c r="C83" s="8" t="inlineStr">
         <is>
-          <t>Côte d'Ivoire</t>
+          <t>Kenya</t>
         </is>
       </c>
       <c r="D83" s="8" t="inlineStr">
         <is>
-          <t>Water / hydrology</t>
+          <t>Ecosystem condition</t>
         </is>
       </c>
       <c r="E83" s="8" t="inlineStr">
         <is>
-          <t>CIV-NZ — N'Zi Watershed</t>
+          <t>KEN-LVB — Lake Victoria Basin (Kenya)</t>
         </is>
       </c>
       <c r="F83" s="8" t="inlineStr">
         <is>
-          <t>Tabular</t>
+          <t>Raster</t>
         </is>
       </c>
       <c r="G83" s="8" t="inlineStr">
         <is>
-          <t>Point level</t>
+          <t>10m</t>
         </is>
       </c>
       <c r="H83" s="8" t="inlineStr">
         <is>
-          <t>2014 - present</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="I83" s="8" t="inlineStr">
         <is>
-          <t>AfricaRice</t>
+          <t>IFPRI</t>
         </is>
       </c>
       <c r="J83" s="8" t="inlineStr">
         <is>
-          <t>Louis Kouadio (a.kouadio2@cgiar.org)</t>
+          <t>z.guo@cgiar.org</t>
         </is>
       </c>
       <c r="K83" s="8" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Restricted</t>
         </is>
       </c>
       <c r="L83" s="8" t="inlineStr">
         <is>
-          <t>AfricaRice Terms of Use (https://www.africarice.org/privacy-policy), the usage policy linked from ARCWeather: attribution with the ARCWeather citation; non-commercial, research, educational or personal use only; reuse under the same conditions. No formal licence issued for the climate data yet</t>
-        </is>
-      </c>
-      <c r="M83" s="8" t="n"/>
+          <t>CGIAR Open Access</t>
+        </is>
+      </c>
+      <c r="M83" s="8" t="inlineStr">
+        <is>
+          <t>Validated</t>
+        </is>
+      </c>
       <c r="N83" s="8" t="n"/>
-      <c r="O83" s="8" t="n"/>
+      <c r="O83" s="8" t="inlineStr">
+        <is>
+          <t>One drive</t>
+        </is>
+      </c>
       <c r="P83" s="8" t="n"/>
       <c r="Q83" s="8" t="n"/>
       <c r="R83" s="9" t="inlineStr">
         <is>
-          <t>Daily weather data from AfricaRice's two weather stations at the M'Bé research station near Bouaké, in the N'Zi watershed: MBE_LOWLAND (273 m) and MBE_UPLAND (303 m), from 2014 onward. Served by AfricaRice's ARCWeather portal.</t>
+          <t>Major crop type maps in Nandi county, Kenya</t>
         </is>
       </c>
       <c r="S83" s="8" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="T83" s="8" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="U83" s="8" t="inlineStr">
@@ -9379,95 +9392,83 @@
           <t>Unknown</t>
         </is>
       </c>
-      <c r="V83" s="8" t="inlineStr">
-        <is>
-          <t>https://arcweather.africarice.org/en/downloads</t>
-        </is>
-      </c>
+      <c r="V83" s="8" t="n"/>
       <c r="W83" s="8" t="n"/>
     </row>
     <row r="84">
       <c r="A84" s="10" t="inlineStr">
         <is>
-          <t>MFL-2026-085</t>
+          <t>MFL-2026-084</t>
         </is>
       </c>
       <c r="B84" s="10" t="inlineStr">
         <is>
-          <t>Landscape Resources</t>
+          <t>Climate data AfricaRice M'Bé Research Station</t>
         </is>
       </c>
       <c r="C84" s="10" t="inlineStr">
         <is>
-          <t>Kenya</t>
+          <t>Côte d'Ivoire</t>
         </is>
       </c>
       <c r="D84" s="10" t="inlineStr">
         <is>
-          <t>Ecosystem services</t>
+          <t>Water / hydrology</t>
         </is>
       </c>
       <c r="E84" s="10" t="inlineStr">
         <is>
-          <t>KEN-LVB — Lake Victoria Basin (Kenya)</t>
+          <t>CIV-NZ — N'Zi Watershed</t>
         </is>
       </c>
       <c r="F84" s="10" t="inlineStr">
         <is>
-          <t>Vector</t>
+          <t>Tabular</t>
         </is>
       </c>
       <c r="G84" s="10" t="inlineStr">
         <is>
-          <t>Basin level</t>
+          <t>Point level</t>
         </is>
       </c>
       <c r="H84" s="10" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2014 - present</t>
         </is>
       </c>
       <c r="I84" s="10" t="inlineStr">
         <is>
-          <t>ILRI</t>
+          <t>AfricaRice</t>
         </is>
       </c>
       <c r="J84" s="10" t="inlineStr">
         <is>
-          <t>Ambica Paliwal (a.paliwal@cgiar.org)</t>
+          <t>Louis Kouadio (a.kouadio2@cgiar.org)</t>
         </is>
       </c>
       <c r="K84" s="10" t="inlineStr">
         <is>
-          <t>Restricted</t>
+          <t>Open</t>
         </is>
       </c>
       <c r="L84" s="10" t="inlineStr">
         <is>
-          <t>Restricted — contact data owner</t>
-        </is>
-      </c>
-      <c r="M84" s="10" t="inlineStr">
-        <is>
-          <t>Raw</t>
-        </is>
-      </c>
+          <t>AfricaRice Terms of Use (https://www.africarice.org/privacy-policy), the usage policy linked from ARCWeather: attribution with the ARCWeather citation; non-commercial, research, educational or personal use only; reuse under the same conditions. No formal licence issued for the climate data yet</t>
+        </is>
+      </c>
+      <c r="M84" s="10" t="n"/>
       <c r="N84" s="10" t="n"/>
-      <c r="O84" s="10" t="inlineStr">
-        <is>
-          <t>One drive</t>
-        </is>
-      </c>
+      <c r="O84" s="10" t="n"/>
       <c r="P84" s="10" t="n"/>
       <c r="Q84" s="10" t="n"/>
       <c r="R84" s="11" t="inlineStr">
         <is>
-          <t>Key natural resources and the ecosystem services they provide to local communities.</t>
+          <t>Daily weather data from AfricaRice's two weather stations at the M'Bé research station near Bouaké, in the N'Zi watershed: MBE_LOWLAND (273 m) and MBE_UPLAND (303 m), from 2014 onward. Served by AfricaRice's ARCWeather portal.</t>
         </is>
       </c>
       <c r="S84" s="10" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="T84" s="10" t="inlineStr">
@@ -9477,12 +9478,12 @@
       </c>
       <c r="U84" s="10" t="inlineStr">
         <is>
-          <t>On-demand</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="V84" s="10" t="inlineStr">
         <is>
-          <t>Internal Available on Request</t>
+          <t>https://arcweather.africarice.org/en/downloads</t>
         </is>
       </c>
       <c r="W84" s="10" t="n"/>
@@ -9490,12 +9491,12 @@
     <row r="85">
       <c r="A85" s="8" t="inlineStr">
         <is>
-          <t>MFL-2026-086</t>
+          <t>MFL-2026-085</t>
         </is>
       </c>
       <c r="B85" s="8" t="inlineStr">
         <is>
-          <t>Resource change</t>
+          <t>Landscape Resources</t>
         </is>
       </c>
       <c r="C85" s="8" t="inlineStr">
@@ -9505,7 +9506,7 @@
       </c>
       <c r="D85" s="8" t="inlineStr">
         <is>
-          <t>Ecosystem condition</t>
+          <t>Ecosystem services</t>
         </is>
       </c>
       <c r="E85" s="8" t="inlineStr">
@@ -9563,7 +9564,7 @@
       <c r="Q85" s="8" t="n"/>
       <c r="R85" s="9" t="inlineStr">
         <is>
-          <t>Changes in the condition and availability of key resources over time.</t>
+          <t>Key natural resources and the ecosystem services they provide to local communities.</t>
         </is>
       </c>
       <c r="S85" s="8" t="inlineStr">
@@ -9591,12 +9592,12 @@
     <row r="86">
       <c r="A86" s="10" t="inlineStr">
         <is>
-          <t>MFL-2026-087</t>
+          <t>MFL-2026-086</t>
         </is>
       </c>
       <c r="B86" s="10" t="inlineStr">
         <is>
-          <t>Environmental challenges</t>
+          <t>Resource change</t>
         </is>
       </c>
       <c r="C86" s="10" t="inlineStr">
@@ -9606,7 +9607,7 @@
       </c>
       <c r="D86" s="10" t="inlineStr">
         <is>
-          <t>Degradation / land health</t>
+          <t>Ecosystem condition</t>
         </is>
       </c>
       <c r="E86" s="10" t="inlineStr">
@@ -9664,7 +9665,7 @@
       <c r="Q86" s="10" t="n"/>
       <c r="R86" s="11" t="inlineStr">
         <is>
-          <t>Areas affected by environmental degradation and land-health challenges.</t>
+          <t>Changes in the condition and availability of key resources over time.</t>
         </is>
       </c>
       <c r="S86" s="10" t="inlineStr">
@@ -9692,12 +9693,12 @@
     <row r="87">
       <c r="A87" s="8" t="inlineStr">
         <is>
-          <t>MFL-2026-088</t>
+          <t>MFL-2026-087</t>
         </is>
       </c>
       <c r="B87" s="8" t="inlineStr">
         <is>
-          <t>Climate risks</t>
+          <t>Environmental challenges</t>
         </is>
       </c>
       <c r="C87" s="8" t="inlineStr">
@@ -9707,7 +9708,7 @@
       </c>
       <c r="D87" s="8" t="inlineStr">
         <is>
-          <t>Ecosystem condition</t>
+          <t>Degradation / land health</t>
         </is>
       </c>
       <c r="E87" s="8" t="inlineStr">
@@ -9765,7 +9766,7 @@
       <c r="Q87" s="8" t="n"/>
       <c r="R87" s="9" t="inlineStr">
         <is>
-          <t>Areas exposed to climate-related environmental risks and stress.</t>
+          <t>Areas affected by environmental degradation and land-health challenges.</t>
         </is>
       </c>
       <c r="S87" s="8" t="inlineStr">
@@ -9793,12 +9794,12 @@
     <row r="88">
       <c r="A88" s="10" t="inlineStr">
         <is>
-          <t>MFL-2026-089</t>
+          <t>MFL-2026-088</t>
         </is>
       </c>
       <c r="B88" s="10" t="inlineStr">
         <is>
-          <t>Livelihood resources</t>
+          <t>Climate risks</t>
         </is>
       </c>
       <c r="C88" s="10" t="inlineStr">
@@ -9808,7 +9809,7 @@
       </c>
       <c r="D88" s="10" t="inlineStr">
         <is>
-          <t>Socio-economic / livelihoods</t>
+          <t>Ecosystem condition</t>
         </is>
       </c>
       <c r="E88" s="10" t="inlineStr">
@@ -9866,7 +9867,7 @@
       <c r="Q88" s="10" t="n"/>
       <c r="R88" s="11" t="inlineStr">
         <is>
-          <t>Resources and infrastructure that support local livelihoods and economic activities.</t>
+          <t>Areas exposed to climate-related environmental risks and stress.</t>
         </is>
       </c>
       <c r="S88" s="10" t="inlineStr">
@@ -9894,12 +9895,12 @@
     <row r="89">
       <c r="A89" s="8" t="inlineStr">
         <is>
-          <t>MFL-2026-090</t>
+          <t>MFL-2026-089</t>
         </is>
       </c>
       <c r="B89" s="8" t="inlineStr">
         <is>
-          <t>Conflicts</t>
+          <t>Livelihood resources</t>
         </is>
       </c>
       <c r="C89" s="8" t="inlineStr">
@@ -9967,7 +9968,7 @@
       <c r="Q89" s="8" t="n"/>
       <c r="R89" s="9" t="inlineStr">
         <is>
-          <t>Locations and resources affected by conflicts and competing uses</t>
+          <t>Resources and infrastructure that support local livelihoods and economic activities.</t>
         </is>
       </c>
       <c r="S89" s="8" t="inlineStr">
@@ -9995,12 +9996,12 @@
     <row r="90">
       <c r="A90" s="10" t="inlineStr">
         <is>
-          <t>MFL-2026-091</t>
+          <t>MFL-2026-090</t>
         </is>
       </c>
       <c r="B90" s="10" t="inlineStr">
         <is>
-          <t>Drivers of change</t>
+          <t>Conflicts</t>
         </is>
       </c>
       <c r="C90" s="10" t="inlineStr">
@@ -10010,7 +10011,7 @@
       </c>
       <c r="D90" s="10" t="inlineStr">
         <is>
-          <t>Pressures / drivers</t>
+          <t>Socio-economic / livelihoods</t>
         </is>
       </c>
       <c r="E90" s="10" t="inlineStr">
@@ -10068,7 +10069,7 @@
       <c r="Q90" s="10" t="n"/>
       <c r="R90" s="11" t="inlineStr">
         <is>
-          <t>Key human and environmental drivers influencing landscape change.</t>
+          <t>Locations and resources affected by conflicts and competing uses</t>
         </is>
       </c>
       <c r="S90" s="10" t="inlineStr">
@@ -10096,12 +10097,12 @@
     <row r="91">
       <c r="A91" s="8" t="inlineStr">
         <is>
-          <t>MFL-2026-092</t>
+          <t>MFL-2026-091</t>
         </is>
       </c>
       <c r="B91" s="8" t="inlineStr">
         <is>
-          <t>Restoration opportunities</t>
+          <t>Drivers of change</t>
         </is>
       </c>
       <c r="C91" s="8" t="inlineStr">
@@ -10111,7 +10112,7 @@
       </c>
       <c r="D91" s="8" t="inlineStr">
         <is>
-          <t>Decision-support outputs</t>
+          <t>Pressures / drivers</t>
         </is>
       </c>
       <c r="E91" s="8" t="inlineStr">
@@ -10169,7 +10170,7 @@
       <c r="Q91" s="8" t="n"/>
       <c r="R91" s="9" t="inlineStr">
         <is>
-          <t>Priority areas and opportunities for restoration and targeted investment.</t>
+          <t>Key human and environmental drivers influencing landscape change.</t>
         </is>
       </c>
       <c r="S91" s="8" t="inlineStr">
@@ -10197,121 +10198,113 @@
     <row r="92">
       <c r="A92" s="10" t="inlineStr">
         <is>
-          <t>MFL-2026-093</t>
+          <t>MFL-2026-092</t>
         </is>
       </c>
       <c r="B92" s="10" t="inlineStr">
         <is>
-          <t>Land cover Kef-Siliana region (2017)</t>
+          <t>Restoration opportunities</t>
         </is>
       </c>
       <c r="C92" s="10" t="inlineStr">
         <is>
-          <t>Tunisia</t>
+          <t>Kenya</t>
         </is>
       </c>
       <c r="D92" s="10" t="inlineStr">
         <is>
-          <t>Land cover / land use</t>
+          <t>Decision-support outputs</t>
         </is>
       </c>
       <c r="E92" s="10" t="inlineStr">
         <is>
-          <t>TUN-NW — Northwestern Tunisia</t>
+          <t>KEN-LVB — Lake Victoria Basin (Kenya)</t>
         </is>
       </c>
       <c r="F92" s="10" t="inlineStr">
         <is>
-          <t>Raster</t>
+          <t>Vector</t>
         </is>
       </c>
       <c r="G92" s="10" t="inlineStr">
         <is>
-          <t>10 m</t>
+          <t>Basin level</t>
         </is>
       </c>
       <c r="H92" s="10" t="inlineStr">
         <is>
-          <t>2017</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="I92" s="10" t="inlineStr">
         <is>
-          <t>ICARDA</t>
+          <t>ILRI</t>
         </is>
       </c>
       <c r="J92" s="10" t="inlineStr">
         <is>
-          <t>Layal Atassi (l.atassi@cgiar.org)</t>
+          <t>Ambica Paliwal (a.paliwal@cgiar.org)</t>
         </is>
       </c>
       <c r="K92" s="10" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Restricted</t>
         </is>
       </c>
       <c r="L92" s="10" t="inlineStr">
         <is>
-          <t>CC BY-SA 4.0</t>
+          <t>Restricted — contact data owner</t>
         </is>
       </c>
       <c r="M92" s="10" t="inlineStr">
         <is>
-          <t>Processed</t>
-        </is>
-      </c>
-      <c r="N92" s="10" t="inlineStr">
-        <is>
-          <t>Land_cover_Kef_Siliana_region_2017.tif; LC_2017.csv</t>
-        </is>
-      </c>
+          <t>Raw</t>
+        </is>
+      </c>
+      <c r="N92" s="10" t="n"/>
       <c r="O92" s="10" t="inlineStr">
         <is>
-          <t>MEL data portal (data.mel.cgiar.org)</t>
+          <t>One drive</t>
         </is>
       </c>
       <c r="P92" s="10" t="n"/>
       <c r="Q92" s="10" t="n"/>
       <c r="R92" s="11" t="inlineStr">
         <is>
-          <t>Land cover map of the Kef-Siliana region, Tunisia, for 2017, produced by ICARDA from ESRI Sentinel-2 Land Cover Explorer rasters (ArcGIS Living Atlas of the World), 10 m cell size. Classes 1 Water; 2 Forest; 4 Flooded vegetation; 5 Crop; 7 Built area; 8 Bare land; 11 Rangeland. Source data coordinate system UTM WGS 84; service coordinate system Web Mercator Auxiliary Sphere WGS 84 (EPSG:3857). Published on ICARDA's MEL data portal with data dictionaries; MOSAIC links to it there.</t>
+          <t>Priority areas and opportunities for restoration and targeted investment.</t>
         </is>
       </c>
       <c r="S92" s="10" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="T92" s="10" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="U92" s="10" t="inlineStr">
         <is>
-          <t>Static</t>
+          <t>On-demand</t>
         </is>
       </c>
       <c r="V92" s="10" t="inlineStr">
         <is>
-          <t>https://hdl.handle.net/20.500.11766.1/FK2/HNCLNU</t>
-        </is>
-      </c>
-      <c r="W92" s="10" t="inlineStr">
-        <is>
-          <t>143 MB</t>
-        </is>
-      </c>
+          <t>Internal Available on Request</t>
+        </is>
+      </c>
+      <c r="W92" s="10" t="n"/>
     </row>
     <row r="93">
       <c r="A93" s="8" t="inlineStr">
         <is>
-          <t>MFL-2026-094</t>
+          <t>MFL-2026-093</t>
         </is>
       </c>
       <c r="B93" s="8" t="inlineStr">
         <is>
-          <t>Land cover Kef-Siliana region (2022)</t>
+          <t>Land cover Kef-Siliana region (2017)</t>
         </is>
       </c>
       <c r="C93" s="8" t="inlineStr">
@@ -10341,7 +10334,7 @@
       </c>
       <c r="H93" s="8" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>2017</t>
         </is>
       </c>
       <c r="I93" s="8" t="inlineStr">
@@ -10371,7 +10364,7 @@
       </c>
       <c r="N93" s="8" t="inlineStr">
         <is>
-          <t>Land_cover_Kef_Siliana_region_2022.tif; LC_2022.csv</t>
+          <t>Land_cover_Kef_Siliana_region_2017.tif; LC_2017.csv</t>
         </is>
       </c>
       <c r="O93" s="8" t="inlineStr">
@@ -10383,7 +10376,7 @@
       <c r="Q93" s="8" t="n"/>
       <c r="R93" s="9" t="inlineStr">
         <is>
-          <t>Land cover map of the Kef-Siliana region, Tunisia, for 2022, produced by ICARDA from ESRI Sentinel-2 Land Cover Explorer rasters (ArcGIS Living Atlas of the World), 10 m cell size. Classes 1 Water; 2 Forest; 4 Flooded vegetation; 5 Crop; 7 Built area; 8 Bare land; 11 Rangeland. Source data coordinate system UTM WGS 84; service coordinate system Web Mercator Auxiliary Sphere WGS 84 (EPSG:3857). Companion to the 2017 map (MFL-2026-093). Published on ICARDA's MEL data portal with data dictionaries; MOSAIC links to it there.</t>
+          <t>Land cover map of the Kef-Siliana region, Tunisia, for 2017, produced by ICARDA from ESRI Sentinel-2 Land Cover Explorer rasters (ArcGIS Living Atlas of the World), 10 m cell size. Classes 1 Water; 2 Forest; 4 Flooded vegetation; 5 Crop; 7 Built area; 8 Bare land; 11 Rangeland. Source data coordinate system UTM WGS 84; service coordinate system Web Mercator Auxiliary Sphere WGS 84 (EPSG:3857). Published on ICARDA's MEL data portal with data dictionaries; MOSAIC links to it there.</t>
         </is>
       </c>
       <c r="S93" s="8" t="inlineStr">
@@ -10393,7 +10386,7 @@
       </c>
       <c r="T93" s="8" t="inlineStr">
         <is>
-          <t>2025-10-30</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="U93" s="8" t="inlineStr">
@@ -10403,7 +10396,7 @@
       </c>
       <c r="V93" s="8" t="inlineStr">
         <is>
-          <t>https://hdl.handle.net/20.500.11766.1/FK2/H4QIFS</t>
+          <t>https://hdl.handle.net/20.500.11766.1/FK2/HNCLNU</t>
         </is>
       </c>
       <c r="W93" s="8" t="inlineStr">
@@ -10415,12 +10408,12 @@
     <row r="94">
       <c r="A94" s="10" t="inlineStr">
         <is>
-          <t>MFL-2026-095</t>
+          <t>MFL-2026-094</t>
         </is>
       </c>
       <c r="B94" s="10" t="inlineStr">
         <is>
-          <t>Land Cover change in Kef-Siliana region (2017-2022)</t>
+          <t>Land cover Kef-Siliana region (2022)</t>
         </is>
       </c>
       <c r="C94" s="10" t="inlineStr">
@@ -10450,7 +10443,7 @@
       </c>
       <c r="H94" s="10" t="inlineStr">
         <is>
-          <t>2017-2022</t>
+          <t>2022</t>
         </is>
       </c>
       <c r="I94" s="10" t="inlineStr">
@@ -10480,7 +10473,7 @@
       </c>
       <c r="N94" s="10" t="inlineStr">
         <is>
-          <t>Land_Cover_change_in_Kef_Siliana_region_2017_2022.tif; LCC_2017_2022.csv</t>
+          <t>Land_cover_Kef_Siliana_region_2022.tif; LC_2022.csv</t>
         </is>
       </c>
       <c r="O94" s="10" t="inlineStr">
@@ -10492,7 +10485,7 @@
       <c r="Q94" s="10" t="n"/>
       <c r="R94" s="11" t="inlineStr">
         <is>
-          <t>Land cover change map of the Kef-Siliana region, Tunisia, between 2017 and 2022, derived from the two land cover maps (MFL-2026-093 and MFL-2026-094) with the Semi-Automatic Classification Plugin in QGIS 3.28.15, 10 m cell size. Pixel values encode the 49 from-to transitions between the seven land cover classes (Water, Forest, Flooded vegetation, Crop, Built area, Bare land, Rangeland); the full key is in the deposit's data dictionary. Source data coordinate system UTM WGS 84; service coordinate system Web Mercator Auxiliary Sphere WGS 84 (EPSG:3857). Published on ICARDA's MEL data portal; MOSAIC links to it there.</t>
+          <t>Land cover map of the Kef-Siliana region, Tunisia, for 2022, produced by ICARDA from ESRI Sentinel-2 Land Cover Explorer rasters (ArcGIS Living Atlas of the World), 10 m cell size. Classes 1 Water; 2 Forest; 4 Flooded vegetation; 5 Crop; 7 Built area; 8 Bare land; 11 Rangeland. Source data coordinate system UTM WGS 84; service coordinate system Web Mercator Auxiliary Sphere WGS 84 (EPSG:3857). Companion to the 2017 map (MFL-2026-093). Published on ICARDA's MEL data portal with data dictionaries; MOSAIC links to it there.</t>
         </is>
       </c>
       <c r="S94" s="10" t="inlineStr">
@@ -10502,7 +10495,7 @@
       </c>
       <c r="T94" s="10" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2025-10-30</t>
         </is>
       </c>
       <c r="U94" s="10" t="inlineStr">
@@ -10512,24 +10505,24 @@
       </c>
       <c r="V94" s="10" t="inlineStr">
         <is>
-          <t>https://hdl.handle.net/20.500.11766.1/FK2/YUXPQY</t>
+          <t>https://hdl.handle.net/20.500.11766.1/FK2/H4QIFS</t>
         </is>
       </c>
       <c r="W94" s="10" t="inlineStr">
         <is>
-          <t>14 MB</t>
+          <t>143 MB</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="8" t="inlineStr">
         <is>
-          <t>MFL-2026-096</t>
+          <t>MFL-2026-095</t>
         </is>
       </c>
       <c r="B95" s="8" t="inlineStr">
         <is>
-          <t>Data on landscape metrics at different scales, Kef-Siliana region and sub-spatial units of the Agroecological Living Lab Landscape in Tunisia (2017-2022)</t>
+          <t>Land Cover change in Kef-Siliana region (2017-2022)</t>
         </is>
       </c>
       <c r="C95" s="8" t="inlineStr">
@@ -10539,7 +10532,7 @@
       </c>
       <c r="D95" s="8" t="inlineStr">
         <is>
-          <t>Ecosystem condition</t>
+          <t>Land cover / land use</t>
         </is>
       </c>
       <c r="E95" s="8" t="inlineStr">
@@ -10549,12 +10542,12 @@
       </c>
       <c r="F95" s="8" t="inlineStr">
         <is>
-          <t>Tabular</t>
+          <t>Raster</t>
         </is>
       </c>
       <c r="G95" s="8" t="inlineStr">
         <is>
-          <t>Region and sub-landscape spatial units</t>
+          <t>10 m</t>
         </is>
       </c>
       <c r="H95" s="8" t="inlineStr">
@@ -10589,7 +10582,7 @@
       </c>
       <c r="N95" s="8" t="inlineStr">
         <is>
-          <t>LM_KS_data.csv; LM_ALL_data.csv</t>
+          <t>Land_Cover_change_in_Kef_Siliana_region_2017_2022.tif; LCC_2017_2022.csv</t>
         </is>
       </c>
       <c r="O95" s="8" t="inlineStr">
@@ -10601,7 +10594,7 @@
       <c r="Q95" s="8" t="n"/>
       <c r="R95" s="9" t="inlineStr">
         <is>
-          <t>Landscape metrics computed from the 2017 and 2022 land cover maps of the Kef-Siliana region (MFL-2026-093 and MFL-2026-094) with the LecoS plugin in QGIS 3.28.15, at two scales - the Kef-Siliana region as a whole and the sub-spatial units of the Agroecological Living Lab Landscape in Tunisia. Delivered as two CSV tables with data dictionaries. Published on ICARDA's MEL data portal; MOSAIC links to it there.</t>
+          <t>Land cover change map of the Kef-Siliana region, Tunisia, between 2017 and 2022, derived from the two land cover maps (MFL-2026-093 and MFL-2026-094) with the Semi-Automatic Classification Plugin in QGIS 3.28.15, 10 m cell size. Pixel values encode the 49 from-to transitions between the seven land cover classes (Water, Forest, Flooded vegetation, Crop, Built area, Bare land, Rangeland); the full key is in the deposit's data dictionary. Source data coordinate system UTM WGS 84; service coordinate system Web Mercator Auxiliary Sphere WGS 84 (EPSG:3857). Published on ICARDA's MEL data portal; MOSAIC links to it there.</t>
         </is>
       </c>
       <c r="S95" s="8" t="inlineStr">
@@ -10621,24 +10614,24 @@
       </c>
       <c r="V95" s="8" t="inlineStr">
         <is>
-          <t>https://hdl.handle.net/20.500.11766.1/FK2/UN7DKQ</t>
+          <t>https://hdl.handle.net/20.500.11766.1/FK2/YUXPQY</t>
         </is>
       </c>
       <c r="W95" s="8" t="inlineStr">
         <is>
-          <t>9.5 KB</t>
+          <t>14 MB</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="10" t="inlineStr">
         <is>
-          <t>MFL-2026-097</t>
+          <t>MFL-2026-096</t>
         </is>
       </c>
       <c r="B96" s="10" t="inlineStr">
         <is>
-          <t>Data on the dynamics of Land Cover at different scales, Kef-Siliana region and sub-spatial units of the Agroecological Living Lab Landscape in Tunisia (2017-2022)</t>
+          <t>Data on landscape metrics at different scales, Kef-Siliana region and sub-spatial units of the Agroecological Living Lab Landscape in Tunisia (2017-2022)</t>
         </is>
       </c>
       <c r="C96" s="10" t="inlineStr">
@@ -10648,7 +10641,7 @@
       </c>
       <c r="D96" s="10" t="inlineStr">
         <is>
-          <t>Degradation / land health</t>
+          <t>Ecosystem condition</t>
         </is>
       </c>
       <c r="E96" s="10" t="inlineStr">
@@ -10698,7 +10691,7 @@
       </c>
       <c r="N96" s="10" t="inlineStr">
         <is>
-          <t>LCD_KS_data.csv; LCD_ALL_data.csv</t>
+          <t>LM_KS_data.csv; LM_ALL_data.csv</t>
         </is>
       </c>
       <c r="O96" s="10" t="inlineStr">
@@ -10710,7 +10703,7 @@
       <c r="Q96" s="10" t="n"/>
       <c r="R96" s="11" t="inlineStr">
         <is>
-          <t>Land cover change statistics and the ecological degradation or improvement they imply, at two scales - the Kef-Siliana region as a whole and the sub-spatial units of the Agroecological Living Lab Landscape in Tunisia. Land cover change was analysed in QGIS 3.28.15 with the Semi-Automatic Classification Plugin; degradation and improvement were assessed following the UNCCD Good Practice Guidance. Delivered as two CSV tables with data dictionaries. Published on ICARDA's MEL data portal; MOSAIC links to it there.</t>
+          <t>Landscape metrics computed from the 2017 and 2022 land cover maps of the Kef-Siliana region (MFL-2026-093 and MFL-2026-094) with the LecoS plugin in QGIS 3.28.15, at two scales - the Kef-Siliana region as a whole and the sub-spatial units of the Agroecological Living Lab Landscape in Tunisia. Delivered as two CSV tables with data dictionaries. Published on ICARDA's MEL data portal; MOSAIC links to it there.</t>
         </is>
       </c>
       <c r="S96" s="10" t="inlineStr">
@@ -10730,64 +10723,64 @@
       </c>
       <c r="V96" s="10" t="inlineStr">
         <is>
-          <t>https://hdl.handle.net/20.500.11766.1/FK2/U4JHNU</t>
+          <t>https://hdl.handle.net/20.500.11766.1/FK2/UN7DKQ</t>
         </is>
       </c>
       <c r="W96" s="10" t="inlineStr">
         <is>
-          <t>18 KB</t>
+          <t>9.5 KB</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="8" t="inlineStr">
         <is>
-          <t>MFL-2026-098</t>
+          <t>MFL-2026-097</t>
         </is>
       </c>
       <c r="B97" s="8" t="inlineStr">
         <is>
-          <t>N'Zi Watershed living landscape boundary</t>
+          <t>Data on the dynamics of Land Cover at different scales, Kef-Siliana region and sub-spatial units of the Agroecological Living Lab Landscape in Tunisia (2017-2022)</t>
         </is>
       </c>
       <c r="C97" s="8" t="inlineStr">
         <is>
-          <t>Côte d'Ivoire</t>
+          <t>Tunisia</t>
         </is>
       </c>
       <c r="D97" s="8" t="inlineStr">
         <is>
-          <t>Boundaries / admin units</t>
+          <t>Degradation / land health</t>
         </is>
       </c>
       <c r="E97" s="8" t="inlineStr">
         <is>
-          <t>CIV-NZ — N'Zi Watershed</t>
+          <t>TUN-NW — Northwestern Tunisia</t>
         </is>
       </c>
       <c r="F97" s="8" t="inlineStr">
         <is>
-          <t>Vector</t>
+          <t>Tabular</t>
         </is>
       </c>
       <c r="G97" s="8" t="inlineStr">
         <is>
-          <t>Landscape boundary</t>
+          <t>Region and sub-landscape spatial units</t>
         </is>
       </c>
       <c r="H97" s="8" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2017-2022</t>
         </is>
       </c>
       <c r="I97" s="8" t="inlineStr">
         <is>
-          <t>Alliance Bioversity-CIAT (MOSAIC)</t>
+          <t>ICARDA</t>
         </is>
       </c>
       <c r="J97" s="8" t="inlineStr">
         <is>
-          <t>Lizeth Llanos (l.llanos@cgiar.org)</t>
+          <t>Layal Atassi (l.atassi@cgiar.org)</t>
         </is>
       </c>
       <c r="K97" s="8" t="inlineStr">
@@ -10797,7 +10790,7 @@
       </c>
       <c r="L97" s="8" t="inlineStr">
         <is>
-          <t>Source terms (https://data.hydrosheds.org/file/technical-documentation/HydroSHEDS_TechDoc_v1_4.pdf)</t>
+          <t>CC BY-SA 4.0</t>
         </is>
       </c>
       <c r="M97" s="8" t="inlineStr">
@@ -10807,29 +10800,29 @@
       </c>
       <c r="N97" s="8" t="inlineStr">
         <is>
-          <t>CIV-NZ_NZi_Watershed_boundary_2026-10-14.zip</t>
+          <t>LCD_KS_data.csv; LCD_ALL_data.csv</t>
         </is>
       </c>
       <c r="O97" s="8" t="inlineStr">
         <is>
-          <t>GitHub release boundaries-2026-10-14 (MOSAIC-mfl/catalog)</t>
+          <t>MEL data portal (data.mel.cgiar.org)</t>
         </is>
       </c>
       <c r="P97" s="8" t="n"/>
       <c r="Q97" s="8" t="n"/>
       <c r="R97" s="9" t="inlineStr">
         <is>
-          <t>Canonical MOSAIC delineation of the N'Zi Watershed living landscape (CIV-NZ), used to define the landscape across the catalogue. Source: HydroBASINS v1c, level 6, basin HYBAS_ID 1060982320 (PFAF_ID 145402), unmodified. HydroSHEDS version 1, World Wildlife Fund (WWF). Full-detail Shapefile and GeoPackage in the dated release boundaries-2026-10-14 of MOSAIC-mfl/catalog; a simplified outline is attached to the landscape's STAC collection.</t>
+          <t>Land cover change statistics and the ecological degradation or improvement they imply, at two scales - the Kef-Siliana region as a whole and the sub-spatial units of the Agroecological Living Lab Landscape in Tunisia. Land cover change was analysed in QGIS 3.28.15 with the Semi-Automatic Classification Plugin; degradation and improvement were assessed following the UNCCD Good Practice Guidance. Delivered as two CSV tables with data dictionaries. Published on ICARDA's MEL data portal; MOSAIC links to it there.</t>
         </is>
       </c>
       <c r="S97" s="8" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="T97" s="8" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="U97" s="8" t="inlineStr">
@@ -10839,29 +10832,29 @@
       </c>
       <c r="V97" s="8" t="inlineStr">
         <is>
-          <t>https://github.com/MOSAIC-mfl/catalog/releases/download/boundaries-2026-10-14/CIV-NZ_NZi_Watershed_boundary_2026-10-14.zip</t>
+          <t>https://hdl.handle.net/20.500.11766.1/FK2/U4JHNU</t>
         </is>
       </c>
       <c r="W97" s="8" t="inlineStr">
         <is>
-          <t>19 KB</t>
+          <t>18 KB</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="10" t="inlineStr">
         <is>
-          <t>MFL-2026-099</t>
+          <t>MFL-2026-098</t>
         </is>
       </c>
       <c r="B98" s="10" t="inlineStr">
         <is>
-          <t>Cumbal (Nariño) living landscape boundary</t>
+          <t>N'Zi Watershed living landscape boundary</t>
         </is>
       </c>
       <c r="C98" s="10" t="inlineStr">
         <is>
-          <t>Colombia</t>
+          <t>Côte d'Ivoire</t>
         </is>
       </c>
       <c r="D98" s="10" t="inlineStr">
@@ -10871,7 +10864,7 @@
       </c>
       <c r="E98" s="10" t="inlineStr">
         <is>
-          <t>COL-CUM — Cumbal (Nariño)</t>
+          <t>CIV-NZ — N'Zi Watershed</t>
         </is>
       </c>
       <c r="F98" s="10" t="inlineStr">
@@ -10906,7 +10899,7 @@
       </c>
       <c r="L98" s="10" t="inlineStr">
         <is>
-          <t>No licence stated by the source</t>
+          <t>Source terms (https://data.hydrosheds.org/file/technical-documentation/HydroSHEDS_TechDoc_v1_4.pdf)</t>
         </is>
       </c>
       <c r="M98" s="10" t="inlineStr">
@@ -10916,7 +10909,7 @@
       </c>
       <c r="N98" s="10" t="inlineStr">
         <is>
-          <t>COL-CUM_Cumbal_Narino_boundary_2026-10-14.zip</t>
+          <t>CIV-NZ_NZi_Watershed_boundary_2026-10-14.zip</t>
         </is>
       </c>
       <c r="O98" s="10" t="inlineStr">
@@ -10928,7 +10921,7 @@
       <c r="Q98" s="10" t="n"/>
       <c r="R98" s="11" t="inlineStr">
         <is>
-          <t>Canonical MOSAIC delineation of the Cumbal (Nariño) living landscape (COL-CUM), used to define the landscape across the catalogue. Source: Nine veredas of the Cumbal indigenous reserve area (Tasmag, Quilismal, Boyera, Cuaical, Cuaspud Grande, Llano de Piedras, Cuetial, Guan, San Martin-Miraflores), layer 'Cumbal_veredas_wgs84' compiled by Javier Ochoa (CIP). Original source to be confirmed. Full-detail Shapefile and GeoPackage in the dated release boundaries-2026-10-14 of MOSAIC-mfl/catalog; a simplified outline is attached to the landscape's STAC collection.</t>
+          <t>Canonical MOSAIC delineation of the N'Zi Watershed living landscape (CIV-NZ), used to define the landscape across the catalogue. Source: HydroBASINS v1c, level 6, basin HYBAS_ID 1060982320 (PFAF_ID 145402), unmodified. HydroSHEDS version 1, World Wildlife Fund (WWF). Full-detail Shapefile and GeoPackage in the dated release boundaries-2026-10-14 of MOSAIC-mfl/catalog; a simplified outline is attached to the landscape's STAC collection.</t>
         </is>
       </c>
       <c r="S98" s="10" t="inlineStr">
@@ -10948,29 +10941,29 @@
       </c>
       <c r="V98" s="10" t="inlineStr">
         <is>
-          <t>https://github.com/MOSAIC-mfl/catalog/releases/download/boundaries-2026-10-14/COL-CUM_Cumbal_Narino_boundary_2026-10-14.zip</t>
+          <t>https://github.com/MOSAIC-mfl/catalog/releases/download/boundaries-2026-10-14/CIV-NZ_NZi_Watershed_boundary_2026-10-14.zip</t>
         </is>
       </c>
       <c r="W98" s="10" t="inlineStr">
         <is>
-          <t>12 KB</t>
+          <t>19 KB</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="8" t="inlineStr">
         <is>
-          <t>MFL-2026-100</t>
+          <t>MFL-2026-099</t>
         </is>
       </c>
       <c r="B99" s="8" t="inlineStr">
         <is>
-          <t>Omo-Gibe Basin living landscape boundary</t>
+          <t>Cumbal (Nariño) living landscape boundary</t>
         </is>
       </c>
       <c r="C99" s="8" t="inlineStr">
         <is>
-          <t>Ethiopia</t>
+          <t>Colombia</t>
         </is>
       </c>
       <c r="D99" s="8" t="inlineStr">
@@ -10980,7 +10973,7 @@
       </c>
       <c r="E99" s="8" t="inlineStr">
         <is>
-          <t>ETH-OG — Omo-Gibe Basin</t>
+          <t>COL-CUM — Cumbal (Nariño)</t>
         </is>
       </c>
       <c r="F99" s="8" t="inlineStr">
@@ -11015,7 +11008,7 @@
       </c>
       <c r="L99" s="8" t="inlineStr">
         <is>
-          <t>CC BY 4.0</t>
+          <t>No licence stated by the source</t>
         </is>
       </c>
       <c r="M99" s="8" t="inlineStr">
@@ -11025,7 +11018,7 @@
       </c>
       <c r="N99" s="8" t="inlineStr">
         <is>
-          <t>ETH-OG_Omo-Gibe_Basin_boundary_2026-10-14.zip</t>
+          <t>COL-CUM_Cumbal_Narino_boundary_2026-10-14.zip</t>
         </is>
       </c>
       <c r="O99" s="8" t="inlineStr">
@@ -11037,7 +11030,7 @@
       <c r="Q99" s="8" t="n"/>
       <c r="R99" s="9" t="inlineStr">
         <is>
-          <t>Canonical MOSAIC delineation of the Omo-Gibe Basin living landscape (ETH-OG), used to define the landscape across the catalogue. Source: Ethiopia River Basins (eth_basins), World Bank Group, World Bank Data Catalog dataset 0040202: Omo basin polygon (79,549 km2). Full-detail Shapefile and GeoPackage in the dated release boundaries-2026-10-14 of MOSAIC-mfl/catalog; a simplified outline is attached to the landscape's STAC collection.</t>
+          <t>Canonical MOSAIC delineation of the Cumbal (Nariño) living landscape (COL-CUM), used to define the landscape across the catalogue. Source: Nine veredas of the Cumbal indigenous reserve area (Tasmag, Quilismal, Boyera, Cuaical, Cuaspud Grande, Llano de Piedras, Cuetial, Guan, San Martin-Miraflores), layer 'Cumbal_veredas_wgs84' compiled by Javier Ochoa (CIP). Original source to be confirmed. Full-detail Shapefile and GeoPackage in the dated release boundaries-2026-10-14 of MOSAIC-mfl/catalog; a simplified outline is attached to the landscape's STAC collection.</t>
         </is>
       </c>
       <c r="S99" s="8" t="inlineStr">
@@ -11057,29 +11050,29 @@
       </c>
       <c r="V99" s="8" t="inlineStr">
         <is>
-          <t>https://github.com/MOSAIC-mfl/catalog/releases/download/boundaries-2026-10-14/ETH-OG_Omo-Gibe_Basin_boundary_2026-10-14.zip</t>
+          <t>https://github.com/MOSAIC-mfl/catalog/releases/download/boundaries-2026-10-14/COL-CUM_Cumbal_Narino_boundary_2026-10-14.zip</t>
         </is>
       </c>
       <c r="W99" s="8" t="inlineStr">
         <is>
-          <t>50 KB</t>
+          <t>12 KB</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="10" t="inlineStr">
         <is>
-          <t>MFL-2026-101</t>
+          <t>MFL-2026-100</t>
         </is>
       </c>
       <c r="B100" s="10" t="inlineStr">
         <is>
-          <t>LEILA (Southern Kenya Rangelands) living landscape boundary</t>
+          <t>Omo-Gibe Basin living landscape boundary</t>
         </is>
       </c>
       <c r="C100" s="10" t="inlineStr">
         <is>
-          <t>Kenya</t>
+          <t>Ethiopia</t>
         </is>
       </c>
       <c r="D100" s="10" t="inlineStr">
@@ -11089,7 +11082,7 @@
       </c>
       <c r="E100" s="10" t="inlineStr">
         <is>
-          <t>KEN-LEI — LEILA (Southern Kenya Rangelands)</t>
+          <t>ETH-OG — Omo-Gibe Basin</t>
         </is>
       </c>
       <c r="F100" s="10" t="inlineStr">
@@ -11124,7 +11117,7 @@
       </c>
       <c r="L100" s="10" t="inlineStr">
         <is>
-          <t>Source terms (https://gadm.org/license.html)</t>
+          <t>CC BY 4.0</t>
         </is>
       </c>
       <c r="M100" s="10" t="inlineStr">
@@ -11134,7 +11127,7 @@
       </c>
       <c r="N100" s="10" t="inlineStr">
         <is>
-          <t>KEN-LEI_LEILA_Southern_Kenya_Rangelands_boundary_2026-10-14.zip</t>
+          <t>ETH-OG_Omo-Gibe_Basin_boundary_2026-10-14.zip</t>
         </is>
       </c>
       <c r="O100" s="10" t="inlineStr">
@@ -11146,7 +11139,7 @@
       <c r="Q100" s="10" t="n"/>
       <c r="R100" s="11" t="inlineStr">
         <is>
-          <t>Canonical MOSAIC delineation of the LEILA (Southern Kenya Rangelands) living landscape (KEN-LEI), used to define the landscape across the catalogue. Source: GADM 4.1, level 1: counties Kajiado (KEN.10_1), Kiambu (KEN.13_1), Machakos (KEN.22_1) and Makueni (KEN.23_1), unmodified. Full-detail Shapefile and GeoPackage in the dated release boundaries-2026-10-14 of MOSAIC-mfl/catalog; a simplified outline is attached to the landscape's STAC collection.</t>
+          <t>Canonical MOSAIC delineation of the Omo-Gibe Basin living landscape (ETH-OG), used to define the landscape across the catalogue. Source: Ethiopia River Basins (eth_basins), World Bank Group, World Bank Data Catalog dataset 0040202: Omo basin polygon (79,549 km2). Full-detail Shapefile and GeoPackage in the dated release boundaries-2026-10-14 of MOSAIC-mfl/catalog; a simplified outline is attached to the landscape's STAC collection.</t>
         </is>
       </c>
       <c r="S100" s="10" t="inlineStr">
@@ -11166,24 +11159,24 @@
       </c>
       <c r="V100" s="10" t="inlineStr">
         <is>
-          <t>https://github.com/MOSAIC-mfl/catalog/releases/download/boundaries-2026-10-14/KEN-LEI_LEILA_Southern_Kenya_Rangelands_boundary_2026-10-14.zip</t>
+          <t>https://github.com/MOSAIC-mfl/catalog/releases/download/boundaries-2026-10-14/ETH-OG_Omo-Gibe_Basin_boundary_2026-10-14.zip</t>
         </is>
       </c>
       <c r="W100" s="10" t="inlineStr">
         <is>
-          <t>315 KB</t>
+          <t>50 KB</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="8" t="inlineStr">
         <is>
-          <t>MFL-2026-102</t>
+          <t>MFL-2026-101</t>
         </is>
       </c>
       <c r="B101" s="8" t="inlineStr">
         <is>
-          <t>Lake Victoria Basin (Kenya) living landscape boundary</t>
+          <t>LEILA (Southern Kenya Rangelands) living landscape boundary</t>
         </is>
       </c>
       <c r="C101" s="8" t="inlineStr">
@@ -11198,7 +11191,7 @@
       </c>
       <c r="E101" s="8" t="inlineStr">
         <is>
-          <t>KEN-LVB — Lake Victoria Basin (Kenya)</t>
+          <t>KEN-LEI — LEILA (Southern Kenya Rangelands)</t>
         </is>
       </c>
       <c r="F101" s="8" t="inlineStr">
@@ -11243,7 +11236,7 @@
       </c>
       <c r="N101" s="8" t="inlineStr">
         <is>
-          <t>KEN-LVB_Lake_Victoria_Basin_Kenya_boundary_2026-10-14.zip</t>
+          <t>KEN-LEI_LEILA_Southern_Kenya_Rangelands_boundary_2026-10-14.zip</t>
         </is>
       </c>
       <c r="O101" s="8" t="inlineStr">
@@ -11255,7 +11248,7 @@
       <c r="Q101" s="8" t="n"/>
       <c r="R101" s="9" t="inlineStr">
         <is>
-          <t>Canonical MOSAIC delineation of the Lake Victoria Basin (Kenya) living landscape (KEN-LVB), used to define the landscape across the catalogue. Source: GADM 4.1, level 1: counties Kakamega (KEN.11_1), Kisumu (KEN.17_1), Siaya (KEN.38_1) and Vihiga (KEN.45_1), unmodified. Full-detail Shapefile and GeoPackage in the dated release boundaries-2026-10-14 of MOSAIC-mfl/catalog; a simplified outline is attached to the landscape's STAC collection.</t>
+          <t>Canonical MOSAIC delineation of the LEILA (Southern Kenya Rangelands) living landscape (KEN-LEI), used to define the landscape across the catalogue. Source: GADM 4.1, level 1: counties Kajiado (KEN.10_1), Kiambu (KEN.13_1), Machakos (KEN.22_1) and Makueni (KEN.23_1), unmodified. Full-detail Shapefile and GeoPackage in the dated release boundaries-2026-10-14 of MOSAIC-mfl/catalog; a simplified outline is attached to the landscape's STAC collection.</t>
         </is>
       </c>
       <c r="S101" s="8" t="inlineStr">
@@ -11275,29 +11268,29 @@
       </c>
       <c r="V101" s="8" t="inlineStr">
         <is>
-          <t>https://github.com/MOSAIC-mfl/catalog/releases/download/boundaries-2026-10-14/KEN-LVB_Lake_Victoria_Basin_Kenya_boundary_2026-10-14.zip</t>
+          <t>https://github.com/MOSAIC-mfl/catalog/releases/download/boundaries-2026-10-14/KEN-LEI_LEILA_Southern_Kenya_Rangelands_boundary_2026-10-14.zip</t>
         </is>
       </c>
       <c r="W101" s="8" t="inlineStr">
         <is>
-          <t>117 KB</t>
+          <t>315 KB</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="10" t="inlineStr">
         <is>
-          <t>MFL-2026-103</t>
+          <t>MFL-2026-102</t>
         </is>
       </c>
       <c r="B102" s="10" t="inlineStr">
         <is>
-          <t>Pucallpa – Ucayali living landscape boundary</t>
+          <t>Lake Victoria Basin (Kenya) living landscape boundary</t>
         </is>
       </c>
       <c r="C102" s="10" t="inlineStr">
         <is>
-          <t>Peru</t>
+          <t>Kenya</t>
         </is>
       </c>
       <c r="D102" s="10" t="inlineStr">
@@ -11307,7 +11300,7 @@
       </c>
       <c r="E102" s="10" t="inlineStr">
         <is>
-          <t>PER-PCL — Pucallpa – Ucayali</t>
+          <t>KEN-LVB — Lake Victoria Basin (Kenya)</t>
         </is>
       </c>
       <c r="F102" s="10" t="inlineStr">
@@ -11342,7 +11335,7 @@
       </c>
       <c r="L102" s="10" t="inlineStr">
         <is>
-          <t>No licence stated by the source</t>
+          <t>Source terms (https://gadm.org/license.html)</t>
         </is>
       </c>
       <c r="M102" s="10" t="inlineStr">
@@ -11352,7 +11345,7 @@
       </c>
       <c r="N102" s="10" t="inlineStr">
         <is>
-          <t>PER-PCL_Pucallpa_Ucayali_boundary_2026-10-14.zip</t>
+          <t>KEN-LVB_Lake_Victoria_Basin_Kenya_boundary_2026-10-14.zip</t>
         </is>
       </c>
       <c r="O102" s="10" t="inlineStr">
@@ -11364,7 +11357,7 @@
       <c r="Q102" s="10" t="n"/>
       <c r="R102" s="11" t="inlineStr">
         <is>
-          <t>Canonical MOSAIC delineation of the Pucallpa – Ucayali living landscape (PER-PCL), used to define the landscape across the catalogue. Source: INEI referential census district limits (cartography of the V Censo Nacional Economico 2022; 'Distrital' layer, ide.inei.gob.pe): 11 whole districts of Coronel Portillo and Padre Abad provinces (Ucayali) and a clipped part of Calleria. Full-detail Shapefile and GeoPackage in the dated release boundaries-2026-10-14 of MOSAIC-mfl/catalog; a simplified outline is attached to the landscape's STAC collection.</t>
+          <t>Canonical MOSAIC delineation of the Lake Victoria Basin (Kenya) living landscape (KEN-LVB), used to define the landscape across the catalogue. Source: GADM 4.1, level 1: counties Kakamega (KEN.11_1), Kisumu (KEN.17_1), Siaya (KEN.38_1) and Vihiga (KEN.45_1), unmodified. Full-detail Shapefile and GeoPackage in the dated release boundaries-2026-10-14 of MOSAIC-mfl/catalog; a simplified outline is attached to the landscape's STAC collection.</t>
         </is>
       </c>
       <c r="S102" s="10" t="inlineStr">
@@ -11384,29 +11377,29 @@
       </c>
       <c r="V102" s="10" t="inlineStr">
         <is>
-          <t>https://github.com/MOSAIC-mfl/catalog/releases/download/boundaries-2026-10-14/PER-PCL_Pucallpa_Ucayali_boundary_2026-10-14.zip</t>
+          <t>https://github.com/MOSAIC-mfl/catalog/releases/download/boundaries-2026-10-14/KEN-LVB_Lake_Victoria_Basin_Kenya_boundary_2026-10-14.zip</t>
         </is>
       </c>
       <c r="W102" s="10" t="inlineStr">
         <is>
-          <t>82 KB</t>
+          <t>117 KB</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="8" t="inlineStr">
         <is>
-          <t>MFL-2026-104</t>
+          <t>MFL-2026-103</t>
         </is>
       </c>
       <c r="B103" s="8" t="inlineStr">
         <is>
-          <t>Fatick Department living landscape boundary</t>
+          <t>Pucallpa – Ucayali living landscape boundary</t>
         </is>
       </c>
       <c r="C103" s="8" t="inlineStr">
         <is>
-          <t>Senegal</t>
+          <t>Peru</t>
         </is>
       </c>
       <c r="D103" s="8" t="inlineStr">
@@ -11416,7 +11409,7 @@
       </c>
       <c r="E103" s="8" t="inlineStr">
         <is>
-          <t>SEN-FK — Fatick Department</t>
+          <t>PER-PCL — Pucallpa – Ucayali</t>
         </is>
       </c>
       <c r="F103" s="8" t="inlineStr">
@@ -11451,7 +11444,7 @@
       </c>
       <c r="L103" s="8" t="inlineStr">
         <is>
-          <t>Source terms (https://gadm.org/license.html)</t>
+          <t>No licence stated by the source</t>
         </is>
       </c>
       <c r="M103" s="8" t="inlineStr">
@@ -11461,7 +11454,7 @@
       </c>
       <c r="N103" s="8" t="inlineStr">
         <is>
-          <t>SEN-FK_Fatick_Department_boundary_2026-10-14.zip</t>
+          <t>PER-PCL_Pucallpa_Ucayali_boundary_2026-10-14.zip</t>
         </is>
       </c>
       <c r="O103" s="8" t="inlineStr">
@@ -11473,7 +11466,7 @@
       <c r="Q103" s="8" t="n"/>
       <c r="R103" s="9" t="inlineStr">
         <is>
-          <t>Canonical MOSAIC delineation of the Fatick Department living landscape (SEN-FK), used to define the landscape across the catalogue. Source: GADM: level 2 unit Fatick departement (GADM v2 attribute schema; geometry identical to GADM 3.6 and 4.1 SEN.3.1_1). Full-detail Shapefile and GeoPackage in the dated release boundaries-2026-10-14 of MOSAIC-mfl/catalog; a simplified outline is attached to the landscape's STAC collection.</t>
+          <t>Canonical MOSAIC delineation of the Pucallpa – Ucayali living landscape (PER-PCL), used to define the landscape across the catalogue. Source: INEI referential census district limits (cartography of the V Censo Nacional Economico 2022; 'Distrital' layer, ide.inei.gob.pe): 11 whole districts of Coronel Portillo and Padre Abad provinces (Ucayali) and a clipped part of Calleria. Full-detail Shapefile and GeoPackage in the dated release boundaries-2026-10-14 of MOSAIC-mfl/catalog; a simplified outline is attached to the landscape's STAC collection.</t>
         </is>
       </c>
       <c r="S103" s="8" t="inlineStr">
@@ -11493,29 +11486,29 @@
       </c>
       <c r="V103" s="8" t="inlineStr">
         <is>
-          <t>https://github.com/MOSAIC-mfl/catalog/releases/download/boundaries-2026-10-14/SEN-FK_Fatick_Department_boundary_2026-10-14.zip</t>
+          <t>https://github.com/MOSAIC-mfl/catalog/releases/download/boundaries-2026-10-14/PER-PCL_Pucallpa_Ucayali_boundary_2026-10-14.zip</t>
         </is>
       </c>
       <c r="W103" s="8" t="inlineStr">
         <is>
-          <t>16 KB</t>
+          <t>82 KB</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="10" t="inlineStr">
         <is>
-          <t>MFL-2026-105</t>
+          <t>MFL-2026-104</t>
         </is>
       </c>
       <c r="B104" s="10" t="inlineStr">
         <is>
-          <t>Mbire – Lower Zambezi Valley living landscape boundary</t>
+          <t>Fatick Department living landscape boundary</t>
         </is>
       </c>
       <c r="C104" s="10" t="inlineStr">
         <is>
-          <t>Zimbabwe</t>
+          <t>Senegal</t>
         </is>
       </c>
       <c r="D104" s="10" t="inlineStr">
@@ -11525,7 +11518,7 @@
       </c>
       <c r="E104" s="10" t="inlineStr">
         <is>
-          <t>ZWE-MB — Mbire – Lower Zambezi Valley</t>
+          <t>SEN-FK — Fatick Department</t>
         </is>
       </c>
       <c r="F104" s="10" t="inlineStr">
@@ -11570,7 +11563,7 @@
       </c>
       <c r="N104" s="10" t="inlineStr">
         <is>
-          <t>ZWE-MB_Mbire_Lower_Zambezi_Valley_boundary_2026-10-14.zip</t>
+          <t>SEN-FK_Fatick_Department_boundary_2026-10-14.zip</t>
         </is>
       </c>
       <c r="O104" s="10" t="inlineStr">
@@ -11582,37 +11575,608 @@
       <c r="Q104" s="10" t="n"/>
       <c r="R104" s="11" t="inlineStr">
         <is>
+          <t>Canonical MOSAIC delineation of the Fatick Department living landscape (SEN-FK), used to define the landscape across the catalogue. Source: GADM: level 2 unit Fatick departement (GADM v2 attribute schema; geometry identical to GADM 3.6 and 4.1 SEN.3.1_1). Full-detail Shapefile and GeoPackage in the dated release boundaries-2026-10-14 of MOSAIC-mfl/catalog; a simplified outline is attached to the landscape's STAC collection.</t>
+        </is>
+      </c>
+      <c r="S104" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="T104" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="U104" s="10" t="inlineStr">
+        <is>
+          <t>Static</t>
+        </is>
+      </c>
+      <c r="V104" s="10" t="inlineStr">
+        <is>
+          <t>https://github.com/MOSAIC-mfl/catalog/releases/download/boundaries-2026-10-14/SEN-FK_Fatick_Department_boundary_2026-10-14.zip</t>
+        </is>
+      </c>
+      <c r="W104" s="10" t="inlineStr">
+        <is>
+          <t>16 KB</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="8" t="inlineStr">
+        <is>
+          <t>MFL-2026-105</t>
+        </is>
+      </c>
+      <c r="B105" s="8" t="inlineStr">
+        <is>
+          <t>Mbire – Lower Zambezi Valley living landscape boundary</t>
+        </is>
+      </c>
+      <c r="C105" s="8" t="inlineStr">
+        <is>
+          <t>Zimbabwe</t>
+        </is>
+      </c>
+      <c r="D105" s="8" t="inlineStr">
+        <is>
+          <t>Boundaries / admin units</t>
+        </is>
+      </c>
+      <c r="E105" s="8" t="inlineStr">
+        <is>
+          <t>ZWE-MB — Mbire – Lower Zambezi Valley</t>
+        </is>
+      </c>
+      <c r="F105" s="8" t="inlineStr">
+        <is>
+          <t>Vector</t>
+        </is>
+      </c>
+      <c r="G105" s="8" t="inlineStr">
+        <is>
+          <t>Landscape boundary</t>
+        </is>
+      </c>
+      <c r="H105" s="8" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="I105" s="8" t="inlineStr">
+        <is>
+          <t>Alliance Bioversity-CIAT (MOSAIC)</t>
+        </is>
+      </c>
+      <c r="J105" s="8" t="inlineStr">
+        <is>
+          <t>Lizeth Llanos (l.llanos@cgiar.org)</t>
+        </is>
+      </c>
+      <c r="K105" s="8" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="L105" s="8" t="inlineStr">
+        <is>
+          <t>Source terms (https://gadm.org/license.html)</t>
+        </is>
+      </c>
+      <c r="M105" s="8" t="inlineStr">
+        <is>
+          <t>Processed</t>
+        </is>
+      </c>
+      <c r="N105" s="8" t="inlineStr">
+        <is>
+          <t>ZWE-MB_Mbire_Lower_Zambezi_Valley_boundary_2026-10-14.zip</t>
+        </is>
+      </c>
+      <c r="O105" s="8" t="inlineStr">
+        <is>
+          <t>GitHub release boundaries-2026-10-14 (MOSAIC-mfl/catalog)</t>
+        </is>
+      </c>
+      <c r="P105" s="8" t="n"/>
+      <c r="Q105" s="8" t="n"/>
+      <c r="R105" s="9" t="inlineStr">
+        <is>
           <t>Canonical MOSAIC delineation of the Mbire – Lower Zambezi Valley living landscape (ZWE-MB), used to define the landscape across the catalogue. Source: GADM 4.1, level 3: all 112 wards of the districts Mbire, Centenary/Muzarabani and Mount Darwin (Mashonaland Central) and Hurungwe (Mashonaland West), unmodified. Full-detail Shapefile and GeoPackage in the dated release boundaries-2026-10-14 of MOSAIC-mfl/catalog; a simplified outline is attached to the landscape's STAC collection.</t>
         </is>
       </c>
-      <c r="S104" s="10" t="inlineStr">
+      <c r="S105" s="8" t="inlineStr">
         <is>
           <t>2026-10-21</t>
         </is>
       </c>
-      <c r="T104" s="10" t="inlineStr">
+      <c r="T105" s="8" t="inlineStr">
         <is>
           <t>2026-10-14</t>
         </is>
       </c>
-      <c r="U104" s="10" t="inlineStr">
+      <c r="U105" s="8" t="inlineStr">
         <is>
           <t>Static</t>
         </is>
       </c>
-      <c r="V104" s="10" t="inlineStr">
+      <c r="V105" s="8" t="inlineStr">
         <is>
           <t>https://github.com/MOSAIC-mfl/catalog/releases/download/boundaries-2026-10-14/ZWE-MB_Mbire_Lower_Zambezi_Valley_boundary_2026-10-14.zip</t>
         </is>
       </c>
-      <c r="W104" s="10" t="inlineStr">
+      <c r="W105" s="8" t="inlineStr">
         <is>
           <t>185 KB</t>
         </is>
       </c>
     </row>
+    <row r="106">
+      <c r="A106" s="10" t="inlineStr">
+        <is>
+          <t>MFL-2026-106</t>
+        </is>
+      </c>
+      <c r="B106" s="10" t="inlineStr">
+        <is>
+          <t>Microwatershed boundaries and drainage network - India</t>
+        </is>
+      </c>
+      <c r="C106" s="10" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="D106" s="10" t="inlineStr">
+        <is>
+          <t>Water / hydrology</t>
+        </is>
+      </c>
+      <c r="E106" s="10" t="inlineStr">
+        <is>
+          <t>IND-CH — Central India Highlands</t>
+        </is>
+      </c>
+      <c r="F106" s="10" t="inlineStr">
+        <is>
+          <t>Mixed</t>
+        </is>
+      </c>
+      <c r="G106" s="10" t="inlineStr">
+        <is>
+          <t>Multiple resolutions</t>
+        </is>
+      </c>
+      <c r="H106" s="10" t="inlineStr">
+        <is>
+          <t>Static</t>
+        </is>
+      </c>
+      <c r="I106" s="10" t="inlineStr">
+        <is>
+          <t>CoRE Stack (external)</t>
+        </is>
+      </c>
+      <c r="J106" s="10" t="inlineStr">
+        <is>
+          <t>Core Stack (Open access)
+Sudharsan Malaiappan - s.maliappan@cgiar.org</t>
+        </is>
+      </c>
+      <c r="K106" s="10" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="L106" s="10" t="inlineStr">
+        <is>
+          <t>CC BY 4.0</t>
+        </is>
+      </c>
+      <c r="M106" s="10" t="inlineStr">
+        <is>
+          <t>Processed</t>
+        </is>
+      </c>
+      <c r="N106" s="10" t="n"/>
+      <c r="O106" s="10" t="inlineStr">
+        <is>
+          <t>CoRE Stack: public Google Earth Engine assets and Google Drive downloads, one row per layer in the CoRE Stack GEE Layers Links sheet (Hydrological boundaries and Drainage layers groups). Map viewer: https://ee-corestackdev.projects.earthengine.app/view/core-stack-gee-app</t>
+        </is>
+      </c>
+      <c r="P106" s="10" t="n"/>
+      <c r="Q106" s="10" t="n"/>
+      <c r="R106" s="11" t="inlineStr">
+        <is>
+          <t>CoRE Stack hydrological layers. Microwatershed boundaries (v1 and v2) and microwatershed connectivity; drainage lines, stream order, distance to upstream drainage line, single-flow and multi-flow catchment area, and natural depressions. Pan-India.</t>
+        </is>
+      </c>
+      <c r="S106" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="T106" s="10" t="n"/>
+      <c r="U106" s="10" t="inlineStr">
+        <is>
+          <t>Static</t>
+        </is>
+      </c>
+      <c r="V106" s="10" t="inlineStr">
+        <is>
+          <t>https://docs.google.com/spreadsheets/d/1xS5d7vgyjyoqqnmmajKDZBx9qS6GqyAdSbNDR62ot2Y/edit?gid=0</t>
+        </is>
+      </c>
+      <c r="W106" s="10" t="n"/>
+    </row>
+    <row r="107">
+      <c r="A107" s="8" t="inlineStr">
+        <is>
+          <t>MFL-2026-107</t>
+        </is>
+      </c>
+      <c r="B107" s="8" t="inlineStr">
+        <is>
+          <t>Climate hazard and drought indices - India</t>
+        </is>
+      </c>
+      <c r="C107" s="8" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="D107" s="8" t="inlineStr">
+        <is>
+          <t>Scenarios / future risks</t>
+        </is>
+      </c>
+      <c r="E107" s="8" t="inlineStr">
+        <is>
+          <t>IND-CH — Central India Highlands</t>
+        </is>
+      </c>
+      <c r="F107" s="8" t="inlineStr">
+        <is>
+          <t>Raster</t>
+        </is>
+      </c>
+      <c r="G107" s="8" t="n"/>
+      <c r="H107" s="8" t="n"/>
+      <c r="I107" s="8" t="inlineStr">
+        <is>
+          <t>CoRE Stack (external)</t>
+        </is>
+      </c>
+      <c r="J107" s="8" t="inlineStr">
+        <is>
+          <t>Core Stack (Open access)
+Sudharsan Malaiappan - s.maliappan@cgiar.org</t>
+        </is>
+      </c>
+      <c r="K107" s="8" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="L107" s="8" t="inlineStr">
+        <is>
+          <t>CoRE Stack layers; no licence stated in the CoRE Stack layer sheet</t>
+        </is>
+      </c>
+      <c r="M107" s="8" t="inlineStr">
+        <is>
+          <t>Processed</t>
+        </is>
+      </c>
+      <c r="N107" s="8" t="n"/>
+      <c r="O107" s="8" t="inlineStr">
+        <is>
+          <t>CoRE Stack: public Google Earth Engine assets and Google Drive downloads, one row per layer in the CoRE Stack GEE Layers Links sheet (Hazard Index group). Map viewer: https://ee-corestackdev.projects.earthengine.app/view/core-stack-gee-app</t>
+        </is>
+      </c>
+      <c r="P107" s="8" t="n"/>
+      <c r="Q107" s="8" t="n"/>
+      <c r="R107" s="9" t="inlineStr">
+        <is>
+          <t>CoRE Stack Hazard Index layers. Extreme rainfall, forest fire and high wind speed indices, and SPEI drought indices at 1, 3 and 12 months (monthly, seasonal and annual drought). Pan-India.</t>
+        </is>
+      </c>
+      <c r="S107" s="8" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="T107" s="8" t="n"/>
+      <c r="U107" s="8" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="V107" s="8" t="inlineStr">
+        <is>
+          <t>https://docs.google.com/spreadsheets/d/1xS5d7vgyjyoqqnmmajKDZBx9qS6GqyAdSbNDR62ot2Y/edit?gid=0</t>
+        </is>
+      </c>
+      <c r="W107" s="8" t="n"/>
+    </row>
+    <row r="108">
+      <c r="A108" s="10" t="inlineStr">
+        <is>
+          <t>MFL-2026-108</t>
+        </is>
+      </c>
+      <c r="B108" s="10" t="inlineStr">
+        <is>
+          <t>Restoration opportunities and plantation site suitability - India</t>
+        </is>
+      </c>
+      <c r="C108" s="10" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="D108" s="10" t="inlineStr">
+        <is>
+          <t>Hotspots / leverage points</t>
+        </is>
+      </c>
+      <c r="E108" s="10" t="inlineStr">
+        <is>
+          <t>IND-CH — Central India Highlands</t>
+        </is>
+      </c>
+      <c r="F108" s="10" t="inlineStr">
+        <is>
+          <t>Raster</t>
+        </is>
+      </c>
+      <c r="G108" s="10" t="n"/>
+      <c r="H108" s="10" t="inlineStr">
+        <is>
+          <t>Static</t>
+        </is>
+      </c>
+      <c r="I108" s="10" t="inlineStr">
+        <is>
+          <t>WRI India and CoRE Stack (external)</t>
+        </is>
+      </c>
+      <c r="J108" s="10" t="inlineStr">
+        <is>
+          <t>Core Stack (Open access)
+Sudharsan Malaiappan - s.maliappan@cgiar.org</t>
+        </is>
+      </c>
+      <c r="K108" s="10" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="L108" s="10" t="inlineStr">
+        <is>
+          <t>Mixed per layer: WRI India atlas re-published by CoRE Stack with no licence stated; plantation site suitability licensed as stated in the CoRE Stack layer sheet</t>
+        </is>
+      </c>
+      <c r="M108" s="10" t="inlineStr">
+        <is>
+          <t>Processed</t>
+        </is>
+      </c>
+      <c r="N108" s="10" t="n"/>
+      <c r="O108" s="10" t="inlineStr">
+        <is>
+          <t>CoRE Stack: public Google Earth Engine assets and Google Drive downloads, one row per layer in the CoRE Stack GEE Layers Links sheet (WRI restoration opportunities atlas and Plantation Site Suitability groups). Map viewer: https://ee-corestackdev.projects.earthengine.app/view/core-stack-gee-app</t>
+        </is>
+      </c>
+      <c r="P108" s="10" t="n"/>
+      <c r="Q108" s="10" t="n"/>
+      <c r="R108" s="11" t="inlineStr">
+        <is>
+          <t>Two layers for restoration planning. The Restoration Opportunities Atlas of WRI India, re-published by CoRE Stack, and the plantation site suitability layer of CoRE Stack (CC BY 4.0 per the sheet). Pan-India.</t>
+        </is>
+      </c>
+      <c r="S108" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="T108" s="10" t="n"/>
+      <c r="U108" s="10" t="inlineStr">
+        <is>
+          <t>Static</t>
+        </is>
+      </c>
+      <c r="V108" s="10" t="inlineStr">
+        <is>
+          <t>https://docs.google.com/spreadsheets/d/1xS5d7vgyjyoqqnmmajKDZBx9qS6GqyAdSbNDR62ot2Y/edit?gid=0</t>
+        </is>
+      </c>
+      <c r="W108" s="10" t="n"/>
+    </row>
+    <row r="109">
+      <c r="A109" s="8" t="inlineStr">
+        <is>
+          <t>MFL-2026-109</t>
+        </is>
+      </c>
+      <c r="B109" s="8" t="inlineStr">
+        <is>
+          <t>Land-use pressures: mining, industry, energy and land conflicts - India</t>
+        </is>
+      </c>
+      <c r="C109" s="8" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="D109" s="8" t="inlineStr">
+        <is>
+          <t>Pressures / drivers</t>
+        </is>
+      </c>
+      <c r="E109" s="8" t="inlineStr">
+        <is>
+          <t>IND-CH — Central India Highlands</t>
+        </is>
+      </c>
+      <c r="F109" s="8" t="inlineStr">
+        <is>
+          <t>Vector</t>
+        </is>
+      </c>
+      <c r="G109" s="8" t="n"/>
+      <c r="H109" s="8" t="n"/>
+      <c r="I109" s="8" t="inlineStr">
+        <is>
+          <t>Land Conflict Watch, ASI, Global Energy Monitor and others, via CoRE Stack (external)</t>
+        </is>
+      </c>
+      <c r="J109" s="8" t="inlineStr">
+        <is>
+          <t>Core Stack (Open access)
+Sudharsan Malaiappan - s.maliappan@cgiar.org</t>
+        </is>
+      </c>
+      <c r="K109" s="8" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="L109" s="8" t="inlineStr">
+        <is>
+          <t>Third-party layers re-published by CoRE Stack; licence set by each source (Land Conflict Watch, Pande et al. 2020, ASI, Global Energy Monitor)</t>
+        </is>
+      </c>
+      <c r="M109" s="8" t="inlineStr">
+        <is>
+          <t>Processed</t>
+        </is>
+      </c>
+      <c r="N109" s="8" t="n"/>
+      <c r="O109" s="8" t="inlineStr">
+        <is>
+          <t>CoRE Stack: public Google Earth Engine assets and Google Drive downloads, one row per layer in the CoRE Stack GEE Layers Links sheet (Industry group). Map viewer: https://ee-corestackdev.projects.earthengine.app/view/core-stack-gee-app</t>
+        </is>
+      </c>
+      <c r="P109" s="8" t="n"/>
+      <c r="Q109" s="8" t="n"/>
+      <c r="R109" s="9" t="inlineStr">
+        <is>
+          <t>Layers re-published by CoRE Stack. Land conflicts (Land Conflict Watch), mining (Pande et al., 2020), industries (Annual Survey of Industries), and solar and wind power plants (Global Energy Monitor). Pan-India.</t>
+        </is>
+      </c>
+      <c r="S109" s="8" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="T109" s="8" t="n"/>
+      <c r="U109" s="8" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="V109" s="8" t="inlineStr">
+        <is>
+          <t>https://docs.google.com/spreadsheets/d/1xS5d7vgyjyoqqnmmajKDZBx9qS6GqyAdSbNDR62ot2Y/edit?gid=0</t>
+        </is>
+      </c>
+      <c r="W109" s="8" t="n"/>
+    </row>
+    <row r="110">
+      <c r="A110" s="10" t="inlineStr">
+        <is>
+          <t>MFL-2026-110</t>
+        </is>
+      </c>
+      <c r="B110" s="10" t="inlineStr">
+        <is>
+          <t>Soil type, nutrients and organic carbon - India</t>
+        </is>
+      </c>
+      <c r="C110" s="10" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="D110" s="10" t="inlineStr">
+        <is>
+          <t>Degradation / land health</t>
+        </is>
+      </c>
+      <c r="E110" s="10" t="inlineStr">
+        <is>
+          <t>IND-CH — Central India Highlands</t>
+        </is>
+      </c>
+      <c r="F110" s="10" t="inlineStr">
+        <is>
+          <t>Raster</t>
+        </is>
+      </c>
+      <c r="G110" s="10" t="n"/>
+      <c r="H110" s="10" t="n"/>
+      <c r="I110" s="10" t="inlineStr">
+        <is>
+          <t>CoRE Stack (external)</t>
+        </is>
+      </c>
+      <c r="J110" s="10" t="inlineStr">
+        <is>
+          <t>Core Stack (Open access)
+Sudharsan Malaiappan - s.maliappan@cgiar.org</t>
+        </is>
+      </c>
+      <c r="K110" s="10" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="L110" s="10" t="inlineStr">
+        <is>
+          <t>CoRE Stack layers; no licence stated in the CoRE Stack layer sheet</t>
+        </is>
+      </c>
+      <c r="M110" s="10" t="inlineStr">
+        <is>
+          <t>Processed</t>
+        </is>
+      </c>
+      <c r="N110" s="10" t="n"/>
+      <c r="O110" s="10" t="inlineStr">
+        <is>
+          <t>CoRE Stack: public Google Earth Engine assets and Google Drive downloads, one row per layer in the CoRE Stack GEE Layers Links sheet (Soil group). Map viewer: https://ee-corestackdev.projects.earthengine.app/view/core-stack-gee-app</t>
+        </is>
+      </c>
+      <c r="P110" s="10" t="n"/>
+      <c r="Q110" s="10" t="n"/>
+      <c r="R110" s="11" t="inlineStr">
+        <is>
+          <t>CoRE Stack soil layers. Soil type; soil nitrogen, phosphorus and potassium; and soil organic carbon over cropland and over trees and shrubs. The nutrient and carbon layers come from Random Forest models trained on Government of India Soil Health Card data (Soil Health Training Data tab of the sheet). Pan-India.</t>
+        </is>
+      </c>
+      <c r="S110" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="T110" s="10" t="n"/>
+      <c r="U110" s="10" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="V110" s="10" t="inlineStr">
+        <is>
+          <t>https://docs.google.com/spreadsheets/d/1xS5d7vgyjyoqqnmmajKDZBx9qS6GqyAdSbNDR62ot2Y/edit?gid=0</t>
+        </is>
+      </c>
+      <c r="W110" s="10" t="n"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A2:W104"/>
+  <autoFilter ref="A2:W110"/>
   <conditionalFormatting sqref="K3:K300">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
       <formula>"Open"</formula>
